--- a/research/traditional_assets/database/data/luxembourg/luxembourg_food_processing.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_food_processing.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,115 +593,115 @@
         <v>0.106</v>
       </c>
       <c r="G2">
-        <v>0.2858866960102229</v>
+        <v>0.2802302312919398</v>
       </c>
       <c r="H2">
-        <v>0.2858866960102229</v>
+        <v>0.2789786668363703</v>
       </c>
       <c r="I2">
-        <v>0.1264375976146528</v>
+        <v>0.1195420829709453</v>
       </c>
       <c r="J2">
-        <v>0.1264375976146528</v>
+        <v>0.1195420829709453</v>
       </c>
       <c r="K2">
-        <v>158.5</v>
+        <v>151.19</v>
       </c>
       <c r="L2">
-        <v>0.1125230725543093</v>
+        <v>0.106906231659631</v>
       </c>
       <c r="M2">
-        <v>100.5</v>
+        <v>100.805</v>
       </c>
       <c r="N2">
-        <v>0.1056893469344831</v>
+        <v>0.1026841193847408</v>
       </c>
       <c r="O2">
-        <v>0.6340694006309149</v>
+        <v>0.6667438322640387</v>
       </c>
       <c r="P2">
         <v>35</v>
       </c>
       <c r="Q2">
-        <v>0.03680723525081502</v>
+        <v>0.03565243964551289</v>
       </c>
       <c r="R2">
-        <v>0.2208201892744479</v>
+        <v>0.2314967921158807</v>
       </c>
       <c r="S2">
-        <v>65.5</v>
+        <v>65.80500000000001</v>
       </c>
       <c r="T2">
-        <v>0.6517412935323383</v>
+        <v>0.6527950002480036</v>
       </c>
       <c r="U2">
-        <v>198.3</v>
+        <v>203.69</v>
       </c>
       <c r="V2">
-        <v>0.2085392785781891</v>
+        <v>0.2074870123255577</v>
       </c>
       <c r="W2">
-        <v>0.1256639974629351</v>
+        <v>-0.2990491893873443</v>
       </c>
       <c r="X2">
-        <v>0.09804474311484875</v>
+        <v>0.09001430126360015</v>
       </c>
       <c r="Y2">
-        <v>0.02761925434808633</v>
+        <v>-0.3890634906509445</v>
       </c>
       <c r="Z2">
-        <v>0.5976240984302079</v>
+        <v>0.5974856451436417</v>
       </c>
       <c r="AA2">
-        <v>0.07556215528213832</v>
+        <v>-0.4156244795863357</v>
       </c>
       <c r="AB2">
-        <v>0.07004807014224784</v>
+        <v>0.06978470351456062</v>
       </c>
       <c r="AC2">
-        <v>0.005514085139890476</v>
+        <v>-0.4854091831008963</v>
       </c>
       <c r="AD2">
-        <v>1213.7</v>
+        <v>1228.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1213.7</v>
+        <v>1228.4</v>
       </c>
       <c r="AG2">
-        <v>1015.4</v>
+        <v>1024.71</v>
       </c>
       <c r="AH2">
-        <v>0.5607040561766609</v>
+        <v>0.5558119542102168</v>
       </c>
       <c r="AI2">
-        <v>0.4580518549269729</v>
+        <v>0.4598647808866361</v>
       </c>
       <c r="AJ2">
-        <v>0.5164013629659767</v>
+        <v>0.5107181483345877</v>
       </c>
       <c r="AK2">
-        <v>0.4142122868564902</v>
+        <v>0.4152776258039417</v>
       </c>
       <c r="AL2">
-        <v>66.5</v>
+        <v>67.67</v>
       </c>
       <c r="AM2">
-        <v>54.1</v>
+        <v>53.88</v>
       </c>
       <c r="AN2">
-        <v>3.095383830655445</v>
+        <v>3.199458248684691</v>
       </c>
       <c r="AO2">
-        <v>2.678195488721804</v>
+        <v>2.498300576326289</v>
       </c>
       <c r="AP2">
-        <v>2.589645498597297</v>
+        <v>2.668932645725895</v>
       </c>
       <c r="AQ2">
-        <v>3.292051756007393</v>
+        <v>3.137713437268003</v>
       </c>
     </row>
     <row r="3">
@@ -775,10 +775,10 @@
         <v>0.1256639974629351</v>
       </c>
       <c r="X3">
-        <v>0.09804474311484875</v>
+        <v>0.09801115439013375</v>
       </c>
       <c r="Y3">
-        <v>0.02761925434808633</v>
+        <v>0.02765284307280133</v>
       </c>
       <c r="Z3">
         <v>0.5976240984302079</v>
@@ -787,10 +787,10 @@
         <v>0.07556215528213832</v>
       </c>
       <c r="AB3">
-        <v>0.07004807014224784</v>
+        <v>0.07003331475172234</v>
       </c>
       <c r="AC3">
-        <v>0.005514085139890476</v>
+        <v>0.005528840530415982</v>
       </c>
       <c r="AD3">
         <v>1213.7</v>
@@ -833,6 +833,134 @@
       </c>
       <c r="AQ3">
         <v>3.292051756007393</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Moolec Science SA (NasdaqCM:MLEC)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Food Processing</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>-1.134991119005329</v>
+      </c>
+      <c r="H4">
+        <v>-1.449378330373002</v>
+      </c>
+      <c r="I4">
+        <v>-1.605683836589698</v>
+      </c>
+      <c r="J4">
+        <v>-1.605683836589698</v>
+      </c>
+      <c r="K4">
+        <v>-7.31</v>
+      </c>
+      <c r="L4">
+        <v>-1.298401420959147</v>
+      </c>
+      <c r="M4">
+        <v>0.305</v>
+      </c>
+      <c r="N4">
+        <v>0.009902597402597402</v>
+      </c>
+      <c r="O4">
+        <v>-0.04172366621067031</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0.305</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>5.39</v>
+      </c>
+      <c r="V4">
+        <v>0.175</v>
+      </c>
+      <c r="W4">
+        <v>-0.7237623762376237</v>
+      </c>
+      <c r="X4">
+        <v>0.08201744813706655</v>
+      </c>
+      <c r="Y4">
+        <v>-0.8057798243746903</v>
+      </c>
+      <c r="Z4">
+        <v>0.5647507272544888</v>
+      </c>
+      <c r="AA4">
+        <v>-0.9068111144548097</v>
+      </c>
+      <c r="AB4">
+        <v>0.06953609227739889</v>
+      </c>
+      <c r="AC4">
+        <v>-0.9763472067322085</v>
+      </c>
+      <c r="AD4">
+        <v>14.7</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>14.7</v>
+      </c>
+      <c r="AG4">
+        <v>9.309999999999999</v>
+      </c>
+      <c r="AH4">
+        <v>0.323076923076923</v>
+      </c>
+      <c r="AI4">
+        <v>0.6830855018587361</v>
+      </c>
+      <c r="AJ4">
+        <v>0.2321116928446771</v>
+      </c>
+      <c r="AK4">
+        <v>0.5771853688778673</v>
+      </c>
+      <c r="AL4">
+        <v>1.17</v>
+      </c>
+      <c r="AM4">
+        <v>-0.22</v>
+      </c>
+      <c r="AN4">
+        <v>-1.801470588235294</v>
+      </c>
+      <c r="AO4">
+        <v>-7.726495726495727</v>
+      </c>
+      <c r="AP4">
+        <v>-1.140931372549019</v>
+      </c>
+      <c r="AQ4">
+        <v>41.09090909090909</v>
       </c>
     </row>
   </sheetData>
@@ -1127,49 +1255,49 @@
         <v>2.6781954887218</v>
       </c>
       <c r="F2">
-        <v>4.58995337175872</v>
+        <v>4.52306435868235</v>
       </c>
       <c r="G2">
         <v>3.09538383065544</v>
       </c>
       <c r="H2">
-        <v>2.64985462892119</v>
+        <v>2.81547054322877</v>
       </c>
       <c r="I2">
         <v>0.560704056176661</v>
       </c>
       <c r="J2">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="K2">
         <v>950.9</v>
       </c>
       <c r="L2">
-        <v>1291.18460693855</v>
+        <v>1354.30487416081</v>
       </c>
       <c r="M2">
         <v>1966.3</v>
       </c>
       <c r="N2">
-        <v>2131.89260693855</v>
+        <v>2259.95087416081</v>
       </c>
       <c r="O2">
         <v>1213.7</v>
       </c>
       <c r="P2">
-        <v>1039.008</v>
+        <v>1103.946</v>
       </c>
       <c r="Q2">
-        <v>0.0700480701422478</v>
+        <v>0.07003331475172229</v>
       </c>
       <c r="R2">
-        <v>0.0681646257628193</v>
+        <v>0.06688451442069759</v>
       </c>
       <c r="S2">
         <v>0.04811346</v>
       </c>
       <c r="T2">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1182,16 +1310,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0980447431148487</v>
+        <v>0.09801115439013371</v>
       </c>
       <c r="X2">
-        <v>0.09096913569772951</v>
+        <v>0.0932966175932604</v>
       </c>
       <c r="Y2">
         <v>1.20580033233565</v>
       </c>
       <c r="Z2">
-        <v>1.0424964424824</v>
+        <v>1.09691957490209</v>
       </c>
       <c r="AA2">
         <v>1213.7</v>
@@ -1224,7 +1352,7 @@
         <v>950.9</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.04329999999999999</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1412,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07248212058192244</v>
+        <v>0.07246496635070977</v>
       </c>
       <c r="C2">
-        <v>1985.226199299361</v>
+        <v>1985.287696500253</v>
       </c>
       <c r="D2">
-        <v>1786.926199299362</v>
+        <v>1786.987696500253</v>
       </c>
       <c r="E2">
         <v>-1213.7</v>
@@ -1463,19 +1591,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07248212058192244</v>
+        <v>0.07246496635070977</v>
       </c>
       <c r="T2">
         <v>0.6158190843120042</v>
       </c>
       <c r="U2">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.2494</v>
       </c>
       <c r="W2">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1494,13 +1622,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07234563557319112</v>
+        <v>0.07231801572463109</v>
       </c>
       <c r="C3">
-        <v>1972.767722319526</v>
+        <v>1973.544359034378</v>
       </c>
       <c r="D3">
-        <v>1796.113722319526</v>
+        <v>1796.890359034378</v>
       </c>
       <c r="E3">
         <v>-1192.054</v>
@@ -1527,37 +1655,37 @@
         <v>276.125</v>
       </c>
       <c r="M3">
-        <v>1.1190982</v>
+        <v>1.0887938</v>
       </c>
       <c r="N3">
-        <v>275.0059018</v>
+        <v>275.0362062</v>
       </c>
       <c r="O3">
-        <v>68.58647190892</v>
+        <v>68.59402982627999</v>
       </c>
       <c r="P3">
-        <v>206.41942989108</v>
+        <v>206.44217637372</v>
       </c>
       <c r="Q3">
-        <v>420.41942989108</v>
+        <v>420.44217637372</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07268441956887993</v>
+        <v>0.07266713527740515</v>
       </c>
       <c r="T3">
         <v>0.6204881126421515</v>
       </c>
       <c r="U3">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.2494</v>
       </c>
       <c r="W3">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1565,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>246.7388474040973</v>
+        <v>253.60633023443</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1576,13 +1704,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07220915056445981</v>
+        <v>0.07217106509855244</v>
       </c>
       <c r="C4">
-        <v>1960.404209330036</v>
+        <v>1961.911385139618</v>
       </c>
       <c r="D4">
-        <v>1805.396209330036</v>
+        <v>1806.903385139618</v>
       </c>
       <c r="E4">
         <v>-1170.408</v>
@@ -1609,37 +1737,37 @@
         <v>276.125</v>
       </c>
       <c r="M4">
-        <v>2.238196400000001</v>
+        <v>2.1775876</v>
       </c>
       <c r="N4">
-        <v>273.8868036</v>
+        <v>273.9474124</v>
       </c>
       <c r="O4">
-        <v>68.30736881784</v>
+        <v>68.32248465256001</v>
       </c>
       <c r="P4">
-        <v>205.57943478216</v>
+        <v>205.62492774744</v>
       </c>
       <c r="Q4">
-        <v>419.57943478216</v>
+        <v>419.62492774744</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07289084710659165</v>
+        <v>0.07287343010056371</v>
       </c>
       <c r="T4">
         <v>0.6252524272647509</v>
       </c>
       <c r="U4">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.2494</v>
       </c>
       <c r="W4">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1647,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>123.3694237020486</v>
+        <v>126.803165117215</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1658,13 +1786,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.0720726655557285</v>
+        <v>0.07202411447247375</v>
       </c>
       <c r="C5">
-        <v>1948.137140328538</v>
+        <v>1950.390630130775</v>
       </c>
       <c r="D5">
-        <v>1814.775140328538</v>
+        <v>1817.028630130775</v>
       </c>
       <c r="E5">
         <v>-1148.762</v>
@@ -1691,37 +1819,37 @@
         <v>276.125</v>
       </c>
       <c r="M5">
-        <v>3.3572946</v>
+        <v>3.2663814</v>
       </c>
       <c r="N5">
-        <v>272.7677054</v>
+        <v>272.8586186</v>
       </c>
       <c r="O5">
-        <v>68.02826572676001</v>
+        <v>68.05093947884001</v>
       </c>
       <c r="P5">
-        <v>204.73943967324</v>
+        <v>204.80767912116</v>
       </c>
       <c r="Q5">
-        <v>418.73943967324</v>
+        <v>418.80767912116</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07310153088219433</v>
+        <v>0.07308397842523068</v>
       </c>
       <c r="T5">
         <v>0.6301149751785378</v>
       </c>
       <c r="U5">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.2494</v>
       </c>
       <c r="W5">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1729,7 +1857,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>82.24628246803245</v>
+        <v>84.53544341147669</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1740,13 +1868,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07193618054699719</v>
+        <v>0.07187716384639509</v>
       </c>
       <c r="C6">
-        <v>1935.968026227291</v>
+        <v>1938.983991143092</v>
       </c>
       <c r="D6">
-        <v>1824.252026227291</v>
+        <v>1827.267991143093</v>
       </c>
       <c r="E6">
         <v>-1127.116</v>
@@ -1773,37 +1901,37 @@
         <v>276.125</v>
       </c>
       <c r="M6">
-        <v>4.476392800000001</v>
+        <v>4.355175200000001</v>
       </c>
       <c r="N6">
-        <v>271.6486072</v>
+        <v>271.7698248</v>
       </c>
       <c r="O6">
-        <v>67.74916263568001</v>
+        <v>67.77939430511999</v>
       </c>
       <c r="P6">
-        <v>203.89944456432</v>
+        <v>203.99043049488</v>
       </c>
       <c r="Q6">
-        <v>417.89944456432</v>
+        <v>417.99043049488</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07331660390312206</v>
+        <v>0.07329891317332822</v>
       </c>
       <c r="T6">
         <v>0.635078826173862</v>
       </c>
       <c r="U6">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.2494</v>
       </c>
       <c r="W6">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1811,7 +1939,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>61.68471185102432</v>
+        <v>63.4015825586075</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1822,13 +1950,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07179969553826587</v>
+        <v>0.07173021322031642</v>
       </c>
       <c r="C7">
-        <v>1923.898409664601</v>
+        <v>1927.693408317279</v>
       </c>
       <c r="D7">
-        <v>1833.828409664601</v>
+        <v>1837.623408317279</v>
       </c>
       <c r="E7">
         <v>-1105.47</v>
@@ -1855,37 +1983,37 @@
         <v>276.125</v>
       </c>
       <c r="M7">
-        <v>5.595491000000001</v>
+        <v>5.443969000000001</v>
       </c>
       <c r="N7">
-        <v>270.529509</v>
+        <v>270.681031</v>
       </c>
       <c r="O7">
-        <v>67.47005954460001</v>
+        <v>67.50784913140001</v>
       </c>
       <c r="P7">
-        <v>203.0594494554</v>
+        <v>203.1731818686</v>
       </c>
       <c r="Q7">
-        <v>417.0594494554</v>
+        <v>417.1731818686001</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07353620477712197</v>
+        <v>0.07351837286349097</v>
       </c>
       <c r="T7">
         <v>0.6401471792954037</v>
       </c>
       <c r="U7">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.2494</v>
       </c>
       <c r="W7">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1893,7 +2021,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>49.34776948081947</v>
+        <v>50.72126604688601</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1904,13 +2032,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07166321052953455</v>
+        <v>0.07158326259423775</v>
       </c>
       <c r="C8">
-        <v>1911.929865841939</v>
+        <v>1916.520866025048</v>
       </c>
       <c r="D8">
-        <v>1843.505865841939</v>
+        <v>1848.096866025048</v>
       </c>
       <c r="E8">
         <v>-1083.824</v>
@@ -1937,37 +2065,37 @@
         <v>276.125</v>
       </c>
       <c r="M8">
-        <v>6.7145892</v>
+        <v>6.5327628</v>
       </c>
       <c r="N8">
-        <v>269.4104108</v>
+        <v>269.5922372</v>
       </c>
       <c r="O8">
-        <v>67.19095645352</v>
+        <v>67.23630395768001</v>
       </c>
       <c r="P8">
-        <v>202.21945434648</v>
+        <v>202.35593324232</v>
       </c>
       <c r="Q8">
-        <v>416.21945434648</v>
+        <v>416.35593324232</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07376047801014314</v>
+        <v>0.07374250190876357</v>
       </c>
       <c r="T8">
         <v>0.6453233697174034</v>
       </c>
       <c r="U8">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.2494</v>
       </c>
       <c r="W8">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1975,7 +2103,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>41.12314123401622</v>
+        <v>42.26772170573835</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1986,13 +2114,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07152672552080325</v>
+        <v>0.07143631196815908</v>
       </c>
       <c r="C9">
-        <v>1900.064003387705</v>
+        <v>1905.468394136803</v>
       </c>
       <c r="D9">
-        <v>1853.286003387705</v>
+        <v>1858.690394136802</v>
       </c>
       <c r="E9">
         <v>-1062.178</v>
@@ -2019,37 +2147,37 @@
         <v>276.125</v>
       </c>
       <c r="M9">
-        <v>7.833687400000002</v>
+        <v>7.621556600000002</v>
       </c>
       <c r="N9">
-        <v>268.2913126</v>
+        <v>268.5034434</v>
       </c>
       <c r="O9">
-        <v>66.91185336244</v>
+        <v>66.96475878395999</v>
       </c>
       <c r="P9">
-        <v>201.37945923756</v>
+        <v>201.53868461604</v>
       </c>
       <c r="Q9">
-        <v>415.37945923756</v>
+        <v>415.53868461604</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07398957432344436</v>
+        <v>0.07397145093350439</v>
       </c>
       <c r="T9">
         <v>0.6506108760624573</v>
       </c>
       <c r="U9">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.2494</v>
       </c>
       <c r="W9">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2057,7 +2185,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>35.24840677201389</v>
+        <v>36.22947574777572</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2068,13 +2196,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07139024051207193</v>
+        <v>0.07128936134208042</v>
       </c>
       <c r="C10">
-        <v>1888.302465248651</v>
+        <v>1894.538069333179</v>
       </c>
       <c r="D10">
-        <v>1863.170465248651</v>
+        <v>1869.406069333179</v>
       </c>
       <c r="E10">
         <v>-1040.532</v>
@@ -2101,37 +2229,37 @@
         <v>276.125</v>
       </c>
       <c r="M10">
-        <v>8.952785600000002</v>
+        <v>8.710350400000001</v>
       </c>
       <c r="N10">
-        <v>267.1722144</v>
+        <v>267.4146496</v>
       </c>
       <c r="O10">
-        <v>66.63275027136</v>
+        <v>66.69321361024001</v>
       </c>
       <c r="P10">
-        <v>200.53946412864</v>
+        <v>200.72143598976</v>
       </c>
       <c r="Q10">
-        <v>414.53946412864</v>
+        <v>414.72143598976</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07422365099138253</v>
+        <v>0.07420537711095697</v>
       </c>
       <c r="T10">
         <v>0.6560133281976207</v>
       </c>
       <c r="U10">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.2494</v>
       </c>
       <c r="W10">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2139,7 +2267,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>30.84235592551216</v>
+        <v>31.70079127930376</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2150,13 +2278,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07125375550334061</v>
+        <v>0.07114241071600175</v>
       </c>
       <c r="C11">
-        <v>1876.646929609952</v>
+        <v>1883.732016462215</v>
       </c>
       <c r="D11">
-        <v>1873.160929609952</v>
+        <v>1880.246016462215</v>
       </c>
       <c r="E11">
         <v>-1018.886</v>
@@ -2183,37 +2311,37 @@
         <v>276.125</v>
       </c>
       <c r="M11">
-        <v>10.0718838</v>
+        <v>9.799144200000001</v>
       </c>
       <c r="N11">
-        <v>266.0531162</v>
+        <v>266.3258558</v>
       </c>
       <c r="O11">
-        <v>66.35364718027999</v>
+        <v>66.42166843652001</v>
       </c>
       <c r="P11">
-        <v>199.69946901972</v>
+        <v>199.90418736348</v>
       </c>
       <c r="Q11">
-        <v>413.69946901972</v>
+        <v>413.90418736348</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.0744628722014732</v>
+        <v>0.07444444452307884</v>
       </c>
       <c r="T11">
         <v>0.6615345155445461</v>
       </c>
       <c r="U11">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.2494</v>
       </c>
       <c r="W11">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2221,7 +2349,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>27.41542748934414</v>
+        <v>28.17848113715889</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2232,13 +2360,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07111727049460929</v>
+        <v>0.07099546008992308</v>
       </c>
       <c r="C12">
-        <v>1865.099110845066</v>
+        <v>1873.052409944013</v>
       </c>
       <c r="D12">
-        <v>1883.259110845066</v>
+        <v>1891.212409944013</v>
       </c>
       <c r="E12">
         <v>-997.24</v>
@@ -2265,37 +2393,37 @@
         <v>276.125</v>
       </c>
       <c r="M12">
-        <v>11.190982</v>
+        <v>10.887938</v>
       </c>
       <c r="N12">
-        <v>264.934018</v>
+        <v>265.237062</v>
       </c>
       <c r="O12">
-        <v>66.0745440892</v>
+        <v>66.15012326279999</v>
       </c>
       <c r="P12">
-        <v>198.8594739108</v>
+        <v>199.0869387372</v>
       </c>
       <c r="Q12">
-        <v>412.8594739108</v>
+        <v>413.0869387372001</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07470740943845477</v>
+        <v>0.07468882454435896</v>
       </c>
       <c r="T12">
         <v>0.6671783959436253</v>
       </c>
       <c r="U12">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.2494</v>
       </c>
       <c r="W12">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +2431,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.67388474040973</v>
+        <v>25.360633023443</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2314,13 +2442,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07098078548587798</v>
+        <v>0.07084850946384441</v>
       </c>
       <c r="C13">
-        <v>1853.660760496471</v>
+        <v>1862.501475224851</v>
       </c>
       <c r="D13">
-        <v>1893.466760496471</v>
+        <v>1902.30747522485</v>
       </c>
       <c r="E13">
         <v>-975.5940000000001</v>
@@ -2347,37 +2475,37 @@
         <v>276.125</v>
       </c>
       <c r="M13">
-        <v>12.3100802</v>
+        <v>11.9767318</v>
       </c>
       <c r="N13">
-        <v>263.8149198</v>
+        <v>264.1482682</v>
       </c>
       <c r="O13">
-        <v>65.79544099812</v>
+        <v>65.87857808908001</v>
       </c>
       <c r="P13">
-        <v>198.01947880188</v>
+        <v>198.26969011092</v>
       </c>
       <c r="Q13">
-        <v>412.01947880188</v>
+        <v>412.26969011092</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07495744189424493</v>
+        <v>0.07493869625151056</v>
       </c>
       <c r="T13">
         <v>0.6729491051157176</v>
       </c>
       <c r="U13">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.2494</v>
       </c>
       <c r="W13">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2513,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>22.43080430946339</v>
+        <v>23.05512093040273</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2396,13 +2524,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07084430047714665</v>
+        <v>0.07070155883776574</v>
       </c>
       <c r="C14">
-        <v>1842.333668288472</v>
+        <v>1852.08149028277</v>
       </c>
       <c r="D14">
-        <v>1903.785668288472</v>
+        <v>1913.533490282769</v>
       </c>
       <c r="E14">
         <v>-953.9480000000001</v>
@@ -2429,37 +2557,37 @@
         <v>276.125</v>
       </c>
       <c r="M14">
-        <v>13.4291784</v>
+        <v>13.0655256</v>
       </c>
       <c r="N14">
-        <v>262.6958216</v>
+        <v>263.0594744</v>
       </c>
       <c r="O14">
-        <v>65.51633790704</v>
+        <v>65.60703291536001</v>
       </c>
       <c r="P14">
-        <v>197.17948369296</v>
+        <v>197.45244148464</v>
       </c>
       <c r="Q14">
-        <v>411.17948369296</v>
+        <v>411.45244148464</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07521315690584848</v>
+        <v>0.07519424686109742</v>
       </c>
       <c r="T14">
         <v>0.6788509667689937</v>
       </c>
       <c r="U14">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.2494</v>
       </c>
       <c r="W14">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2467,7 +2595,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.56157061700811</v>
+        <v>21.13386085286917</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2478,13 +2606,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07070781546841536</v>
+        <v>0.07055460821168705</v>
       </c>
       <c r="C15">
-        <v>1831.119663173305</v>
+        <v>1841.794787186804</v>
       </c>
       <c r="D15">
-        <v>1914.217663173305</v>
+        <v>1924.892787186804</v>
       </c>
       <c r="E15">
         <v>-932.302</v>
@@ -2511,37 +2639,37 @@
         <v>276.125</v>
       </c>
       <c r="M15">
-        <v>14.5482766</v>
+        <v>14.1543194</v>
       </c>
       <c r="N15">
-        <v>261.5767234</v>
+        <v>261.9706806</v>
       </c>
       <c r="O15">
-        <v>65.23723481595999</v>
+        <v>65.33548774163999</v>
       </c>
       <c r="P15">
-        <v>196.33948858404</v>
+        <v>196.63519285836</v>
       </c>
       <c r="Q15">
-        <v>410.3394885840401</v>
+        <v>410.63519285836</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07547475042346592</v>
+        <v>0.07545567219734145</v>
       </c>
       <c r="T15">
         <v>0.684888503402805</v>
       </c>
       <c r="U15">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.2494</v>
       </c>
       <c r="W15">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2677,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.97991133877671</v>
+        <v>19.50817924880231</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2560,13 +2688,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07057133045968404</v>
+        <v>0.07040765758560838</v>
       </c>
       <c r="C16">
-        <v>1820.020614411836</v>
+        <v>1831.643753712055</v>
       </c>
       <c r="D16">
-        <v>1924.764614411836</v>
+        <v>1936.387753712055</v>
       </c>
       <c r="E16">
         <v>-910.6559999999999</v>
@@ -2593,37 +2721,37 @@
         <v>276.125</v>
       </c>
       <c r="M16">
-        <v>15.6673748</v>
+        <v>15.2431132</v>
       </c>
       <c r="N16">
-        <v>260.4576252</v>
+        <v>260.8818868</v>
       </c>
       <c r="O16">
-        <v>64.95813172488</v>
+        <v>65.06394256792001</v>
       </c>
       <c r="P16">
-        <v>195.49949347512</v>
+        <v>195.81794423208</v>
       </c>
       <c r="Q16">
-        <v>409.4994934751201</v>
+        <v>409.81794423208</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07574242751126051</v>
+        <v>0.07572317719256789</v>
       </c>
       <c r="T16">
         <v>0.6910664478653096</v>
       </c>
       <c r="U16">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.2494</v>
       </c>
       <c r="W16">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2759,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.62420338600695</v>
+        <v>18.11473787388786</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2642,13 +2770,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07043484545095273</v>
+        <v>0.07026070695952971</v>
       </c>
       <c r="C17">
-        <v>1809.038432690167</v>
+        <v>1821.630835013011</v>
       </c>
       <c r="D17">
-        <v>1935.428432690167</v>
+        <v>1948.020835013011</v>
       </c>
       <c r="E17">
         <v>-889.01</v>
@@ -2675,37 +2803,37 @@
         <v>276.125</v>
       </c>
       <c r="M17">
-        <v>16.786473</v>
+        <v>16.331907</v>
       </c>
       <c r="N17">
-        <v>259.338527</v>
+        <v>259.793093</v>
       </c>
       <c r="O17">
-        <v>64.6790286338</v>
+        <v>64.79239739420001</v>
       </c>
       <c r="P17">
-        <v>194.6594983662</v>
+        <v>195.0006956058</v>
       </c>
       <c r="Q17">
-        <v>408.6594983662001</v>
+        <v>409.0006956058</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07601640288347379</v>
+        <v>0.07599697642297615</v>
       </c>
       <c r="T17">
         <v>0.6973897557269318</v>
       </c>
       <c r="U17">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V17">
         <v>0.2494</v>
       </c>
       <c r="W17">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2841,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.44925649360648</v>
+        <v>16.90708868229534</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2724,13 +2852,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07029836044222142</v>
+        <v>0.07011375633345104</v>
       </c>
       <c r="C18">
-        <v>1798.175071273575</v>
+        <v>1811.758535357519</v>
       </c>
       <c r="D18">
-        <v>1946.211071273575</v>
+        <v>1959.794535357519</v>
       </c>
       <c r="E18">
         <v>-867.364</v>
@@ -2757,37 +2885,37 @@
         <v>276.125</v>
       </c>
       <c r="M18">
-        <v>17.9055712</v>
+        <v>17.4207008</v>
       </c>
       <c r="N18">
-        <v>258.2194288</v>
+        <v>258.7042992</v>
       </c>
       <c r="O18">
-        <v>64.39992554272</v>
+        <v>64.52085222047999</v>
       </c>
       <c r="P18">
-        <v>193.81950325728</v>
+        <v>194.18344697952</v>
       </c>
       <c r="Q18">
-        <v>407.8195032572801</v>
+        <v>408.18344697952</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07629690147883501</v>
+        <v>0.07627729468267982</v>
       </c>
       <c r="T18">
         <v>0.7038636185376403</v>
       </c>
       <c r="U18">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V18">
         <v>0.2494</v>
       </c>
       <c r="W18">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +2923,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.42117796275608</v>
+        <v>15.85039563965188</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2806,13 +2934,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07016187543349009</v>
+        <v>0.06996680570737238</v>
       </c>
       <c r="C19">
-        <v>1787.432527199248</v>
+        <v>1802.029419924042</v>
       </c>
       <c r="D19">
-        <v>1957.114527199248</v>
+        <v>1971.711419924042</v>
       </c>
       <c r="E19">
         <v>-845.7180000000001</v>
@@ -2839,37 +2967,37 @@
         <v>276.125</v>
       </c>
       <c r="M19">
-        <v>19.0246694</v>
+        <v>18.5094946</v>
       </c>
       <c r="N19">
-        <v>257.1003306</v>
+        <v>257.6155054</v>
       </c>
       <c r="O19">
-        <v>64.12082245164001</v>
+        <v>64.24930704676001</v>
       </c>
       <c r="P19">
-        <v>192.97950814836</v>
+        <v>193.36619835324</v>
       </c>
       <c r="Q19">
-        <v>406.97950814836</v>
+        <v>407.3661983532401</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07658415907649409</v>
+        <v>0.07656436759924383</v>
       </c>
       <c r="T19">
         <v>0.7104934780425829</v>
       </c>
       <c r="U19">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V19">
         <v>0.2494</v>
       </c>
       <c r="W19">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +3005,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.51404984729984</v>
+        <v>14.91801942555471</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2888,13 +3016,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07002539042475879</v>
+        <v>0.06981985508129372</v>
       </c>
       <c r="C20">
-        <v>1776.812842509318</v>
+        <v>1792.44611666487</v>
       </c>
       <c r="D20">
-        <v>1968.140842509318</v>
+        <v>1983.774116664869</v>
       </c>
       <c r="E20">
         <v>-824.0720000000001</v>
@@ -2921,37 +3049,37 @@
         <v>276.125</v>
       </c>
       <c r="M20">
-        <v>20.1437676</v>
+        <v>19.5982884</v>
       </c>
       <c r="N20">
-        <v>255.9812324</v>
+        <v>256.5267116</v>
       </c>
       <c r="O20">
-        <v>63.84171936056001</v>
+        <v>63.97776187304</v>
       </c>
       <c r="P20">
-        <v>192.13951303944</v>
+        <v>192.54894972696</v>
       </c>
       <c r="Q20">
-        <v>406.13951303944</v>
+        <v>406.54894972696</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07687842295702291</v>
+        <v>0.07685844229426063</v>
       </c>
       <c r="T20">
         <v>0.7172850414378898</v>
       </c>
       <c r="U20">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V20">
         <v>0.2494</v>
       </c>
       <c r="W20">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +3087,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>13.70771374467207</v>
+        <v>14.08924056857945</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2970,13 +3098,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.06988890541602746</v>
+        <v>0.06967290445521504</v>
       </c>
       <c r="C21">
-        <v>1766.318105525846</v>
+        <v>1783.011318238162</v>
       </c>
       <c r="D21">
-        <v>1979.292105525845</v>
+        <v>1995.985318238162</v>
       </c>
       <c r="E21">
         <v>-802.426</v>
@@ -3003,37 +3131,37 @@
         <v>276.125</v>
       </c>
       <c r="M21">
-        <v>21.2628658</v>
+        <v>20.6870822</v>
       </c>
       <c r="N21">
-        <v>254.8621342</v>
+        <v>255.4379178</v>
       </c>
       <c r="O21">
-        <v>63.56261626948</v>
+        <v>63.70621669932</v>
       </c>
       <c r="P21">
-        <v>191.29951793052</v>
+        <v>191.73170110068</v>
       </c>
       <c r="Q21">
-        <v>405.29951793052</v>
+        <v>405.73170110068</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07717995261237959</v>
+        <v>0.07715977809285807</v>
       </c>
       <c r="T21">
         <v>0.7242442977565376</v>
       </c>
       <c r="U21">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V21">
         <v>0.2494</v>
       </c>
       <c r="W21">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3169,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.98625512653144</v>
+        <v>13.34770159128579</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3052,13 +3180,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.06991755240729615</v>
+        <v>0.06975113382913638</v>
       </c>
       <c r="C22">
-        <v>1742.321089025181</v>
+        <v>1754.846015940581</v>
       </c>
       <c r="D22">
-        <v>1976.941089025181</v>
+        <v>1989.466015940581</v>
       </c>
       <c r="E22">
         <v>-780.78</v>
@@ -3085,37 +3213,37 @@
         <v>276.125</v>
       </c>
       <c r="M22">
-        <v>22.858176</v>
+        <v>22.425256</v>
       </c>
       <c r="N22">
-        <v>253.266824</v>
+        <v>253.699744</v>
       </c>
       <c r="O22">
-        <v>63.1647459056</v>
+        <v>63.27271615360001</v>
       </c>
       <c r="P22">
-        <v>190.1020780944</v>
+        <v>190.4270278464</v>
       </c>
       <c r="Q22">
-        <v>404.1020780944</v>
+        <v>404.4270278464001</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07748902050912018</v>
+        <v>0.07746864728642047</v>
       </c>
       <c r="T22">
         <v>0.7313775354831518</v>
       </c>
       <c r="U22">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V22">
         <v>0.2494</v>
       </c>
       <c r="W22">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3251,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.07992273749226</v>
+        <v>12.31312587914269</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3134,13 +3262,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.06978932399856484</v>
+        <v>0.06961544220305771</v>
       </c>
       <c r="C23">
-        <v>1731.242290085803</v>
+        <v>1744.535261216715</v>
       </c>
       <c r="D23">
-        <v>1987.508290085803</v>
+        <v>2000.801261216714</v>
       </c>
       <c r="E23">
         <v>-759.134</v>
@@ -3167,37 +3295,37 @@
         <v>276.125</v>
       </c>
       <c r="M23">
-        <v>24.0010848</v>
+        <v>23.5465188</v>
       </c>
       <c r="N23">
-        <v>252.1239152</v>
+        <v>252.5784812</v>
       </c>
       <c r="O23">
-        <v>62.87970445088001</v>
+        <v>62.99307321128001</v>
       </c>
       <c r="P23">
-        <v>189.24421074912</v>
+        <v>189.58540798872</v>
       </c>
       <c r="Q23">
-        <v>403.24421074912</v>
+        <v>403.58540798872</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07780591290957575</v>
+        <v>0.0777853359532376</v>
       </c>
       <c r="T23">
         <v>0.7386913615066422</v>
       </c>
       <c r="U23">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V23">
         <v>0.2494</v>
       </c>
       <c r="W23">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3333,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.5046883214212</v>
+        <v>11.72678655156447</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3216,13 +3344,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.06966109558983352</v>
+        <v>0.06947975057697903</v>
       </c>
       <c r="C24">
-        <v>1720.277066432326</v>
+        <v>1734.35441477533</v>
       </c>
       <c r="D24">
-        <v>1998.189066432326</v>
+        <v>2012.26641477533</v>
       </c>
       <c r="E24">
         <v>-737.4880000000001</v>
@@ -3249,37 +3377,37 @@
         <v>276.125</v>
       </c>
       <c r="M24">
-        <v>25.1439936</v>
+        <v>24.6677816</v>
       </c>
       <c r="N24">
-        <v>250.9810064</v>
+        <v>251.4572184</v>
       </c>
       <c r="O24">
-        <v>62.59466299616</v>
+        <v>62.71343026896</v>
       </c>
       <c r="P24">
-        <v>188.38634340384</v>
+        <v>188.74378813104</v>
       </c>
       <c r="Q24">
-        <v>402.38634340384</v>
+        <v>402.74378813104</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07813093075619683</v>
+        <v>0.07811014484228081</v>
       </c>
       <c r="T24">
         <v>0.7461927215307348</v>
       </c>
       <c r="U24">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V24">
         <v>0.2494</v>
       </c>
       <c r="W24">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3415,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.98174794317479</v>
+        <v>11.19375079922063</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3298,13 +3426,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.06953286718110221</v>
+        <v>0.06934405895090037</v>
       </c>
       <c r="C25">
-        <v>1709.427259002642</v>
+        <v>1724.305722720139</v>
       </c>
       <c r="D25">
-        <v>2008.985259002642</v>
+        <v>2023.863722720138</v>
       </c>
       <c r="E25">
         <v>-715.8420000000001</v>
@@ -3331,37 +3459,37 @@
         <v>276.125</v>
       </c>
       <c r="M25">
-        <v>26.2869024</v>
+        <v>25.7890444</v>
       </c>
       <c r="N25">
-        <v>249.8380976</v>
+        <v>250.3359556</v>
       </c>
       <c r="O25">
-        <v>62.30962154144</v>
+        <v>62.43378732664</v>
       </c>
       <c r="P25">
-        <v>187.52847605856</v>
+        <v>187.90216827336</v>
       </c>
       <c r="Q25">
-        <v>401.52847605856</v>
+        <v>401.9021682733601</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07846439062480806</v>
+        <v>0.07844339032584463</v>
       </c>
       <c r="T25">
         <v>0.7538889220749337</v>
       </c>
       <c r="U25">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V25">
         <v>0.2494</v>
       </c>
       <c r="W25">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3497,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.50428064129762</v>
+        <v>10.70706598186321</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3380,13 +3508,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.06940463877237089</v>
+        <v>0.06920836732482169</v>
       </c>
       <c r="C26">
-        <v>1698.694748737046</v>
+        <v>1714.391483234951</v>
       </c>
       <c r="D26">
-        <v>2019.898748737046</v>
+        <v>2035.59548323495</v>
       </c>
       <c r="E26">
         <v>-694.1960000000001</v>
@@ -3413,37 +3541,37 @@
         <v>276.125</v>
       </c>
       <c r="M26">
-        <v>27.4298112</v>
+        <v>26.9103072</v>
       </c>
       <c r="N26">
-        <v>248.6951888</v>
+        <v>249.2146928</v>
       </c>
       <c r="O26">
-        <v>62.02458008672001</v>
+        <v>62.15414438432</v>
       </c>
       <c r="P26">
-        <v>186.67060871328</v>
+        <v>187.06054841568</v>
       </c>
       <c r="Q26">
-        <v>400.67060871328</v>
+        <v>401.06054841568</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.0788066257531196</v>
+        <v>0.07878540542739695</v>
       </c>
       <c r="T26">
         <v>0.7617876542124011</v>
       </c>
       <c r="U26">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V26">
         <v>0.2494</v>
       </c>
       <c r="W26">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3579,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.06660228124355</v>
+        <v>10.26093823261891</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3462,13 +3590,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.06968924036363959</v>
+        <v>0.06907267569874302</v>
       </c>
       <c r="C27">
-        <v>1652.984927981691</v>
+        <v>1704.614048101923</v>
       </c>
       <c r="D27">
-        <v>1995.834927981691</v>
+        <v>2047.464048101923</v>
       </c>
       <c r="E27">
         <v>-672.5500000000001</v>
@@ -3495,45 +3623,45 @@
         <v>276.125</v>
       </c>
       <c r="M27">
-        <v>29.76325</v>
+        <v>28.03157</v>
       </c>
       <c r="N27">
-        <v>246.36175</v>
+        <v>248.09343</v>
       </c>
       <c r="O27">
-        <v>61.44262045</v>
+        <v>61.874501442</v>
       </c>
       <c r="P27">
-        <v>184.91912955</v>
+        <v>186.218928558</v>
       </c>
       <c r="Q27">
-        <v>398.91912955</v>
+        <v>400.218928558</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07915798715151945</v>
+        <v>0.07913654093165737</v>
       </c>
       <c r="T27">
         <v>0.7698970192068676</v>
       </c>
       <c r="U27">
-        <v>0.05500000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V27">
         <v>0.2494</v>
       </c>
       <c r="W27">
-        <v>0.041283</v>
+        <v>0.03888108</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>9.277380662394059</v>
+        <v>9.850500703314156</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3544,13 +3672,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.06957752515490827</v>
+        <v>0.06926874927266435</v>
       </c>
       <c r="C28">
-        <v>1640.716065178272</v>
+        <v>1665.862168759031</v>
       </c>
       <c r="D28">
-        <v>2005.212065178272</v>
+        <v>2030.358168759031</v>
       </c>
       <c r="E28">
         <v>-650.904</v>
@@ -3577,37 +3705,37 @@
         <v>276.125</v>
       </c>
       <c r="M28">
-        <v>30.95378000000001</v>
+        <v>30.10958600000001</v>
       </c>
       <c r="N28">
-        <v>245.17122</v>
+        <v>246.015414</v>
       </c>
       <c r="O28">
-        <v>61.145702268</v>
+        <v>61.3562442516</v>
       </c>
       <c r="P28">
-        <v>184.025517732</v>
+        <v>184.6591697484</v>
       </c>
       <c r="Q28">
-        <v>398.025517732</v>
+        <v>398.6591697484</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.07951884480393009</v>
+        <v>0.07949716658468156</v>
       </c>
       <c r="T28">
         <v>0.7782255562282115</v>
       </c>
       <c r="U28">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V28">
         <v>0.2494</v>
       </c>
       <c r="W28">
-        <v>0.041283</v>
+        <v>0.0401571</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3743,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.920558329225056</v>
+        <v>9.170667441259402</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3626,13 +3754,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.06946580994617695</v>
+        <v>0.06914581784658569</v>
       </c>
       <c r="C29">
-        <v>1628.535732523756</v>
+        <v>1654.907369503258</v>
       </c>
       <c r="D29">
-        <v>2014.677732523757</v>
+        <v>2041.049369503258</v>
       </c>
       <c r="E29">
         <v>-629.258</v>
@@ -3659,37 +3787,37 @@
         <v>276.125</v>
       </c>
       <c r="M29">
-        <v>32.14431</v>
+        <v>31.267647</v>
       </c>
       <c r="N29">
-        <v>243.98069</v>
+        <v>244.857353</v>
       </c>
       <c r="O29">
-        <v>60.84878408599999</v>
+        <v>61.0674238382</v>
       </c>
       <c r="P29">
-        <v>183.131905914</v>
+        <v>183.7899291618</v>
       </c>
       <c r="Q29">
-        <v>397.131905914</v>
+        <v>397.7899291618</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.07988958896736569</v>
+        <v>0.07986767239258313</v>
       </c>
       <c r="T29">
         <v>0.7867822723460307</v>
       </c>
       <c r="U29">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V29">
         <v>0.2494</v>
       </c>
       <c r="W29">
-        <v>0.041283</v>
+        <v>0.0401571</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3825,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.590167279994498</v>
+        <v>8.831013091583129</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3708,13 +3836,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.06935409473744564</v>
+        <v>0.06902288642050701</v>
       </c>
       <c r="C30">
-        <v>1616.445189692628</v>
+        <v>1644.065758981237</v>
       </c>
       <c r="D30">
-        <v>2024.233189692628</v>
+        <v>2051.853758981237</v>
       </c>
       <c r="E30">
         <v>-607.612</v>
@@ -3741,37 +3869,37 @@
         <v>276.125</v>
       </c>
       <c r="M30">
-        <v>33.33484000000001</v>
+        <v>32.42570800000001</v>
       </c>
       <c r="N30">
-        <v>242.79016</v>
+        <v>243.699292</v>
       </c>
       <c r="O30">
-        <v>60.551865904</v>
+        <v>60.7786034248</v>
       </c>
       <c r="P30">
-        <v>182.238294096</v>
+        <v>182.9206885752</v>
       </c>
       <c r="Q30">
-        <v>396.238294096</v>
+        <v>396.9206885752</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.08027063157978562</v>
+        <v>0.08024847002848196</v>
       </c>
       <c r="T30">
         <v>0.7955766750226783</v>
       </c>
       <c r="U30">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V30">
         <v>0.2494</v>
       </c>
       <c r="W30">
-        <v>0.041283</v>
+        <v>0.0401571</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3907,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.283375591423265</v>
+        <v>8.515619766883731</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3790,13 +3918,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.06924237952871432</v>
+        <v>0.06889995499442833</v>
       </c>
       <c r="C31">
-        <v>1604.44572037141</v>
+        <v>1633.339144268235</v>
       </c>
       <c r="D31">
-        <v>2033.87972037141</v>
+        <v>2062.773144268234</v>
       </c>
       <c r="E31">
         <v>-585.9660000000001</v>
@@ -3823,37 +3951,37 @@
         <v>276.125</v>
       </c>
       <c r="M31">
-        <v>34.52537</v>
+        <v>33.583769</v>
       </c>
       <c r="N31">
-        <v>241.59963</v>
+        <v>242.541231</v>
       </c>
       <c r="O31">
-        <v>60.254947722</v>
+        <v>60.48978301140001</v>
       </c>
       <c r="P31">
-        <v>181.344682278</v>
+        <v>182.0514479886</v>
       </c>
       <c r="Q31">
-        <v>395.3446822780001</v>
+        <v>396.0514479886</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08066240778692157</v>
+        <v>0.08063999435834976</v>
       </c>
       <c r="T31">
         <v>0.8046188073521888</v>
       </c>
       <c r="U31">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V31">
         <v>0.2494</v>
       </c>
       <c r="W31">
-        <v>0.041283</v>
+        <v>0.0401571</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3989,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.997741950339706</v>
+        <v>8.221977705956709</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3872,13 +4000,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.06913066431998301</v>
+        <v>0.06877702356834967</v>
       </c>
       <c r="C32">
-        <v>1592.53863283354</v>
+        <v>1622.729371112297</v>
       </c>
       <c r="D32">
-        <v>2043.61863283354</v>
+        <v>2073.809371112297</v>
       </c>
       <c r="E32">
         <v>-564.3200000000001</v>
@@ -3905,37 +4033,37 @@
         <v>276.125</v>
       </c>
       <c r="M32">
-        <v>35.7159</v>
+        <v>34.74183</v>
       </c>
       <c r="N32">
-        <v>240.4091</v>
+        <v>241.38317</v>
       </c>
       <c r="O32">
-        <v>59.95802954</v>
+        <v>60.200962598</v>
       </c>
       <c r="P32">
-        <v>180.45107046</v>
+        <v>181.182207402</v>
       </c>
       <c r="Q32">
-        <v>394.45107046</v>
+        <v>395.182207402</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08106537759997573</v>
+        <v>0.08104270509764239</v>
       </c>
       <c r="T32">
         <v>0.8139192863196858</v>
       </c>
       <c r="U32">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V32">
         <v>0.2494</v>
       </c>
       <c r="W32">
-        <v>0.041283</v>
+        <v>0.0401571</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +4071,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.731150551995049</v>
+        <v>7.947911782424818</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3954,13 +4082,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.06936797811125169</v>
+        <v>0.068654092142271</v>
       </c>
       <c r="C33">
-        <v>1550.314758763236</v>
+        <v>1612.238324974349</v>
       </c>
       <c r="D33">
-        <v>2023.040758763236</v>
+        <v>2084.964324974349</v>
       </c>
       <c r="E33">
         <v>-542.6740000000001</v>
@@ -3987,45 +4115,45 @@
         <v>276.125</v>
       </c>
       <c r="M33">
-        <v>37.912969</v>
+        <v>35.899891</v>
       </c>
       <c r="N33">
-        <v>238.212031</v>
+        <v>240.225109</v>
       </c>
       <c r="O33">
-        <v>59.4100805314</v>
+        <v>59.9121421846</v>
       </c>
       <c r="P33">
-        <v>178.8019504686</v>
+        <v>180.3129668154</v>
       </c>
       <c r="Q33">
-        <v>392.8019504686</v>
+        <v>394.3129668154</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08148002769746622</v>
+        <v>0.08145708861198696</v>
       </c>
       <c r="T33">
         <v>0.8234893443876897</v>
       </c>
       <c r="U33">
-        <v>0.05650000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V33">
         <v>0.2494</v>
       </c>
       <c r="W33">
-        <v>0.0424089</v>
+        <v>0.0401571</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>7.283127839447235</v>
+        <v>7.691527531378855</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4036,13 +4164,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.06926752190252036</v>
+        <v>0.06872331431619232</v>
       </c>
       <c r="C34">
-        <v>1537.328684833762</v>
+        <v>1584.296299838875</v>
       </c>
       <c r="D34">
-        <v>2031.700684833762</v>
+        <v>2078.668299838875</v>
       </c>
       <c r="E34">
         <v>-521.028</v>
@@ -4069,37 +4197,37 @@
         <v>276.125</v>
       </c>
       <c r="M34">
-        <v>39.13596800000001</v>
+        <v>37.6120896</v>
       </c>
       <c r="N34">
-        <v>236.989032</v>
+        <v>238.5129104</v>
       </c>
       <c r="O34">
-        <v>59.1050645808</v>
+        <v>59.48511985376</v>
       </c>
       <c r="P34">
-        <v>177.8839674192</v>
+        <v>179.02779054624</v>
       </c>
       <c r="Q34">
-        <v>391.8839674192001</v>
+        <v>393.02779054624</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08190687338605937</v>
+        <v>0.08188365987675342</v>
       </c>
       <c r="T34">
         <v>0.8333408747518114</v>
       </c>
       <c r="U34">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V34">
         <v>0.2494</v>
       </c>
       <c r="W34">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.055530094464508</v>
+        <v>7.341389508973199</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4118,13 +4246,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.06916706569378907</v>
+        <v>0.06860638769011365</v>
       </c>
       <c r="C35">
-        <v>1524.417069833134</v>
+        <v>1573.307475115352</v>
       </c>
       <c r="D35">
-        <v>2040.435069833134</v>
+        <v>2089.325475115352</v>
       </c>
       <c r="E35">
         <v>-499.3820000000001</v>
@@ -4151,37 +4279,37 @@
         <v>276.125</v>
       </c>
       <c r="M35">
-        <v>40.35896700000001</v>
+        <v>38.7874674</v>
       </c>
       <c r="N35">
-        <v>235.766033</v>
+        <v>237.3375326</v>
       </c>
       <c r="O35">
-        <v>58.8000486302</v>
+        <v>59.19198063044</v>
       </c>
       <c r="P35">
-        <v>176.9659843698</v>
+        <v>178.14555196956</v>
       </c>
       <c r="Q35">
-        <v>390.9659843698</v>
+        <v>392.1455519695601</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08234646073699861</v>
+        <v>0.08232296461210994</v>
       </c>
       <c r="T35">
         <v>0.8434864806491905</v>
       </c>
       <c r="U35">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V35">
         <v>0.2494</v>
       </c>
       <c r="W35">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4317,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.841726152208008</v>
+        <v>7.118923160216435</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4200,13 +4328,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.06906660948505774</v>
+        <v>0.06848946106403499</v>
       </c>
       <c r="C36">
-        <v>1511.580878215809</v>
+        <v>1562.428490598707</v>
       </c>
       <c r="D36">
-        <v>2049.244878215809</v>
+        <v>2100.092490598707</v>
       </c>
       <c r="E36">
         <v>-477.736</v>
@@ -4233,37 +4361,37 @@
         <v>276.125</v>
       </c>
       <c r="M36">
-        <v>41.58196600000001</v>
+        <v>39.96284520000001</v>
       </c>
       <c r="N36">
-        <v>234.543034</v>
+        <v>236.1621548</v>
       </c>
       <c r="O36">
-        <v>58.49503267959999</v>
+        <v>58.89884140712</v>
       </c>
       <c r="P36">
-        <v>176.0480013204</v>
+        <v>177.26331339288</v>
       </c>
       <c r="Q36">
-        <v>390.0480013204</v>
+        <v>391.26331339288</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.08279936891675416</v>
+        <v>0.08277558161217423</v>
       </c>
       <c r="T36">
         <v>0.8539395291495204</v>
       </c>
       <c r="U36">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V36">
         <v>0.2494</v>
       </c>
       <c r="W36">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4399,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.640498912437184</v>
+        <v>6.909543067268892</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4282,13 +4410,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.06896615327632644</v>
+        <v>0.06837253443795632</v>
       </c>
       <c r="C37">
-        <v>1498.821091165024</v>
+        <v>1551.661053218859</v>
       </c>
       <c r="D37">
-        <v>2058.131091165024</v>
+        <v>2110.971053218859</v>
       </c>
       <c r="E37">
         <v>-456.09</v>
@@ -4315,37 +4443,37 @@
         <v>276.125</v>
       </c>
       <c r="M37">
-        <v>42.80496500000001</v>
+        <v>41.138223</v>
       </c>
       <c r="N37">
-        <v>233.320035</v>
+        <v>234.986777</v>
       </c>
       <c r="O37">
-        <v>58.190016729</v>
+        <v>58.6057021838</v>
       </c>
       <c r="P37">
-        <v>175.130018271</v>
+        <v>176.3810748162</v>
       </c>
       <c r="Q37">
-        <v>389.130018271</v>
+        <v>390.3810748162</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.0832662127328099</v>
+        <v>0.08324212528916357</v>
       </c>
       <c r="T37">
         <v>0.864714209911399</v>
       </c>
       <c r="U37">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V37">
         <v>0.2494</v>
       </c>
       <c r="W37">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4481,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.450770372081835</v>
+        <v>6.712127551061211</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4364,13 +4492,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.06886569706759513</v>
+        <v>0.06825560781187764</v>
       </c>
       <c r="C38">
-        <v>1486.138706957106</v>
+        <v>1541.00690545775</v>
       </c>
       <c r="D38">
-        <v>2067.094706957106</v>
+        <v>2121.96290545775</v>
       </c>
       <c r="E38">
         <v>-434.4440000000001</v>
@@ -4397,37 +4525,37 @@
         <v>276.125</v>
       </c>
       <c r="M38">
-        <v>44.027964</v>
+        <v>42.3136008</v>
       </c>
       <c r="N38">
-        <v>232.097036</v>
+        <v>233.8113992</v>
       </c>
       <c r="O38">
-        <v>57.88500077840001</v>
+        <v>58.31256296048</v>
       </c>
       <c r="P38">
-        <v>174.2120352216</v>
+        <v>175.49883623952</v>
       </c>
       <c r="Q38">
-        <v>388.2120352216</v>
+        <v>389.49883623952</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08374764541811738</v>
+        <v>0.08372324845605883</v>
       </c>
       <c r="T38">
         <v>0.8758255994470863</v>
       </c>
       <c r="U38">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V38">
         <v>0.2494</v>
       </c>
       <c r="W38">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4563,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.271582306190674</v>
+        <v>6.525679563531733</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4446,13 +4574,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.0691540516588638</v>
+        <v>0.06813868118579898</v>
       </c>
       <c r="C39">
-        <v>1438.970101370506</v>
+        <v>1530.467826279781</v>
       </c>
       <c r="D39">
-        <v>2041.572101370506</v>
+        <v>2133.069826279781</v>
       </c>
       <c r="E39">
         <v>-412.7980000000001</v>
@@ -4479,45 +4607,45 @@
         <v>276.125</v>
       </c>
       <c r="M39">
-        <v>46.3722258</v>
+        <v>43.4889786</v>
       </c>
       <c r="N39">
-        <v>229.7527742</v>
+        <v>232.6360214</v>
       </c>
       <c r="O39">
-        <v>57.30034188548</v>
+        <v>58.01942373716</v>
       </c>
       <c r="P39">
-        <v>172.45243231452</v>
+        <v>174.61659766284</v>
       </c>
       <c r="Q39">
-        <v>386.45243231452</v>
+        <v>388.61659766284</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08424436168073619</v>
+        <v>0.08421964537428409</v>
       </c>
       <c r="T39">
         <v>0.8872897315077158</v>
       </c>
       <c r="U39">
-        <v>0.05790000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V39">
         <v>0.2494</v>
       </c>
       <c r="W39">
-        <v>0.04345974</v>
+        <v>0.04075758</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y39">
-        <v>5.954534103903203</v>
+        <v>6.349309845598443</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4528,13 +4656,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.06906410385013249</v>
+        <v>0.06802175455972032</v>
       </c>
       <c r="C40">
-        <v>1425.217589899797</v>
+        <v>1520.045632091639</v>
       </c>
       <c r="D40">
-        <v>2049.465589899797</v>
+        <v>2144.293632091639</v>
       </c>
       <c r="E40">
         <v>-391.152</v>
@@ -4561,45 +4689,45 @@
         <v>276.125</v>
       </c>
       <c r="M40">
-        <v>47.6255292</v>
+        <v>44.66435640000001</v>
       </c>
       <c r="N40">
-        <v>228.4994708</v>
+        <v>231.4606436</v>
       </c>
       <c r="O40">
-        <v>56.98776801752</v>
+        <v>57.72628451384</v>
       </c>
       <c r="P40">
-        <v>171.51170278248</v>
+        <v>173.73435908616</v>
       </c>
       <c r="Q40">
-        <v>385.51170278248</v>
+        <v>387.73435908616</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08475710104860079</v>
+        <v>0.08473205509632308</v>
       </c>
       <c r="T40">
         <v>0.8991236742799789</v>
       </c>
       <c r="U40">
-        <v>0.05790000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V40">
         <v>0.2494</v>
       </c>
       <c r="W40">
-        <v>0.04345974</v>
+        <v>0.04075758</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y40">
-        <v>5.797835838011013</v>
+        <v>6.182222744398483</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4610,13 +4738,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.06897415604140118</v>
+        <v>0.06819756193364164</v>
       </c>
       <c r="C41">
-        <v>1411.52635375624</v>
+        <v>1481.568218320304</v>
       </c>
       <c r="D41">
-        <v>2057.42035375624</v>
+        <v>2127.462218320304</v>
       </c>
       <c r="E41">
         <v>-369.5060000000001</v>
@@ -4643,37 +4771,37 @@
         <v>276.125</v>
       </c>
       <c r="M41">
-        <v>48.8788326</v>
+        <v>46.6839282</v>
       </c>
       <c r="N41">
-        <v>227.2461674</v>
+        <v>229.4410718</v>
       </c>
       <c r="O41">
-        <v>56.67519414956</v>
+        <v>57.22260330692</v>
       </c>
       <c r="P41">
-        <v>170.57097325044</v>
+        <v>172.21846849308</v>
       </c>
       <c r="Q41">
-        <v>384.57097325044</v>
+        <v>386.21846849308</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08528665154328062</v>
+        <v>0.08526126513711743</v>
       </c>
       <c r="T41">
         <v>0.9113456151759226</v>
       </c>
       <c r="U41">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V41">
         <v>0.2494</v>
       </c>
       <c r="W41">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4809,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.649173380626116</v>
+        <v>5.91477646904615</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4692,13 +4820,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.06888420823266986</v>
+        <v>0.06808814130756297</v>
       </c>
       <c r="C42">
-        <v>1397.897109219297</v>
+        <v>1470.3667073728</v>
       </c>
       <c r="D42">
-        <v>2065.437109219297</v>
+        <v>2137.9067073728</v>
       </c>
       <c r="E42">
         <v>-347.86</v>
@@ -4725,37 +4853,37 @@
         <v>276.125</v>
       </c>
       <c r="M42">
-        <v>50.13213600000001</v>
+        <v>47.88095200000001</v>
       </c>
       <c r="N42">
-        <v>225.992864</v>
+        <v>228.244048</v>
       </c>
       <c r="O42">
-        <v>56.3626202816</v>
+        <v>56.9240655712</v>
       </c>
       <c r="P42">
-        <v>169.6302437184</v>
+        <v>171.3199824288</v>
       </c>
       <c r="Q42">
-        <v>383.6302437184</v>
+        <v>385.3199824288</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08583385372111643</v>
+        <v>0.08580811551260495</v>
       </c>
       <c r="T42">
         <v>0.923974954101731</v>
       </c>
       <c r="U42">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V42">
         <v>0.2494</v>
       </c>
       <c r="W42">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4891,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.507944046110462</v>
+        <v>5.766907057319996</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4774,13 +4902,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.06879426042393855</v>
+        <v>0.06797872068148431</v>
       </c>
       <c r="C43">
-        <v>1384.330583776053</v>
+        <v>1459.268253995441</v>
       </c>
       <c r="D43">
-        <v>2073.516583776052</v>
+        <v>2148.454253995441</v>
       </c>
       <c r="E43">
         <v>-326.2140000000001</v>
@@ -4807,37 +4935,37 @@
         <v>276.125</v>
       </c>
       <c r="M43">
-        <v>51.3854394</v>
+        <v>49.0779758</v>
       </c>
       <c r="N43">
-        <v>224.7395606</v>
+        <v>227.0470242</v>
       </c>
       <c r="O43">
-        <v>56.05004641364</v>
+        <v>56.62552783548001</v>
       </c>
       <c r="P43">
-        <v>168.68951418636</v>
+        <v>170.42149636452</v>
       </c>
       <c r="Q43">
-        <v>382.68951418636</v>
+        <v>384.4214963645201</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08639960512531958</v>
+        <v>0.08637350318895644</v>
       </c>
       <c r="T43">
         <v>0.9370324062114653</v>
       </c>
       <c r="U43">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V43">
         <v>0.2494</v>
       </c>
       <c r="W43">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.373603947424842</v>
+        <v>5.626250787629265</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4856,13 +4984,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.06870431261520724</v>
+        <v>0.06786930005540563</v>
       </c>
       <c r="C44">
-        <v>1370.827516341287</v>
+        <v>1448.274391081048</v>
       </c>
       <c r="D44">
-        <v>2081.659516341287</v>
+        <v>2159.106391081048</v>
       </c>
       <c r="E44">
         <v>-304.5680000000001</v>
@@ -4889,37 +5017,37 @@
         <v>276.125</v>
       </c>
       <c r="M44">
-        <v>52.6387428</v>
+        <v>50.27499960000001</v>
       </c>
       <c r="N44">
-        <v>223.4862572</v>
+        <v>225.8500004</v>
       </c>
       <c r="O44">
-        <v>55.73747254568001</v>
+        <v>56.32699009976</v>
       </c>
       <c r="P44">
-        <v>167.74878465432</v>
+        <v>169.52301030024</v>
       </c>
       <c r="Q44">
-        <v>381.74878465432</v>
+        <v>383.52301030024</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08698486519863316</v>
+        <v>0.08695838699207867</v>
       </c>
       <c r="T44">
         <v>0.9505401152905005</v>
       </c>
       <c r="U44">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V44">
         <v>0.2494</v>
       </c>
       <c r="W44">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.245660996295679</v>
+        <v>5.492292435542853</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4938,13 +5066,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.06861436480647592</v>
+        <v>0.06775987942932696</v>
       </c>
       <c r="C45">
-        <v>1357.38865748275</v>
+        <v>1437.386682074534</v>
       </c>
       <c r="D45">
-        <v>2089.86665748275</v>
+        <v>2169.864682074533</v>
       </c>
       <c r="E45">
         <v>-282.9220000000001</v>
@@ -4971,37 +5099,37 @@
         <v>276.125</v>
       </c>
       <c r="M45">
-        <v>53.8920462</v>
+        <v>51.4720234</v>
       </c>
       <c r="N45">
-        <v>222.2329538</v>
+        <v>224.6529766</v>
       </c>
       <c r="O45">
-        <v>55.42489867772</v>
+        <v>56.02845236404</v>
       </c>
       <c r="P45">
-        <v>166.80805512228</v>
+        <v>168.62452423596</v>
       </c>
       <c r="Q45">
-        <v>380.8080551222801</v>
+        <v>382.6245242359601</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08759066071311564</v>
+        <v>0.08756379303390693</v>
       </c>
       <c r="T45">
         <v>0.9645217790740633</v>
       </c>
       <c r="U45">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V45">
         <v>0.2494</v>
       </c>
       <c r="W45">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5137,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.123668880102755</v>
+        <v>5.364564704483717</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5020,13 +5148,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.0685244169977446</v>
+        <v>0.06765045880324828</v>
       </c>
       <c r="C46">
-        <v>1344.014769651784</v>
+        <v>1426.606721737889</v>
       </c>
       <c r="D46">
-        <v>2098.138769651784</v>
+        <v>2180.730721737888</v>
       </c>
       <c r="E46">
         <v>-261.2760000000001</v>
@@ -5053,37 +5181,37 @@
         <v>276.125</v>
       </c>
       <c r="M46">
-        <v>55.1453496</v>
+        <v>52.66904720000001</v>
       </c>
       <c r="N46">
-        <v>220.9796504</v>
+        <v>223.4559528</v>
       </c>
       <c r="O46">
-        <v>55.11232480976</v>
+        <v>55.72991462832</v>
       </c>
       <c r="P46">
-        <v>165.86732559024</v>
+        <v>167.72603817168</v>
       </c>
       <c r="Q46">
-        <v>379.8673255902401</v>
+        <v>381.72603817168</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.08821809178168678</v>
+        <v>0.08819082072008622</v>
       </c>
       <c r="T46">
         <v>0.9790027879927535</v>
       </c>
       <c r="U46">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V46">
         <v>0.2494</v>
       </c>
       <c r="W46">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.007221860100421</v>
+        <v>5.242642779381814</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5102,13 +5230,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.06843446918901329</v>
+        <v>0.06754103817716961</v>
       </c>
       <c r="C47">
-        <v>1330.70662741944</v>
+        <v>1415.93613693826</v>
       </c>
       <c r="D47">
-        <v>2106.476627419439</v>
+        <v>2191.70613693826</v>
       </c>
       <c r="E47">
         <v>-239.6300000000001</v>
@@ -5135,37 +5263,37 @@
         <v>276.125</v>
       </c>
       <c r="M47">
-        <v>56.398653</v>
+        <v>53.86607100000001</v>
       </c>
       <c r="N47">
-        <v>219.726347</v>
+        <v>222.258929</v>
       </c>
       <c r="O47">
-        <v>54.79975094180001</v>
+        <v>55.4313768926</v>
       </c>
       <c r="P47">
-        <v>164.9265960582</v>
+        <v>166.8275521074</v>
       </c>
       <c r="Q47">
-        <v>378.9265960582001</v>
+        <v>380.8275521074</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.08886833852547871</v>
+        <v>0.08884064941303565</v>
       </c>
       <c r="T47">
         <v>0.9940103790539416</v>
       </c>
       <c r="U47">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V47">
         <v>0.2494</v>
       </c>
       <c r="W47">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.895950263209301</v>
+        <v>5.126139606506663</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5184,13 +5312,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.06834452138028198</v>
+        <v>0.06743161755109095</v>
       </c>
       <c r="C48">
-        <v>1317.465017718265</v>
+        <v>1405.376587459947</v>
       </c>
       <c r="D48">
-        <v>2114.881017718265</v>
+        <v>2202.792587459947</v>
       </c>
       <c r="E48">
         <v>-217.984</v>
@@ -5217,37 +5345,37 @@
         <v>276.125</v>
       </c>
       <c r="M48">
-        <v>57.65195640000001</v>
+        <v>55.06309480000001</v>
       </c>
       <c r="N48">
-        <v>218.4730436</v>
+        <v>221.0619052</v>
       </c>
       <c r="O48">
-        <v>54.48717707383999</v>
+        <v>55.13283915688</v>
       </c>
       <c r="P48">
-        <v>163.98586652616</v>
+        <v>165.92906604312</v>
       </c>
       <c r="Q48">
-        <v>377.98586652616</v>
+        <v>379.92906604312</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.08954266848200365</v>
+        <v>0.08951454583535359</v>
       </c>
       <c r="T48">
         <v>1.0095738068211</v>
       </c>
       <c r="U48">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V48">
         <v>0.2494</v>
       </c>
       <c r="W48">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.789516561835184</v>
+        <v>5.014701788973909</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5266,13 +5394,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.06825457357155067</v>
+        <v>0.06732219692501229</v>
       </c>
       <c r="C49">
-        <v>1304.290740089881</v>
+        <v>1394.929766841174</v>
       </c>
       <c r="D49">
-        <v>2123.352740089881</v>
+        <v>2213.991766841174</v>
       </c>
       <c r="E49">
         <v>-196.3380000000001</v>
@@ -5299,37 +5427,37 @@
         <v>276.125</v>
       </c>
       <c r="M49">
-        <v>58.9052598</v>
+        <v>56.26011860000001</v>
       </c>
       <c r="N49">
-        <v>217.2197402</v>
+        <v>219.8648814</v>
       </c>
       <c r="O49">
-        <v>54.17460320588</v>
+        <v>54.83430142116</v>
       </c>
       <c r="P49">
-        <v>163.04513699412</v>
+        <v>165.03057997884</v>
       </c>
       <c r="Q49">
-        <v>377.04513699412</v>
+        <v>379.03057997884</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.09024244485198238</v>
+        <v>0.09021387231134392</v>
       </c>
       <c r="T49">
         <v>1.025724533749282</v>
       </c>
       <c r="U49">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V49">
         <v>0.2494</v>
       </c>
       <c r="W49">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5465,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.687611954136564</v>
+        <v>4.908006006229783</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5348,13 +5476,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.06816462576281934</v>
+        <v>0.0672127762989336</v>
       </c>
       <c r="C50">
-        <v>1291.184606938548</v>
+        <v>1384.597403236511</v>
       </c>
       <c r="D50">
-        <v>2131.892606938547</v>
+        <v>2225.30540323651</v>
       </c>
       <c r="E50">
         <v>-174.6920000000002</v>
@@ -5381,37 +5509,37 @@
         <v>276.125</v>
       </c>
       <c r="M50">
-        <v>60.1585632</v>
+        <v>57.4571424</v>
       </c>
       <c r="N50">
-        <v>215.9664368</v>
+        <v>218.6678576</v>
       </c>
       <c r="O50">
-        <v>53.86202933792</v>
+        <v>54.53576368544</v>
       </c>
       <c r="P50">
-        <v>162.10440746208</v>
+        <v>164.13209391456</v>
       </c>
       <c r="Q50">
-        <v>376.10440746208</v>
+        <v>378.13209391456</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.09096913569772949</v>
+        <v>0.0909400959594877</v>
       </c>
       <c r="T50">
         <v>1.042496442482395</v>
       </c>
       <c r="U50">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V50">
         <v>0.2494</v>
       </c>
       <c r="W50">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.589953371758719</v>
+        <v>4.805755881099997</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5430,13 +5558,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.06903094235408803</v>
+        <v>0.06710335567285494</v>
       </c>
       <c r="C51">
-        <v>1190.03714255353</v>
+        <v>1374.381260305865</v>
       </c>
       <c r="D51">
-        <v>2052.39114255353</v>
+        <v>2236.735260305865</v>
       </c>
       <c r="E51">
         <v>-153.046</v>
@@ -5463,45 +5591,45 @@
         <v>276.125</v>
       </c>
       <c r="M51">
-        <v>64.169567</v>
+        <v>58.65416620000001</v>
       </c>
       <c r="N51">
-        <v>211.955433</v>
+        <v>217.4708338</v>
       </c>
       <c r="O51">
-        <v>52.8616849902</v>
+        <v>54.23722594972</v>
       </c>
       <c r="P51">
-        <v>159.0937480098</v>
+        <v>163.23360785028</v>
       </c>
       <c r="Q51">
-        <v>373.0937480098</v>
+        <v>377.23360785028</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09172432422370203</v>
+        <v>0.09169479896638222</v>
       </c>
       <c r="T51">
         <v>1.05992607312661</v>
       </c>
       <c r="U51">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V51">
         <v>0.2494</v>
       </c>
       <c r="W51">
-        <v>0.0454113</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.303052255284815</v>
+        <v>4.707679230465303</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5512,13 +5640,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.0689605101453567</v>
+        <v>0.06699393504677627</v>
       </c>
       <c r="C52">
-        <v>1174.63256126337</v>
+        <v>1364.283138131042</v>
       </c>
       <c r="D52">
-        <v>2058.63256126337</v>
+        <v>2248.283138131042</v>
       </c>
       <c r="E52">
         <v>-131.4000000000001</v>
@@ -5545,45 +5673,45 @@
         <v>276.125</v>
       </c>
       <c r="M52">
-        <v>65.47915</v>
+        <v>59.85119000000001</v>
       </c>
       <c r="N52">
-        <v>210.64585</v>
+        <v>216.27381</v>
       </c>
       <c r="O52">
-        <v>52.53507499</v>
+        <v>53.938688214</v>
       </c>
       <c r="P52">
-        <v>158.11077501</v>
+        <v>162.335121786</v>
       </c>
       <c r="Q52">
-        <v>372.11077501</v>
+        <v>376.3351217860001</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.09250972029071342</v>
+        <v>0.09247969009355253</v>
       </c>
       <c r="T52">
         <v>1.078052888996594</v>
       </c>
       <c r="U52">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V52">
         <v>0.2494</v>
       </c>
       <c r="W52">
-        <v>0.0454113</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y52">
-        <v>4.216991210179118</v>
+        <v>4.613525645855996</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5594,13 +5722,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.0688900779366254</v>
+        <v>0.06688451442069759</v>
       </c>
       <c r="C53">
-        <v>1159.266056666284</v>
+        <v>1354.304874160805</v>
       </c>
       <c r="D53">
-        <v>2064.912056666284</v>
+        <v>2259.950874160805</v>
       </c>
       <c r="E53">
         <v>-109.7540000000001</v>
@@ -5627,45 +5755,45 @@
         <v>276.125</v>
       </c>
       <c r="M53">
-        <v>66.78873299999999</v>
+        <v>61.04821380000001</v>
       </c>
       <c r="N53">
-        <v>209.336267</v>
+        <v>215.0767862</v>
       </c>
       <c r="O53">
-        <v>52.20846498980001</v>
+        <v>53.64015047828</v>
       </c>
       <c r="P53">
-        <v>157.1278020102</v>
+        <v>161.43663572172</v>
       </c>
       <c r="Q53">
-        <v>371.1278020102001</v>
+        <v>375.43663572172</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09332717334005183</v>
+        <v>0.0932966175932604</v>
       </c>
       <c r="T53">
         <v>1.096919574902088</v>
       </c>
       <c r="U53">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V53">
         <v>0.2494</v>
       </c>
       <c r="W53">
-        <v>0.0454113</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.134305108018744</v>
+        <v>4.523064358682349</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5676,13 +5804,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.06881964572789409</v>
+        <v>0.06775087379461892</v>
       </c>
       <c r="C54">
-        <v>1143.937978267079</v>
+        <v>1243.462897601964</v>
       </c>
       <c r="D54">
-        <v>2071.229978267079</v>
+        <v>2170.754897601964</v>
       </c>
       <c r="E54">
         <v>-88.10799999999995</v>
@@ -5709,37 +5837,37 @@
         <v>276.125</v>
       </c>
       <c r="M54">
-        <v>68.09831600000001</v>
+        <v>65.05921760000001</v>
       </c>
       <c r="N54">
-        <v>208.026684</v>
+        <v>211.0657824</v>
       </c>
       <c r="O54">
-        <v>51.8818549896</v>
+        <v>52.63980613056</v>
       </c>
       <c r="P54">
-        <v>156.1448290104</v>
+        <v>158.42597626944</v>
       </c>
       <c r="Q54">
-        <v>370.1448290104</v>
+        <v>372.42597626944</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.09417868693311268</v>
+        <v>0.09414758373878943</v>
       </c>
       <c r="T54">
         <v>1.11657237272031</v>
       </c>
       <c r="U54">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V54">
         <v>0.2494</v>
       </c>
       <c r="W54">
-        <v>0.0454113</v>
+        <v>0.04338468</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5875,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.054799240556844</v>
+        <v>4.244210277745485</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5758,13 +5886,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.06982332211916278</v>
+        <v>0.06766021816854026</v>
       </c>
       <c r="C55">
-        <v>1035.757542281792</v>
+        <v>1230.819147386856</v>
       </c>
       <c r="D55">
-        <v>1984.695542281791</v>
+        <v>2179.757147386856</v>
       </c>
       <c r="E55">
         <v>-66.46199999999999</v>
@@ -5791,45 +5919,45 @@
         <v>276.125</v>
       </c>
       <c r="M55">
-        <v>72.50544160000001</v>
+        <v>66.3103564</v>
       </c>
       <c r="N55">
-        <v>203.6195584</v>
+        <v>209.8146436</v>
       </c>
       <c r="O55">
-        <v>50.78271786496</v>
+        <v>52.32777211384001</v>
       </c>
       <c r="P55">
-        <v>152.83684053504</v>
+        <v>157.48687148616</v>
       </c>
       <c r="Q55">
-        <v>366.83684053504</v>
+        <v>371.48687148616</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.09506643514715485</v>
+        <v>0.09503476120966012</v>
       </c>
       <c r="T55">
         <v>1.137061459807393</v>
       </c>
       <c r="U55">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V55">
         <v>0.2494</v>
       </c>
       <c r="W55">
-        <v>0.04743792</v>
+        <v>0.04338468</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.808334849173582</v>
+        <v>4.164130838542741</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5840,13 +5968,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.06977315611043146</v>
+        <v>0.06756956254246159</v>
       </c>
       <c r="C56">
-        <v>1018.264698146813</v>
+        <v>1218.250373835958</v>
       </c>
       <c r="D56">
-        <v>1988.848698146813</v>
+        <v>2188.834373835958</v>
       </c>
       <c r="E56">
         <v>-44.81600000000003</v>
@@ -5873,45 +6001,45 @@
         <v>276.125</v>
       </c>
       <c r="M56">
-        <v>73.87346880000001</v>
+        <v>67.56149520000001</v>
       </c>
       <c r="N56">
-        <v>202.2515312</v>
+        <v>208.5635048</v>
       </c>
       <c r="O56">
-        <v>50.44153188128</v>
+        <v>52.01573809711999</v>
       </c>
       <c r="P56">
-        <v>151.80999931872</v>
+        <v>156.54776670288</v>
       </c>
       <c r="Q56">
-        <v>365.80999931872</v>
+        <v>370.54776670288</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.09599278110963361</v>
+        <v>0.09596051161404692</v>
       </c>
       <c r="T56">
         <v>1.158441376767828</v>
       </c>
       <c r="U56">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V56">
         <v>0.2494</v>
       </c>
       <c r="W56">
-        <v>0.04743792</v>
+        <v>0.04338468</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.737810129744441</v>
+        <v>4.087017304495652</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5922,13 +6050,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.06972299010170015</v>
+        <v>0.06747890691638292</v>
       </c>
       <c r="C57">
-        <v>1000.789272173402</v>
+        <v>1205.757517548783</v>
       </c>
       <c r="D57">
-        <v>1993.019272173402</v>
+        <v>2197.987517548783</v>
       </c>
       <c r="E57">
         <v>-23.17000000000007</v>
@@ -5955,45 +6083,45 @@
         <v>276.125</v>
       </c>
       <c r="M57">
-        <v>75.24149600000001</v>
+        <v>68.812634</v>
       </c>
       <c r="N57">
-        <v>200.883504</v>
+        <v>207.312366</v>
       </c>
       <c r="O57">
-        <v>50.1003458976</v>
+        <v>51.7037040804</v>
       </c>
       <c r="P57">
-        <v>150.7831581024</v>
+        <v>155.6086619196</v>
       </c>
       <c r="Q57">
-        <v>364.7831581024</v>
+        <v>369.6086619196</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.0969602980037781</v>
+        <v>0.09692740648085094</v>
       </c>
       <c r="T57">
         <v>1.180771512259837</v>
       </c>
       <c r="U57">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V57">
         <v>0.2494</v>
       </c>
       <c r="W57">
-        <v>0.04743792</v>
+        <v>0.04338468</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>3.66984994556727</v>
+        <v>4.012707898959368</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6004,13 +6132,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06967282409296882</v>
+        <v>0.06885942729030424</v>
       </c>
       <c r="C58">
-        <v>983.3313741683812</v>
+        <v>1052.522536113989</v>
       </c>
       <c r="D58">
-        <v>1997.207374168381</v>
+        <v>2066.398536113988</v>
       </c>
       <c r="E58">
         <v>-1.523999999999887</v>
@@ -6037,37 +6165,37 @@
         <v>276.125</v>
       </c>
       <c r="M58">
-        <v>76.60952320000001</v>
+        <v>74.30638880000002</v>
       </c>
       <c r="N58">
-        <v>199.5154768</v>
+        <v>201.8186112</v>
       </c>
       <c r="O58">
-        <v>49.75915991392</v>
+        <v>50.33356163327999</v>
       </c>
       <c r="P58">
-        <v>149.75631688608</v>
+        <v>151.48504956672</v>
       </c>
       <c r="Q58">
-        <v>363.75631688608</v>
+        <v>365.48504956672</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.09797179293856553</v>
+        <v>0.09793825111432783</v>
       </c>
       <c r="T58">
         <v>1.204116653910574</v>
       </c>
       <c r="U58">
-        <v>0.06320000000000001</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V58">
         <v>0.2494</v>
       </c>
       <c r="W58">
-        <v>0.04743792</v>
+        <v>0.04601178</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6203,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.604316910824997</v>
+        <v>3.716033095662965</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6086,13 +6214,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06962265808423751</v>
+        <v>0.06879504266422556</v>
       </c>
       <c r="C59">
-        <v>965.8911148634998</v>
+        <v>1036.66231781572</v>
       </c>
       <c r="D59">
-        <v>2001.4131148635</v>
+        <v>2072.18431781572</v>
       </c>
       <c r="E59">
         <v>20.12200000000007</v>
@@ -6119,37 +6247,37 @@
         <v>276.125</v>
       </c>
       <c r="M59">
-        <v>77.97755040000001</v>
+        <v>75.63328860000001</v>
       </c>
       <c r="N59">
-        <v>198.1474496</v>
+        <v>200.4917114</v>
       </c>
       <c r="O59">
-        <v>49.41797393024</v>
+        <v>50.00263282316</v>
       </c>
       <c r="P59">
-        <v>148.72947566976</v>
+        <v>150.48907857684</v>
       </c>
       <c r="Q59">
-        <v>362.72947566976</v>
+        <v>364.48907857684</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.09903033414938957</v>
+        <v>0.09899611177726877</v>
       </c>
       <c r="T59">
         <v>1.228547616103205</v>
       </c>
       <c r="U59">
-        <v>0.06320000000000001</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V59">
         <v>0.2494</v>
       </c>
       <c r="W59">
-        <v>0.04743792</v>
+        <v>0.04601178</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.541083280810524</v>
+        <v>3.65083953258116</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6168,13 +6296,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.07161862767550621</v>
+        <v>0.0687306580381469</v>
       </c>
       <c r="C60">
-        <v>789.5211780593881</v>
+        <v>1020.834590115045</v>
       </c>
       <c r="D60">
-        <v>1846.689178059388</v>
+        <v>2078.002590115045</v>
       </c>
       <c r="E60">
         <v>41.7679999999998</v>
@@ -6201,45 +6329,45 @@
         <v>276.125</v>
       </c>
       <c r="M60">
-        <v>85.24627720000001</v>
+        <v>76.96018839999999</v>
       </c>
       <c r="N60">
-        <v>190.8787228</v>
+        <v>199.1648116</v>
       </c>
       <c r="O60">
-        <v>47.60515346632</v>
+        <v>49.67170401304001</v>
       </c>
       <c r="P60">
-        <v>143.27356933368</v>
+        <v>149.49310758696</v>
       </c>
       <c r="Q60">
-        <v>357.27356933368</v>
+        <v>363.49310758696</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1001392820845386</v>
+        <v>0.1001043467574926</v>
       </c>
       <c r="T60">
         <v>1.254141957447867</v>
       </c>
       <c r="U60">
-        <v>0.06790000000000002</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V60">
         <v>0.2494</v>
       </c>
       <c r="W60">
-        <v>0.05096574000000001</v>
+        <v>0.04601178</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.239144383421825</v>
+        <v>3.587894023398727</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6250,13 +6378,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.07160373986677489</v>
+        <v>0.06866627341206823</v>
       </c>
       <c r="C61">
-        <v>768.9406497860098</v>
+        <v>1005.039627463547</v>
       </c>
       <c r="D61">
-        <v>1847.75464978601</v>
+        <v>2083.853627463547</v>
       </c>
       <c r="E61">
         <v>63.41399999999976</v>
@@ -6283,45 +6411,45 @@
         <v>276.125</v>
       </c>
       <c r="M61">
-        <v>86.71604060000001</v>
+        <v>78.2870882</v>
       </c>
       <c r="N61">
-        <v>189.4089594</v>
+        <v>197.8379118</v>
       </c>
       <c r="O61">
-        <v>47.23859447436</v>
+        <v>49.34077520292</v>
       </c>
       <c r="P61">
-        <v>142.17036492564</v>
+        <v>148.49713659708</v>
       </c>
       <c r="Q61">
-        <v>356.17036492564</v>
+        <v>362.49713659708</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1013023250409144</v>
+        <v>0.1012666419806542</v>
       </c>
       <c r="T61">
         <v>1.280984803248366</v>
       </c>
       <c r="U61">
-        <v>0.06790000000000002</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V61">
         <v>0.2494</v>
       </c>
       <c r="W61">
-        <v>0.05096574000000001</v>
+        <v>0.04601178</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.184243631160438</v>
+        <v>3.527082260290273</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6332,13 +6460,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.07158885205804358</v>
+        <v>0.06986289678598956</v>
       </c>
       <c r="C62">
-        <v>748.3613516983899</v>
+        <v>879.7657068257661</v>
       </c>
       <c r="D62">
-        <v>1848.82135169839</v>
+        <v>1980.225706825766</v>
       </c>
       <c r="E62">
         <v>85.05999999999995</v>
@@ -6365,37 +6493,37 @@
         <v>276.125</v>
       </c>
       <c r="M62">
-        <v>88.18580400000002</v>
+        <v>83.250516</v>
       </c>
       <c r="N62">
-        <v>187.939196</v>
+        <v>192.874484</v>
       </c>
       <c r="O62">
-        <v>46.87203548239999</v>
+        <v>48.1028963096</v>
       </c>
       <c r="P62">
-        <v>141.0671605176</v>
+        <v>144.7715876904</v>
       </c>
       <c r="Q62">
-        <v>355.0671605176</v>
+        <v>358.7715876904</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1025235201451089</v>
+        <v>0.1024870519649739</v>
       </c>
       <c r="T62">
         <v>1.30916979133889</v>
       </c>
       <c r="U62">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V62">
         <v>0.2494</v>
       </c>
       <c r="W62">
-        <v>0.05096574000000001</v>
+        <v>0.04811346</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.13117290397443</v>
+        <v>3.316796258656222</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6414,13 +6542,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.07157396424931226</v>
+        <v>0.06981952895991089</v>
       </c>
       <c r="C63">
-        <v>727.7832859283058</v>
+        <v>861.6950510464399</v>
       </c>
       <c r="D63">
-        <v>1849.889285928306</v>
+        <v>1983.80105104644</v>
       </c>
       <c r="E63">
         <v>106.7059999999999</v>
@@ -6447,37 +6575,37 @@
         <v>276.125</v>
       </c>
       <c r="M63">
-        <v>89.65556740000002</v>
+        <v>84.63802460000001</v>
       </c>
       <c r="N63">
-        <v>186.4694326</v>
+        <v>191.4869754</v>
       </c>
       <c r="O63">
-        <v>46.50547649044</v>
+        <v>47.75685166476001</v>
       </c>
       <c r="P63">
-        <v>139.96395610956</v>
+        <v>143.73012373524</v>
       </c>
       <c r="Q63">
-        <v>353.96395610956</v>
+        <v>357.73012373524</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1038073406392622</v>
+        <v>0.1037700470766946</v>
       </c>
       <c r="T63">
         <v>1.338800163434056</v>
       </c>
       <c r="U63">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V63">
         <v>0.2494</v>
       </c>
       <c r="W63">
-        <v>0.05096574000000001</v>
+        <v>0.04811346</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.079842200630587</v>
+        <v>3.262422549497924</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6496,13 +6624,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.07155907644058096</v>
+        <v>0.06977616113383223</v>
       </c>
       <c r="C64">
-        <v>707.2064546124591</v>
+        <v>843.6373293565591</v>
       </c>
       <c r="D64">
-        <v>1850.958454612459</v>
+        <v>1987.389329356559</v>
       </c>
       <c r="E64">
         <v>128.3519999999999</v>
@@ -6529,37 +6657,37 @@
         <v>276.125</v>
       </c>
       <c r="M64">
-        <v>91.12533080000001</v>
+        <v>86.0255332</v>
       </c>
       <c r="N64">
-        <v>184.9996692</v>
+        <v>190.0994668</v>
       </c>
       <c r="O64">
-        <v>46.13891749848</v>
+        <v>47.41080701992001</v>
       </c>
       <c r="P64">
-        <v>138.86075170152</v>
+        <v>142.68865978008</v>
       </c>
       <c r="Q64">
-        <v>352.86075170152</v>
+        <v>356.68865978008</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1051587306331077</v>
+        <v>0.1051205682469269</v>
       </c>
       <c r="T64">
         <v>1.369990028797389</v>
       </c>
       <c r="U64">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V64">
         <v>0.2494</v>
       </c>
       <c r="W64">
-        <v>0.05096574000000001</v>
+        <v>0.04811346</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.030167326426868</v>
+        <v>3.209802830957635</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6578,13 +6706,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.07594195403184963</v>
+        <v>0.06973279330775356</v>
       </c>
       <c r="C65">
-        <v>416.4165124341221</v>
+        <v>825.5926120684362</v>
       </c>
       <c r="D65">
-        <v>1581.814512434122</v>
+        <v>1990.990612068436</v>
       </c>
       <c r="E65">
         <v>149.9979999999998</v>
@@ -6611,45 +6739,45 @@
         <v>276.125</v>
       </c>
       <c r="M65">
-        <v>105.2774856</v>
+        <v>87.4130418</v>
       </c>
       <c r="N65">
-        <v>170.8475144</v>
+        <v>188.7119582</v>
       </c>
       <c r="O65">
-        <v>42.60937009136001</v>
+        <v>47.06476237508</v>
       </c>
       <c r="P65">
-        <v>128.23814430864</v>
+        <v>141.64719582492</v>
       </c>
       <c r="Q65">
-        <v>342.23814430864</v>
+        <v>355.64719582492</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1065831687347287</v>
+        <v>0.1065440905614961</v>
       </c>
       <c r="T65">
         <v>1.402865832829009</v>
       </c>
       <c r="U65">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V65">
         <v>0.2494</v>
       </c>
       <c r="W65">
-        <v>0.05794632</v>
+        <v>0.04811346</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.62283049814784</v>
+        <v>3.158853579672593</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6660,13 +6788,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.07599687202311831</v>
+        <v>0.06968942548167488</v>
       </c>
       <c r="C66">
-        <v>391.8937219004526</v>
+        <v>807.5609700049508</v>
       </c>
       <c r="D66">
-        <v>1578.937721900453</v>
+        <v>1994.604970004951</v>
       </c>
       <c r="E66">
         <v>171.644</v>
@@ -6693,45 +6821,45 @@
         <v>276.125</v>
       </c>
       <c r="M66">
-        <v>106.9485568</v>
+        <v>88.80055040000001</v>
       </c>
       <c r="N66">
-        <v>169.1764432</v>
+        <v>187.3244496</v>
       </c>
       <c r="O66">
-        <v>42.19260493408</v>
+        <v>46.71871773023999</v>
       </c>
       <c r="P66">
-        <v>126.98383826592</v>
+        <v>140.60573186976</v>
       </c>
       <c r="Q66">
-        <v>340.98383826592</v>
+        <v>354.60573186976</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1080867422864397</v>
+        <v>0.1080466974490969</v>
       </c>
       <c r="T66">
         <v>1.437568070417943</v>
       </c>
       <c r="U66">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V66">
         <v>0.2494</v>
       </c>
       <c r="W66">
-        <v>0.05794632</v>
+        <v>0.04811346</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.581848771614279</v>
+        <v>3.109496492490208</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6742,13 +6870,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.076051790014387</v>
+        <v>0.0696460576555962</v>
       </c>
       <c r="C67">
-        <v>367.3813762070606</v>
+        <v>789.5424745041926</v>
       </c>
       <c r="D67">
-        <v>1576.071376207061</v>
+        <v>1998.232474504192</v>
       </c>
       <c r="E67">
         <v>193.29</v>
@@ -6775,45 +6903,45 @@
         <v>276.125</v>
       </c>
       <c r="M67">
-        <v>108.619628</v>
+        <v>90.18805900000001</v>
       </c>
       <c r="N67">
-        <v>167.505372</v>
+        <v>185.936941</v>
       </c>
       <c r="O67">
-        <v>41.7758397768</v>
+        <v>46.3726730854</v>
       </c>
       <c r="P67">
-        <v>125.7295322232</v>
+        <v>139.5642679146</v>
       </c>
       <c r="Q67">
-        <v>339.7295322232</v>
+        <v>353.5642679146</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.10967623432682</v>
+        <v>0.1096351675874178</v>
       </c>
       <c r="T67">
         <v>1.474253293011958</v>
       </c>
       <c r="U67">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V67">
         <v>0.2494</v>
       </c>
       <c r="W67">
-        <v>0.05794632</v>
+        <v>0.04811346</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.542128021281752</v>
+        <v>3.061658084913436</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6824,13 +6952,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.07610670800565568</v>
+        <v>0.06960268982951753</v>
       </c>
       <c r="C68">
-        <v>342.879418573483</v>
+        <v>771.537197424153</v>
       </c>
       <c r="D68">
-        <v>1573.215418573483</v>
+        <v>2001.873197424153</v>
       </c>
       <c r="E68">
         <v>214.9359999999999</v>
@@ -6857,45 +6985,45 @@
         <v>276.125</v>
       </c>
       <c r="M68">
-        <v>110.2906992</v>
+        <v>91.5755676</v>
       </c>
       <c r="N68">
-        <v>165.8343008</v>
+        <v>184.5494324</v>
       </c>
       <c r="O68">
-        <v>41.35907461952</v>
+        <v>46.02662844056</v>
       </c>
       <c r="P68">
-        <v>124.47522618048</v>
+        <v>138.52280395944</v>
       </c>
       <c r="Q68">
-        <v>338.47522618048</v>
+        <v>352.52280395944</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1113592258989873</v>
+        <v>0.1113170771456398</v>
       </c>
       <c r="T68">
         <v>1.513096469876209</v>
       </c>
       <c r="U68">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V68">
         <v>0.2494</v>
       </c>
       <c r="W68">
-        <v>0.05794632</v>
+        <v>0.04811346</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.50361093005021</v>
+        <v>3.015269326051111</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6906,13 +7034,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.07852526539692437</v>
+        <v>0.07348195760343887</v>
       </c>
       <c r="C69">
-        <v>204.9650940083795</v>
+        <v>469.3546005008322</v>
       </c>
       <c r="D69">
-        <v>1456.94709400838</v>
+        <v>1721.336600500832</v>
       </c>
       <c r="E69">
         <v>236.5819999999999</v>
@@ -6939,45 +7067,45 @@
         <v>276.125</v>
       </c>
       <c r="M69">
-        <v>118.7780958</v>
+        <v>104.2752758</v>
       </c>
       <c r="N69">
-        <v>157.3469042</v>
+        <v>171.8497242</v>
       </c>
       <c r="O69">
-        <v>39.24231790748001</v>
+        <v>42.85932121548</v>
       </c>
       <c r="P69">
-        <v>118.10458629252</v>
+        <v>128.99040298452</v>
       </c>
       <c r="Q69">
-        <v>332.10458629252</v>
+        <v>342.99040298452</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1131442169603769</v>
+        <v>0.1131009206164814</v>
       </c>
       <c r="T69">
         <v>1.554293778671627</v>
       </c>
       <c r="U69">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V69">
         <v>0.2494</v>
       </c>
       <c r="W69">
-        <v>0.06147414</v>
+        <v>0.05396814</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.324713139575353</v>
+        <v>2.648039028250645</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6988,13 +7116,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.07861546158819305</v>
+        <v>0.07349713657736021</v>
       </c>
       <c r="C70">
-        <v>179.3145463835849</v>
+        <v>446.7652494329025</v>
       </c>
       <c r="D70">
-        <v>1452.942546383585</v>
+        <v>1720.393249432903</v>
       </c>
       <c r="E70">
         <v>258.2280000000001</v>
@@ -7021,45 +7149,45 @@
         <v>276.125</v>
       </c>
       <c r="M70">
-        <v>120.5509032</v>
+        <v>105.8316232</v>
       </c>
       <c r="N70">
-        <v>155.5740968</v>
+        <v>170.2933768</v>
       </c>
       <c r="O70">
-        <v>38.80017974192</v>
+        <v>42.47116817392</v>
       </c>
       <c r="P70">
-        <v>116.77391705808</v>
+        <v>127.82220862608</v>
       </c>
       <c r="Q70">
-        <v>330.77391705808</v>
+        <v>341.82220862608</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1150407699631033</v>
+        <v>0.1149962543042506</v>
       </c>
       <c r="T70">
         <v>1.598065919266759</v>
       </c>
       <c r="U70">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V70">
         <v>0.2494</v>
       </c>
       <c r="W70">
-        <v>0.06147414</v>
+        <v>0.05396814</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y70">
-        <v>2.290526181640421</v>
+        <v>2.609097277835194</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7070,13 +7198,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07870565777946173</v>
+        <v>0.07351231555128152</v>
       </c>
       <c r="C71">
-        <v>153.685952122916</v>
+        <v>424.1769317756425</v>
       </c>
       <c r="D71">
-        <v>1448.959952122916</v>
+        <v>1719.450931775643</v>
       </c>
       <c r="E71">
         <v>279.874</v>
@@ -7103,45 +7231,45 @@
         <v>276.125</v>
       </c>
       <c r="M71">
-        <v>122.3237106</v>
+        <v>107.3879706</v>
       </c>
       <c r="N71">
-        <v>153.8012894</v>
+        <v>168.7370294</v>
       </c>
       <c r="O71">
-        <v>38.35804157635999</v>
+        <v>42.08301513236</v>
       </c>
       <c r="P71">
-        <v>115.44324782364</v>
+        <v>126.65401426764</v>
       </c>
       <c r="Q71">
-        <v>329.44324782364</v>
+        <v>340.65401426764</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1170596812240701</v>
+        <v>0.1170138675847791</v>
       </c>
       <c r="T71">
         <v>1.644662068932544</v>
       </c>
       <c r="U71">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V71">
         <v>0.2494</v>
       </c>
       <c r="W71">
-        <v>0.06147414</v>
+        <v>0.05396814</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.257330150022443</v>
+        <v>2.571284273808597</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7152,13 +7280,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07879585397073041</v>
+        <v>0.07352749452520285</v>
       </c>
       <c r="C72">
-        <v>128.0791311937694</v>
+        <v>401.5896458318757</v>
       </c>
       <c r="D72">
-        <v>1444.999131193769</v>
+        <v>1718.509645831876</v>
       </c>
       <c r="E72">
         <v>301.52</v>
@@ -7185,45 +7313,45 @@
         <v>276.125</v>
       </c>
       <c r="M72">
-        <v>124.096518</v>
+        <v>108.944318</v>
       </c>
       <c r="N72">
-        <v>152.028482</v>
+        <v>167.180682</v>
       </c>
       <c r="O72">
-        <v>37.9159034108</v>
+        <v>41.6948620908</v>
       </c>
       <c r="P72">
-        <v>114.1125785892</v>
+        <v>125.4858199092</v>
       </c>
       <c r="Q72">
-        <v>328.1125785892</v>
+        <v>339.4858199092</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1192131865691014</v>
+        <v>0.1191659884173429</v>
       </c>
       <c r="T72">
         <v>1.694364628576049</v>
       </c>
       <c r="U72">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V72">
         <v>0.2494</v>
       </c>
       <c r="W72">
-        <v>0.06147414</v>
+        <v>0.05396814</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.225082576450695</v>
+        <v>2.534551641325617</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7234,13 +7362,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.07888605016199911</v>
+        <v>0.0756210848991242</v>
       </c>
       <c r="C73">
-        <v>102.4939055266952</v>
+        <v>259.2956122618345</v>
       </c>
       <c r="D73">
-        <v>1441.059905526695</v>
+        <v>1597.861612261834</v>
       </c>
       <c r="E73">
         <v>323.1659999999997</v>
@@ -7267,37 +7395,37 @@
         <v>276.125</v>
       </c>
       <c r="M73">
-        <v>125.8693254</v>
+        <v>116.4944428</v>
       </c>
       <c r="N73">
-        <v>150.2556746</v>
+        <v>159.6305572</v>
       </c>
       <c r="O73">
-        <v>37.47376524524001</v>
+        <v>39.81186096568</v>
       </c>
       <c r="P73">
-        <v>112.78190935476</v>
+        <v>119.81869623432</v>
       </c>
       <c r="Q73">
-        <v>326.78190935476</v>
+        <v>333.81869623432</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1215152095241349</v>
+        <v>0.1214665313762903</v>
       </c>
       <c r="T73">
         <v>1.747494950953587</v>
       </c>
       <c r="U73">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V73">
         <v>0.2494</v>
       </c>
       <c r="W73">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.19374338523308</v>
+        <v>2.370284739453683</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7316,13 +7444,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.0789762463532678</v>
+        <v>0.07566553727304554</v>
       </c>
       <c r="C74">
-        <v>76.9300989887131</v>
+        <v>235.2713278461401</v>
       </c>
       <c r="D74">
-        <v>1437.142098988713</v>
+        <v>1595.48332784614</v>
       </c>
       <c r="E74">
         <v>344.8119999999999</v>
@@ -7349,37 +7477,37 @@
         <v>276.125</v>
       </c>
       <c r="M74">
-        <v>127.6421328</v>
+        <v>118.1352096</v>
       </c>
       <c r="N74">
-        <v>148.4828672</v>
+        <v>157.9897904</v>
       </c>
       <c r="O74">
-        <v>37.03162707968</v>
+        <v>39.40265372576</v>
       </c>
       <c r="P74">
-        <v>111.45124012032</v>
+        <v>118.58713667424</v>
       </c>
       <c r="Q74">
-        <v>325.45124012032</v>
+        <v>332.58713667424</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1239816626902421</v>
+        <v>0.1239313988323054</v>
       </c>
       <c r="T74">
         <v>1.804420296358094</v>
       </c>
       <c r="U74">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V74">
         <v>0.2494</v>
       </c>
       <c r="W74">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.163274727104842</v>
+        <v>2.337364118072382</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7398,13 +7526,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.07906644254453647</v>
+        <v>0.07570998964696685</v>
       </c>
       <c r="C75">
-        <v>51.38753735705973</v>
+        <v>211.254112666471</v>
       </c>
       <c r="D75">
-        <v>1433.24553735706</v>
+        <v>1593.112112666471</v>
       </c>
       <c r="E75">
         <v>366.4579999999999</v>
@@ -7431,37 +7559,37 @@
         <v>276.125</v>
       </c>
       <c r="M75">
-        <v>129.4149402</v>
+        <v>119.7759764</v>
       </c>
       <c r="N75">
-        <v>146.7100598</v>
+        <v>156.3490236</v>
       </c>
       <c r="O75">
-        <v>36.58948891412</v>
+        <v>38.99344648584</v>
       </c>
       <c r="P75">
-        <v>110.12057088588</v>
+        <v>117.35557711416</v>
       </c>
       <c r="Q75">
-        <v>324.1205708858801</v>
+        <v>331.35557711416</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1266308160908758</v>
+        <v>0.1265788490628402</v>
       </c>
       <c r="T75">
         <v>1.865562334014785</v>
       </c>
       <c r="U75">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V75">
         <v>0.2494</v>
       </c>
       <c r="W75">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.133640826733543</v>
+        <v>2.305345431523445</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7480,13 +7608,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.07915663873580517</v>
+        <v>0.07575444202088819</v>
       </c>
       <c r="C76">
-        <v>25.86604829335829</v>
+        <v>187.2439352505983</v>
       </c>
       <c r="D76">
-        <v>1429.370048293358</v>
+        <v>1590.747935250598</v>
       </c>
       <c r="E76">
         <v>388.1039999999998</v>
@@ -7513,37 +7641,37 @@
         <v>276.125</v>
       </c>
       <c r="M76">
-        <v>131.1877476</v>
+        <v>121.4167432</v>
       </c>
       <c r="N76">
-        <v>144.9372524</v>
+        <v>154.7082568</v>
       </c>
       <c r="O76">
-        <v>36.14735074856</v>
+        <v>38.58423924592</v>
       </c>
       <c r="P76">
-        <v>108.78990165144</v>
+        <v>116.12401755408</v>
       </c>
       <c r="Q76">
-        <v>322.78990165144</v>
+        <v>330.1240175540801</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1294837505223276</v>
+        <v>0.1294299493111084</v>
       </c>
       <c r="T76">
         <v>1.931407605337376</v>
       </c>
       <c r="U76">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V76">
         <v>0.2494</v>
       </c>
       <c r="W76">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.104807842588495</v>
+        <v>2.274192114881237</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7562,13 +7690,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.07924683492707385</v>
+        <v>0.07579889439480951</v>
       </c>
       <c r="C77">
-        <v>0.3654613182170579</v>
+        <v>163.2407643128395</v>
       </c>
       <c r="D77">
-        <v>1425.515461318217</v>
+        <v>1588.390764312839</v>
       </c>
       <c r="E77">
         <v>409.7499999999998</v>
@@ -7595,37 +7723,37 @@
         <v>276.125</v>
       </c>
       <c r="M77">
-        <v>132.960555</v>
+        <v>123.05751</v>
       </c>
       <c r="N77">
-        <v>143.164445</v>
+        <v>153.06749</v>
       </c>
       <c r="O77">
-        <v>35.70521258300001</v>
+        <v>38.17503200600001</v>
       </c>
       <c r="P77">
-        <v>107.459232417</v>
+        <v>114.892457994</v>
       </c>
       <c r="Q77">
-        <v>321.459232417</v>
+        <v>328.892457994</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1325649197082954</v>
+        <v>0.132509137579238</v>
       </c>
       <c r="T77">
         <v>2.002520498365775</v>
       </c>
       <c r="U77">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V77">
         <v>0.2494</v>
       </c>
       <c r="W77">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.076743738020649</v>
+        <v>2.243869553349487</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7644,13 +7772,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.07933703111834253</v>
+        <v>0.07584334676873083</v>
       </c>
       <c r="C78">
-        <v>-25.11439221377327</v>
+        <v>139.2445687526726</v>
       </c>
       <c r="D78">
-        <v>1421.681607786227</v>
+        <v>1586.040568752673</v>
       </c>
       <c r="E78">
         <v>431.396</v>
@@ -7677,37 +7805,37 @@
         <v>276.125</v>
       </c>
       <c r="M78">
-        <v>134.7333624</v>
+        <v>124.6982768</v>
       </c>
       <c r="N78">
-        <v>141.3916376</v>
+        <v>151.4267232</v>
       </c>
       <c r="O78">
-        <v>35.26307441744</v>
+        <v>37.76582476607999</v>
       </c>
       <c r="P78">
-        <v>106.12856318256</v>
+        <v>113.66089843392</v>
       </c>
       <c r="Q78">
-        <v>320.12856318256</v>
+        <v>327.66089843392</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1359028529930939</v>
+        <v>0.1358449248697118</v>
       </c>
       <c r="T78">
         <v>2.079559465813207</v>
       </c>
       <c r="U78">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V78">
         <v>0.2494</v>
       </c>
       <c r="W78">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.049418162520376</v>
+        <v>2.214344953963309</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7726,13 +7854,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.07942722730961121</v>
+        <v>0.07588779914265217</v>
       </c>
       <c r="C79">
-        <v>-50.57367913863368</v>
+        <v>115.2553176533704</v>
       </c>
       <c r="D79">
-        <v>1417.868320861366</v>
+        <v>1583.69731765337</v>
       </c>
       <c r="E79">
         <v>453.0419999999999</v>
@@ -7759,37 +7887,37 @@
         <v>276.125</v>
       </c>
       <c r="M79">
-        <v>136.5061698</v>
+        <v>126.3390436</v>
       </c>
       <c r="N79">
-        <v>139.6188302</v>
+        <v>149.7859564</v>
       </c>
       <c r="O79">
-        <v>34.82093625188</v>
+        <v>37.35661752615999</v>
       </c>
       <c r="P79">
-        <v>104.79789394812</v>
+        <v>112.42933887384</v>
       </c>
       <c r="Q79">
-        <v>318.79789394812</v>
+        <v>326.42933887384</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1395310413461357</v>
+        <v>0.1394707806202268</v>
       </c>
       <c r="T79">
         <v>2.163297473908241</v>
       </c>
       <c r="U79">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V79">
         <v>0.2494</v>
       </c>
       <c r="W79">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.022802342227904</v>
+        <v>2.185587227288461</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7808,13 +7936,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.0890605519008799</v>
+        <v>0.0759322515165735</v>
       </c>
       <c r="C80">
-        <v>-387.9527237338605</v>
+        <v>91.27298028064524</v>
       </c>
       <c r="D80">
-        <v>1102.135276266139</v>
+        <v>1581.360980280645</v>
       </c>
       <c r="E80">
         <v>474.6879999999999</v>
@@ -7841,45 +7969,45 @@
         <v>276.125</v>
       </c>
       <c r="M80">
-        <v>165.7997016</v>
+        <v>127.9798104</v>
       </c>
       <c r="N80">
-        <v>110.3252984</v>
+        <v>148.1451896</v>
       </c>
       <c r="O80">
-        <v>27.51512942096</v>
+        <v>36.94741028624</v>
       </c>
       <c r="P80">
-        <v>82.81016897903999</v>
+        <v>111.19777931376</v>
       </c>
       <c r="Q80">
-        <v>296.81016897904</v>
+        <v>325.19777931376</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1434890650039996</v>
+        <v>0.1434262596207886</v>
       </c>
       <c r="T80">
         <v>2.254648028193734</v>
       </c>
       <c r="U80">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V80">
         <v>0.2494</v>
       </c>
       <c r="W80">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y80">
-        <v>1.665413130031833</v>
+        <v>2.15756687822066</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7890,13 +8018,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.08927309589214859</v>
+        <v>0.07597670389049482</v>
       </c>
       <c r="C81">
-        <v>-414.9871651532796</v>
+        <v>67.29752608130252</v>
       </c>
       <c r="D81">
-        <v>1096.746834846721</v>
+        <v>1579.031526081303</v>
       </c>
       <c r="E81">
         <v>496.3340000000001</v>
@@ -7923,45 +8051,45 @@
         <v>276.125</v>
       </c>
       <c r="M81">
-        <v>167.9253388</v>
+        <v>129.6205772</v>
       </c>
       <c r="N81">
-        <v>108.1996612</v>
+        <v>146.5044228</v>
       </c>
       <c r="O81">
-        <v>26.98499550328</v>
+        <v>36.53820304632</v>
       </c>
       <c r="P81">
-        <v>81.21466569671998</v>
+        <v>109.96621975368</v>
       </c>
       <c r="Q81">
-        <v>295.21466569672</v>
+        <v>323.96621975368</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1478240432959457</v>
+        <v>0.1477584509071183</v>
       </c>
       <c r="T81">
         <v>2.354698635268321</v>
       </c>
       <c r="U81">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V81">
         <v>0.2494</v>
       </c>
       <c r="W81">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y81">
-        <v>1.644331951170671</v>
+        <v>2.130255905078626</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7972,13 +8100,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.08948563988341728</v>
+        <v>0.07602115626441616</v>
       </c>
       <c r="C82">
-        <v>-441.9691737435555</v>
+        <v>43.32892468191153</v>
       </c>
       <c r="D82">
-        <v>1091.410826256445</v>
+        <v>1576.708924681912</v>
       </c>
       <c r="E82">
         <v>517.98</v>
@@ -8005,45 +8133,45 @@
         <v>276.125</v>
       </c>
       <c r="M82">
-        <v>170.050976</v>
+        <v>131.261344</v>
       </c>
       <c r="N82">
-        <v>106.074024</v>
+        <v>144.863656</v>
       </c>
       <c r="O82">
-        <v>26.4548615856</v>
+        <v>36.1289958064</v>
       </c>
       <c r="P82">
-        <v>79.61916241439998</v>
+        <v>108.7346601936</v>
       </c>
       <c r="Q82">
-        <v>293.6191624144</v>
+        <v>322.7346601936</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1525925194170864</v>
+        <v>0.1525238613220808</v>
       </c>
       <c r="T82">
         <v>2.464754303050366</v>
       </c>
       <c r="U82">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V82">
         <v>0.2494</v>
       </c>
       <c r="W82">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y82">
-        <v>1.623777801781038</v>
+        <v>2.103627706265144</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8054,13 +8182,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08969818387468596</v>
+        <v>0.07606560863833749</v>
       </c>
       <c r="C83">
-        <v>-468.8995111044953</v>
+        <v>19.367145887486</v>
       </c>
       <c r="D83">
-        <v>1086.126488895505</v>
+        <v>1574.393145887486</v>
       </c>
       <c r="E83">
         <v>539.626</v>
@@ -8087,45 +8215,45 @@
         <v>276.125</v>
       </c>
       <c r="M83">
-        <v>172.1766132</v>
+        <v>132.9021108</v>
       </c>
       <c r="N83">
-        <v>103.9483868</v>
+        <v>143.2228892</v>
       </c>
       <c r="O83">
-        <v>25.92472766792</v>
+        <v>35.71978856648</v>
       </c>
       <c r="P83">
-        <v>78.02365913207998</v>
+        <v>107.50310063352</v>
       </c>
       <c r="Q83">
-        <v>292.02365913208</v>
+        <v>321.50310063352</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.157862940393084</v>
+        <v>0.1577908938859868</v>
       </c>
       <c r="T83">
         <v>2.586394777967363</v>
       </c>
       <c r="U83">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V83">
         <v>0.2494</v>
       </c>
       <c r="W83">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y83">
-        <v>1.603731162252877</v>
+        <v>2.077656993842117</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8136,13 +8264,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08991072786595465</v>
+        <v>0.07611006101225881</v>
       </c>
       <c r="C84">
-        <v>-495.7789241570754</v>
+        <v>-4.587840319828274</v>
       </c>
       <c r="D84">
-        <v>1080.893075842925</v>
+        <v>1572.084159680172</v>
       </c>
       <c r="E84">
         <v>561.2719999999999</v>
@@ -8169,45 +8297,45 @@
         <v>276.125</v>
       </c>
       <c r="M84">
-        <v>174.3022504</v>
+        <v>134.5428776</v>
       </c>
       <c r="N84">
-        <v>101.8227496</v>
+        <v>141.5821224</v>
       </c>
       <c r="O84">
-        <v>25.39459375023999</v>
+        <v>35.31058132656</v>
       </c>
       <c r="P84">
-        <v>76.42815584975999</v>
+        <v>106.27154107344</v>
       </c>
       <c r="Q84">
-        <v>290.42815584976</v>
+        <v>320.2715410734401</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1637189636997481</v>
+        <v>0.1636431522903268</v>
       </c>
       <c r="T84">
         <v>2.721550861208472</v>
       </c>
       <c r="U84">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V84">
         <v>0.2494</v>
       </c>
       <c r="W84">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y84">
-        <v>1.584173465152232</v>
+        <v>2.052319713429409</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8218,13 +8346,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09012327185722332</v>
+        <v>0.07615451338618015</v>
       </c>
       <c r="C85">
-        <v>-522.6081454953912</v>
+        <v>-28.5360637820479</v>
       </c>
       <c r="D85">
-        <v>1075.709854504609</v>
+        <v>1569.781936217952</v>
       </c>
       <c r="E85">
         <v>582.9180000000001</v>
@@ -8251,45 +8379,45 @@
         <v>276.125</v>
       </c>
       <c r="M85">
-        <v>176.4278876</v>
+        <v>136.1836444</v>
       </c>
       <c r="N85">
-        <v>99.69711239999998</v>
+        <v>139.9413556</v>
       </c>
       <c r="O85">
-        <v>24.86445983256</v>
+        <v>34.90137408664</v>
       </c>
       <c r="P85">
-        <v>74.83265256743998</v>
+        <v>105.03998151336</v>
       </c>
       <c r="Q85">
-        <v>288.83265256744</v>
+        <v>319.03998151336</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1702639309248432</v>
+        <v>0.1701839116834127</v>
       </c>
       <c r="T85">
         <v>2.872607660125005</v>
       </c>
       <c r="U85">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V85">
         <v>0.2494</v>
       </c>
       <c r="W85">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y85">
-        <v>1.565087037861241</v>
+        <v>2.027592969894114</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8300,13 +8428,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.09033581584849201</v>
+        <v>0.07619896576010148</v>
       </c>
       <c r="C86">
-        <v>-549.3878937285269</v>
+        <v>-52.47755416663472</v>
       </c>
       <c r="D86">
-        <v>1070.576106271473</v>
+        <v>1567.486445833365</v>
       </c>
       <c r="E86">
         <v>604.5639999999999</v>
@@ -8333,45 +8461,45 @@
         <v>276.125</v>
       </c>
       <c r="M86">
-        <v>178.5535248</v>
+        <v>137.8244112</v>
       </c>
       <c r="N86">
-        <v>97.57147519999998</v>
+        <v>138.3005888</v>
       </c>
       <c r="O86">
-        <v>24.33432591488</v>
+        <v>34.49216684672</v>
       </c>
       <c r="P86">
-        <v>73.23714928511998</v>
+        <v>103.80842195328</v>
       </c>
       <c r="Q86">
-        <v>287.23714928512</v>
+        <v>317.80842195328</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1776270190530751</v>
+        <v>0.1775422660006342</v>
       </c>
       <c r="T86">
         <v>3.042546558906102</v>
       </c>
       <c r="U86">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V86">
         <v>0.2494</v>
       </c>
       <c r="W86">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y86">
-        <v>1.546455049315274</v>
+        <v>2.003454958347756</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8382,13 +8510,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.0905483598397607</v>
+        <v>0.08530316013402281</v>
       </c>
       <c r="C87">
-        <v>-576.118873812683</v>
+        <v>-435.3782293100335</v>
       </c>
       <c r="D87">
-        <v>1065.491126187317</v>
+        <v>1206.231770689966</v>
       </c>
       <c r="E87">
         <v>626.2099999999998</v>
@@ -8415,37 +8543,37 @@
         <v>276.125</v>
       </c>
       <c r="M87">
-        <v>180.679162</v>
+        <v>165.5919</v>
       </c>
       <c r="N87">
-        <v>95.44583800000001</v>
+        <v>110.5331</v>
       </c>
       <c r="O87">
-        <v>23.8041919972</v>
+        <v>27.56695514</v>
       </c>
       <c r="P87">
-        <v>71.6416460028</v>
+        <v>82.96614485999999</v>
       </c>
       <c r="Q87">
-        <v>285.6416460028</v>
+        <v>296.96614486</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.1859718522650713</v>
+        <v>0.1858817342268187</v>
       </c>
       <c r="T87">
         <v>3.235143977524682</v>
       </c>
       <c r="U87">
-        <v>0.09820000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V87">
         <v>0.2494</v>
       </c>
       <c r="W87">
-        <v>0.07370892</v>
+        <v>0.067554</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.5282614604998</v>
+        <v>1.667503060234226</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8464,13 +8592,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.09076090383102939</v>
+        <v>0.08545419770794414</v>
       </c>
       <c r="C88">
-        <v>-602.8017773738816</v>
+        <v>-461.6186059652782</v>
       </c>
       <c r="D88">
-        <v>1060.454222626118</v>
+        <v>1201.637394034722</v>
       </c>
       <c r="E88">
         <v>647.8559999999998</v>
@@ -8497,37 +8625,37 @@
         <v>276.125</v>
       </c>
       <c r="M88">
-        <v>182.8047992</v>
+        <v>167.54004</v>
       </c>
       <c r="N88">
-        <v>93.32020080000001</v>
+        <v>108.58496</v>
       </c>
       <c r="O88">
-        <v>23.27405807952</v>
+        <v>27.081089024</v>
       </c>
       <c r="P88">
-        <v>70.04614272048001</v>
+        <v>81.503870976</v>
       </c>
       <c r="Q88">
-        <v>284.04614272048</v>
+        <v>295.503870976</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.1955088045073528</v>
+        <v>0.1954125550567438</v>
       </c>
       <c r="T88">
         <v>3.455255313088773</v>
       </c>
       <c r="U88">
-        <v>0.09820000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V88">
         <v>0.2494</v>
       </c>
       <c r="W88">
-        <v>0.07370892</v>
+        <v>0.067554</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.510490978400965</v>
+        <v>1.648113489766386</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8546,13 +8674,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1379649270352246</v>
+        <v>0.08560523528186548</v>
       </c>
       <c r="C89">
-        <v>-1167.579610079597</v>
+        <v>-487.8241166789569</v>
       </c>
       <c r="D89">
-        <v>517.3223899204029</v>
+        <v>1197.077883321043</v>
       </c>
       <c r="E89">
         <v>669.502</v>
@@ -8579,45 +8707,45 @@
         <v>276.125</v>
       </c>
       <c r="M89">
-        <v>308.0918472</v>
+        <v>169.48818</v>
       </c>
       <c r="N89">
-        <v>-31.96684720000002</v>
+        <v>106.63682</v>
       </c>
       <c r="O89">
-        <v>-7.972531691680005</v>
+        <v>26.59522290799999</v>
       </c>
       <c r="P89">
-        <v>-23.99431550832001</v>
+        <v>80.04159709199998</v>
       </c>
       <c r="Q89">
-        <v>190.00568449168</v>
+        <v>294.041597092</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2111337282441489</v>
+        <v>0.2064096560143497</v>
       </c>
       <c r="T89">
-        <v>3.815876059048442</v>
+        <v>3.709229931047339</v>
       </c>
       <c r="U89">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V89">
-        <v>0.2235228735387322</v>
+        <v>0.2494</v>
       </c>
       <c r="W89">
-        <v>0.1270316578890634</v>
+        <v>0.067554</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.8962424760975628</v>
+        <v>1.629169656550681</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8628,13 +8756,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1391429270352246</v>
+        <v>0.0857562728557868</v>
       </c>
       <c r="C90">
-        <v>-1195.754286591919</v>
+        <v>-513.9951568383394</v>
       </c>
       <c r="D90">
-        <v>510.7937134080811</v>
+        <v>1192.552843161661</v>
       </c>
       <c r="E90">
         <v>691.1479999999999</v>
@@ -8661,45 +8789,45 @@
         <v>276.125</v>
       </c>
       <c r="M90">
-        <v>311.6331328000001</v>
+        <v>171.43632</v>
       </c>
       <c r="N90">
-        <v>-35.50813280000006</v>
+        <v>104.68868</v>
       </c>
       <c r="O90">
-        <v>-8.855728320320015</v>
+        <v>26.109356792</v>
       </c>
       <c r="P90">
-        <v>-26.65240447968004</v>
+        <v>78.57932320799998</v>
       </c>
       <c r="Q90">
-        <v>187.34759552032</v>
+        <v>292.579323208</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2249115389311614</v>
+        <v>0.2192396071315567</v>
       </c>
       <c r="T90">
-        <v>4.133865730635812</v>
+        <v>4.005533651999</v>
       </c>
       <c r="U90">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V90">
-        <v>0.2209828408848829</v>
+        <v>0.2494</v>
       </c>
       <c r="W90">
-        <v>0.1274472072312332</v>
+        <v>0.067554</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.8860579025055449</v>
+        <v>1.610656364998968</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8710,13 +8838,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1403209270352246</v>
+        <v>0.08590731042970813</v>
       </c>
       <c r="C91">
-        <v>-1223.766231290816</v>
+        <v>-540.1321158748422</v>
       </c>
       <c r="D91">
-        <v>504.4277687091841</v>
+        <v>1188.061884125158</v>
       </c>
       <c r="E91">
         <v>712.7939999999999</v>
@@ -8743,45 +8871,45 @@
         <v>276.125</v>
       </c>
       <c r="M91">
-        <v>315.1744184</v>
+        <v>173.38446</v>
       </c>
       <c r="N91">
-        <v>-39.04941840000004</v>
+        <v>102.74054</v>
       </c>
       <c r="O91">
-        <v>-9.73892494896001</v>
+        <v>25.623490676</v>
       </c>
       <c r="P91">
-        <v>-29.31049345104002</v>
+        <v>77.11704932399999</v>
       </c>
       <c r="Q91">
-        <v>184.68950654896</v>
+        <v>291.117049324</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2411944061067215</v>
+        <v>0.2344022766337103</v>
       </c>
       <c r="T91">
-        <v>4.509671706148159</v>
+        <v>4.355710776760053</v>
       </c>
       <c r="U91">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V91">
-        <v>0.2184998876165135</v>
+        <v>0.2494</v>
       </c>
       <c r="W91">
-        <v>0.1278534183859384</v>
+        <v>0.067554</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.8761021957358198</v>
+        <v>1.59255910247089</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8792,13 +8920,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1414989270352246</v>
+        <v>0.08605834800362946</v>
       </c>
       <c r="C92">
-        <v>-1251.621453587746</v>
+        <v>-566.2353773757488</v>
       </c>
       <c r="D92">
-        <v>498.2185464122538</v>
+        <v>1183.604622624251</v>
       </c>
       <c r="E92">
         <v>734.4399999999998</v>
@@ -8825,45 +8953,45 @@
         <v>276.125</v>
       </c>
       <c r="M92">
-        <v>318.715704</v>
+        <v>175.3326</v>
       </c>
       <c r="N92">
-        <v>-42.59070400000002</v>
+        <v>100.7924</v>
       </c>
       <c r="O92">
-        <v>-10.62212157760001</v>
+        <v>25.13762456</v>
       </c>
       <c r="P92">
-        <v>-31.96858242240001</v>
+        <v>75.65477543999998</v>
       </c>
       <c r="Q92">
-        <v>182.0314175776</v>
+        <v>289.65477544</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2607338467173937</v>
+        <v>0.2525974800362946</v>
       </c>
       <c r="T92">
-        <v>4.960638876762977</v>
+        <v>4.775923326473317</v>
       </c>
       <c r="U92">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V92">
-        <v>0.2160721110874411</v>
+        <v>0.2494</v>
       </c>
       <c r="W92">
-        <v>0.1282506026260947</v>
+        <v>0.067554</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.8663677268943107</v>
+        <v>1.574864001332325</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8874,13 +9002,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1426769270352246</v>
+        <v>0.08620938557755078</v>
       </c>
       <c r="C93">
-        <v>-1279.325670602209</v>
+        <v>-592.3053191934275</v>
       </c>
       <c r="D93">
-        <v>492.1603293977914</v>
+        <v>1179.180680806573</v>
       </c>
       <c r="E93">
         <v>756.086</v>
@@ -8907,45 +9035,45 @@
         <v>276.125</v>
       </c>
       <c r="M93">
-        <v>322.2569896000001</v>
+        <v>177.28074</v>
       </c>
       <c r="N93">
-        <v>-46.13198960000005</v>
+        <v>98.84425999999996</v>
       </c>
       <c r="O93">
-        <v>-11.50531820624001</v>
+        <v>24.65175844399999</v>
       </c>
       <c r="P93">
-        <v>-34.62667139376004</v>
+        <v>74.19250155599997</v>
       </c>
       <c r="Q93">
-        <v>179.37332860624</v>
+        <v>288.192501556</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.2846153852415485</v>
+        <v>0.2748360619727866</v>
       </c>
       <c r="T93">
-        <v>5.511820974181084</v>
+        <v>5.289516442789529</v>
       </c>
       <c r="U93">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V93">
-        <v>0.2136976922842824</v>
+        <v>0.2494</v>
       </c>
       <c r="W93">
-        <v>0.1286390575422914</v>
+        <v>0.067554</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.8568472024229445</v>
+        <v>1.557557803515486</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8956,13 +9084,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.1438549270352246</v>
+        <v>0.08636042315147213</v>
       </c>
       <c r="C94">
-        <v>-1306.884324719246</v>
+        <v>-618.3423135521116</v>
       </c>
       <c r="D94">
-        <v>486.2476752807543</v>
+        <v>1174.789686447888</v>
       </c>
       <c r="E94">
         <v>777.732</v>
@@ -8989,45 +9117,45 @@
         <v>276.125</v>
       </c>
       <c r="M94">
-        <v>325.7982752</v>
+        <v>179.22888</v>
       </c>
       <c r="N94">
-        <v>-49.67327520000003</v>
+        <v>96.89611999999997</v>
       </c>
       <c r="O94">
-        <v>-12.38851483488001</v>
+        <v>24.16589232799999</v>
       </c>
       <c r="P94">
-        <v>-37.28476036512002</v>
+        <v>72.73022767199997</v>
       </c>
       <c r="Q94">
-        <v>176.71523963488</v>
+        <v>286.730227672</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3144673083967422</v>
+        <v>0.3026342893934016</v>
       </c>
       <c r="T94">
-        <v>6.200798595953723</v>
+        <v>5.931507838184796</v>
       </c>
       <c r="U94">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V94">
-        <v>0.2113748912811924</v>
+        <v>0.2494</v>
       </c>
       <c r="W94">
-        <v>0.129019067786397</v>
+        <v>0.067554</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.8475336458748692</v>
+        <v>1.540627827390318</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9038,13 +9166,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1450329270352246</v>
+        <v>0.08651146072539345</v>
       </c>
       <c r="C95">
-        <v>-1334.302599896389</v>
+        <v>-644.3467271522945</v>
       </c>
       <c r="D95">
-        <v>480.4754001036106</v>
+        <v>1170.431272847705</v>
       </c>
       <c r="E95">
         <v>799.3779999999999</v>
@@ -9071,45 +9199,45 @@
         <v>276.125</v>
       </c>
       <c r="M95">
-        <v>329.3395608</v>
+        <v>181.17702</v>
       </c>
       <c r="N95">
-        <v>-53.21456080000002</v>
+        <v>94.94797999999997</v>
       </c>
       <c r="O95">
-        <v>-13.27171146352</v>
+        <v>23.68002621199999</v>
       </c>
       <c r="P95">
-        <v>-39.94284933648001</v>
+        <v>71.26795378799997</v>
       </c>
       <c r="Q95">
-        <v>174.05715066352</v>
+        <v>285.267953788</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3528483524534197</v>
+        <v>0.3383748675056209</v>
       </c>
       <c r="T95">
-        <v>7.086626966804254</v>
+        <v>6.756925346550137</v>
       </c>
       <c r="U95">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V95">
-        <v>0.2091020429878462</v>
+        <v>0.2494</v>
       </c>
       <c r="W95">
-        <v>0.1293909057671884</v>
+        <v>0.067554</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.838420380865462</v>
+        <v>1.524061936773217</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9120,13 +9248,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1462109270352246</v>
+        <v>0.08666249829931477</v>
       </c>
       <c r="C96">
-        <v>-1361.585436822748</v>
+        <v>-670.3189212728221</v>
       </c>
       <c r="D96">
-        <v>474.838563177252</v>
+        <v>1166.105078727178</v>
       </c>
       <c r="E96">
         <v>821.0239999999999</v>
@@ -9153,45 +9281,45 @@
         <v>276.125</v>
       </c>
       <c r="M96">
-        <v>332.8808464000001</v>
+        <v>183.12516</v>
       </c>
       <c r="N96">
-        <v>-56.75584640000005</v>
+        <v>92.99983999999998</v>
       </c>
       <c r="O96">
-        <v>-14.15490809216001</v>
+        <v>23.19416009599999</v>
       </c>
       <c r="P96">
-        <v>-42.60093830784004</v>
+        <v>69.80567990399999</v>
       </c>
       <c r="Q96">
-        <v>171.39906169216</v>
+        <v>283.805679904</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4040230778623231</v>
+        <v>0.3860289716552466</v>
       </c>
       <c r="T96">
-        <v>8.267731461271632</v>
+        <v>7.857482024370592</v>
       </c>
       <c r="U96">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V96">
-        <v>0.2068775531688266</v>
+        <v>0.2494</v>
       </c>
       <c r="W96">
-        <v>0.12975483230158</v>
+        <v>0.067554</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.829501015111574</v>
+        <v>1.507848511913928</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9202,13 +9330,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1473889270352245</v>
+        <v>0.1308216841750686</v>
       </c>
       <c r="C97">
-        <v>-1388.737547023408</v>
+        <v>-1297.625129275076</v>
       </c>
       <c r="D97">
-        <v>469.3324529765915</v>
+        <v>560.4448707249237</v>
       </c>
       <c r="E97">
         <v>842.6699999999998</v>
@@ -9235,37 +9363,37 @@
         <v>276.125</v>
       </c>
       <c r="M97">
-        <v>336.422132</v>
+        <v>301.875116</v>
       </c>
       <c r="N97">
-        <v>-60.29713200000003</v>
+        <v>-25.75011599999999</v>
       </c>
       <c r="O97">
-        <v>-15.03810472080001</v>
+        <v>-6.422078930399998</v>
       </c>
       <c r="P97">
-        <v>-45.25902727920003</v>
+        <v>-19.32803706959999</v>
       </c>
       <c r="Q97">
-        <v>168.7409727208</v>
+        <v>194.6719629304</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.4756676934347879</v>
+        <v>0.4635228362316688</v>
       </c>
       <c r="T97">
-        <v>9.921277753525965</v>
+        <v>9.647178665858405</v>
       </c>
       <c r="U97">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2046998947144179</v>
+        <v>0.2281260407035339</v>
       </c>
       <c r="W97">
-        <v>0.1301110972247213</v>
+        <v>0.1133110972247212</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8207694254788207</v>
+        <v>0.9146994414736722</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9284,13 +9412,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.1485669270352245</v>
+        <v>0.1318316841750686</v>
       </c>
       <c r="C98">
-        <v>-1415.763425993779</v>
+        <v>-1325.850674065578</v>
       </c>
       <c r="D98">
-        <v>463.9525740062209</v>
+        <v>553.865325934422</v>
       </c>
       <c r="E98">
         <v>864.3159999999996</v>
@@ -9317,37 +9445,37 @@
         <v>276.125</v>
       </c>
       <c r="M98">
-        <v>339.9634176</v>
+        <v>305.0527488</v>
       </c>
       <c r="N98">
-        <v>-63.83841760000001</v>
+        <v>-28.92774879999996</v>
       </c>
       <c r="O98">
-        <v>-15.92130134944</v>
+        <v>-7.21458055071999</v>
       </c>
       <c r="P98">
-        <v>-47.91711625056001</v>
+        <v>-21.71316824927997</v>
       </c>
       <c r="Q98">
-        <v>166.08288374944</v>
+        <v>192.2868317507201</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.5831346167934836</v>
+        <v>0.5679535452895849</v>
       </c>
       <c r="T98">
-        <v>12.40159719190743</v>
+        <v>12.05897333232298</v>
       </c>
       <c r="U98">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2025676041444761</v>
+        <v>0.2257497277795387</v>
       </c>
       <c r="W98">
-        <v>0.1304599399619637</v>
+        <v>0.1136599399619637</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8122197439634163</v>
+        <v>0.9051713222916549</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9366,13 +9494,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1497449270352245</v>
+        <v>0.1328416841750686</v>
       </c>
       <c r="C99">
-        <v>-1442.66736544083</v>
+        <v>-1353.923525573513</v>
       </c>
       <c r="D99">
-        <v>458.6946345591701</v>
+        <v>547.4384744264868</v>
       </c>
       <c r="E99">
         <v>885.9619999999998</v>
@@ -9399,37 +9527,37 @@
         <v>276.125</v>
       </c>
       <c r="M99">
-        <v>343.5047032</v>
+        <v>308.2303816</v>
       </c>
       <c r="N99">
-        <v>-67.37970319999999</v>
+        <v>-32.10538159999999</v>
       </c>
       <c r="O99">
-        <v>-16.80449797808</v>
+        <v>-8.007082171039997</v>
       </c>
       <c r="P99">
-        <v>-50.57520522191999</v>
+        <v>-24.09829942895999</v>
       </c>
       <c r="Q99">
-        <v>163.42479477808</v>
+        <v>189.90170057104</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.7622461557246449</v>
+        <v>0.7420047270527798</v>
       </c>
       <c r="T99">
-        <v>16.53546292254324</v>
+        <v>16.07863110976397</v>
       </c>
       <c r="U99">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2004792783285536</v>
+        <v>0.2234224109983064</v>
       </c>
       <c r="W99">
-        <v>0.1308015900654486</v>
+        <v>0.1140015900654486</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8038463445411131</v>
+        <v>0.895839659175246</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9448,13 +9576,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2033340336826368</v>
+        <v>0.1338516841750686</v>
       </c>
       <c r="C100">
-        <v>-1620.34971590658</v>
+        <v>-1381.848938220197</v>
       </c>
       <c r="D100">
-        <v>302.6582840934202</v>
+        <v>541.1590617798028</v>
       </c>
       <c r="E100">
         <v>907.6079999999999</v>
@@ -9481,45 +9609,45 @@
         <v>276.125</v>
       </c>
       <c r="M100">
-        <v>457.7782664000001</v>
+        <v>311.4080144</v>
       </c>
       <c r="N100">
-        <v>-181.6532664000001</v>
+        <v>-35.28301440000001</v>
       </c>
       <c r="O100">
-        <v>-45.30432464016002</v>
+        <v>-8.799583791360003</v>
       </c>
       <c r="P100">
-        <v>-136.34894175984</v>
+        <v>-26.48343060864001</v>
       </c>
       <c r="Q100">
-        <v>77.65105824015998</v>
+        <v>187.51656939136</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.183224565957578</v>
+        <v>1.09010709057917</v>
       </c>
       <c r="T100">
-        <v>26.25157743858406</v>
+        <v>24.11794666464596</v>
       </c>
       <c r="U100">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1504343479247358</v>
+        <v>0.2211425904779155</v>
       </c>
       <c r="W100">
-        <v>0.183336267717842</v>
+        <v>0.114336267717842</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.6031850357848267</v>
+        <v>0.8866984381632537</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9530,13 +9658,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2050340336826368</v>
+        <v>0.1348616841750686</v>
       </c>
       <c r="C101">
-        <v>-1645.226928927184</v>
+        <v>-1409.631928076836</v>
       </c>
       <c r="D101">
-        <v>299.4270710728152</v>
+        <v>535.0220719231633</v>
       </c>
       <c r="E101">
         <v>929.2539999999997</v>
@@ -9563,45 +9691,45 @@
         <v>276.125</v>
       </c>
       <c r="M101">
-        <v>462.4494732</v>
+        <v>314.5856472</v>
       </c>
       <c r="N101">
-        <v>-186.3244732</v>
+        <v>-38.46064719999998</v>
       </c>
       <c r="O101">
-        <v>-46.46932361608</v>
+        <v>-9.592085411679996</v>
       </c>
       <c r="P101">
-        <v>-139.85514958392</v>
+        <v>-28.86856178831999</v>
       </c>
       <c r="Q101">
-        <v>74.14485041608003</v>
+        <v>185.13143821168</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.320649131915156</v>
+        <v>2.134414181158339</v>
       </c>
       <c r="T101">
-        <v>52.50315487716811</v>
+        <v>48.23589332929192</v>
       </c>
       <c r="U101">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V101">
-        <v>0.1489148090568092</v>
+        <v>0.2189088269377345</v>
       </c>
       <c r="W101">
-        <v>0.1836641842055406</v>
+        <v>0.1146641842055406</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.5970922576455862</v>
+        <v>0.8777418882828167</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/luxembourg/luxembourg_food_processing.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_food_processing.xlsx
@@ -1400,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1537,22 +1537,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07246496635070977</v>
+        <v>0.07231801572463109</v>
       </c>
       <c r="C2">
-        <v>1985.287696500253</v>
+        <v>1973.544359034378</v>
       </c>
       <c r="D2">
-        <v>1786.987696500253</v>
+        <v>1796.890359034378</v>
       </c>
       <c r="E2">
-        <v>-1213.7</v>
+        <v>-1192.054</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>21.646</v>
       </c>
       <c r="G2">
         <v>198.3</v>
@@ -1573,28 +1573,28 @@
         <v>276.125</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.0887938</v>
       </c>
       <c r="N2">
-        <v>276.125</v>
+        <v>275.0362062</v>
       </c>
       <c r="O2">
-        <v>68.86557500000001</v>
+        <v>68.59402982627999</v>
       </c>
       <c r="P2">
-        <v>207.259425</v>
+        <v>206.44217637372</v>
       </c>
       <c r="Q2">
-        <v>421.259425</v>
+        <v>420.44217637372</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07246496635070977</v>
+        <v>0.07266713527740515</v>
       </c>
       <c r="T2">
-        <v>0.6158190843120042</v>
+        <v>0.6204881126421515</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>253.60633023443</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07231801572463109</v>
+        <v>0.07217106509855244</v>
       </c>
       <c r="C3">
-        <v>1973.544359034378</v>
+        <v>1961.911385139618</v>
       </c>
       <c r="D3">
-        <v>1796.890359034378</v>
+        <v>1806.903385139618</v>
       </c>
       <c r="E3">
-        <v>-1192.054</v>
+        <v>-1170.408</v>
       </c>
       <c r="F3">
-        <v>21.646</v>
+        <v>43.292</v>
       </c>
       <c r="G3">
         <v>198.3</v>
@@ -1655,28 +1655,28 @@
         <v>276.125</v>
       </c>
       <c r="M3">
-        <v>1.0887938</v>
+        <v>2.1775876</v>
       </c>
       <c r="N3">
-        <v>275.0362062</v>
+        <v>273.9474124</v>
       </c>
       <c r="O3">
-        <v>68.59402982627999</v>
+        <v>68.32248465256001</v>
       </c>
       <c r="P3">
-        <v>206.44217637372</v>
+        <v>205.62492774744</v>
       </c>
       <c r="Q3">
-        <v>420.44217637372</v>
+        <v>419.62492774744</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07266713527740515</v>
+        <v>0.07287343010056371</v>
       </c>
       <c r="T3">
-        <v>0.6204881126421515</v>
+        <v>0.6252524272647509</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>253.60633023443</v>
+        <v>126.803165117215</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1701,22 +1701,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07217106509855244</v>
+        <v>0.07202411447247375</v>
       </c>
       <c r="C4">
-        <v>1961.911385139618</v>
+        <v>1950.390630130775</v>
       </c>
       <c r="D4">
-        <v>1806.903385139618</v>
+        <v>1817.028630130775</v>
       </c>
       <c r="E4">
-        <v>-1170.408</v>
+        <v>-1148.762</v>
       </c>
       <c r="F4">
-        <v>43.292</v>
+        <v>64.93799999999999</v>
       </c>
       <c r="G4">
         <v>198.3</v>
@@ -1737,28 +1737,28 @@
         <v>276.125</v>
       </c>
       <c r="M4">
-        <v>2.1775876</v>
+        <v>3.2663814</v>
       </c>
       <c r="N4">
-        <v>273.9474124</v>
+        <v>272.8586186</v>
       </c>
       <c r="O4">
-        <v>68.32248465256001</v>
+        <v>68.05093947884001</v>
       </c>
       <c r="P4">
-        <v>205.62492774744</v>
+        <v>204.80767912116</v>
       </c>
       <c r="Q4">
-        <v>419.62492774744</v>
+        <v>418.80767912116</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07287343010056371</v>
+        <v>0.07308397842523068</v>
       </c>
       <c r="T4">
-        <v>0.6252524272647509</v>
+        <v>0.6301149751785378</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>126.803165117215</v>
+        <v>84.53544341147669</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07202411447247375</v>
+        <v>0.07187716384639509</v>
       </c>
       <c r="C5">
-        <v>1950.390630130775</v>
+        <v>1938.983991143092</v>
       </c>
       <c r="D5">
-        <v>1817.028630130775</v>
+        <v>1827.267991143093</v>
       </c>
       <c r="E5">
-        <v>-1148.762</v>
+        <v>-1127.116</v>
       </c>
       <c r="F5">
-        <v>64.93799999999999</v>
+        <v>86.584</v>
       </c>
       <c r="G5">
         <v>198.3</v>
@@ -1819,28 +1819,28 @@
         <v>276.125</v>
       </c>
       <c r="M5">
-        <v>3.2663814</v>
+        <v>4.355175200000001</v>
       </c>
       <c r="N5">
-        <v>272.8586186</v>
+        <v>271.7698248</v>
       </c>
       <c r="O5">
-        <v>68.05093947884001</v>
+        <v>67.77939430511999</v>
       </c>
       <c r="P5">
-        <v>204.80767912116</v>
+        <v>203.99043049488</v>
       </c>
       <c r="Q5">
-        <v>418.80767912116</v>
+        <v>417.99043049488</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07308397842523068</v>
+        <v>0.07329891317332822</v>
       </c>
       <c r="T5">
-        <v>0.6301149751785378</v>
+        <v>0.635078826173862</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>84.53544341147669</v>
+        <v>63.4015825586075</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1865,22 +1865,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07187716384639509</v>
+        <v>0.07173021322031642</v>
       </c>
       <c r="C6">
-        <v>1938.983991143092</v>
+        <v>1927.693408317279</v>
       </c>
       <c r="D6">
-        <v>1827.267991143093</v>
+        <v>1837.623408317279</v>
       </c>
       <c r="E6">
-        <v>-1127.116</v>
+        <v>-1105.47</v>
       </c>
       <c r="F6">
-        <v>86.584</v>
+        <v>108.23</v>
       </c>
       <c r="G6">
         <v>198.3</v>
@@ -1901,28 +1901,28 @@
         <v>276.125</v>
       </c>
       <c r="M6">
-        <v>4.355175200000001</v>
+        <v>5.443969000000001</v>
       </c>
       <c r="N6">
-        <v>271.7698248</v>
+        <v>270.681031</v>
       </c>
       <c r="O6">
-        <v>67.77939430511999</v>
+        <v>67.50784913140001</v>
       </c>
       <c r="P6">
-        <v>203.99043049488</v>
+        <v>203.1731818686</v>
       </c>
       <c r="Q6">
-        <v>417.99043049488</v>
+        <v>417.1731818686001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07329891317332822</v>
+        <v>0.07351837286349097</v>
       </c>
       <c r="T6">
-        <v>0.635078826173862</v>
+        <v>0.6401471792954037</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>63.4015825586075</v>
+        <v>50.72126604688601</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07173021322031642</v>
+        <v>0.07158326259423775</v>
       </c>
       <c r="C7">
-        <v>1927.693408317279</v>
+        <v>1916.520866025048</v>
       </c>
       <c r="D7">
-        <v>1837.623408317279</v>
+        <v>1848.096866025048</v>
       </c>
       <c r="E7">
-        <v>-1105.47</v>
+        <v>-1083.824</v>
       </c>
       <c r="F7">
-        <v>108.23</v>
+        <v>129.876</v>
       </c>
       <c r="G7">
         <v>198.3</v>
@@ -1983,28 +1983,28 @@
         <v>276.125</v>
       </c>
       <c r="M7">
-        <v>5.443969000000001</v>
+        <v>6.5327628</v>
       </c>
       <c r="N7">
-        <v>270.681031</v>
+        <v>269.5922372</v>
       </c>
       <c r="O7">
-        <v>67.50784913140001</v>
+        <v>67.23630395768001</v>
       </c>
       <c r="P7">
-        <v>203.1731818686</v>
+        <v>202.35593324232</v>
       </c>
       <c r="Q7">
-        <v>417.1731818686001</v>
+        <v>416.35593324232</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07351837286349097</v>
+        <v>0.07374250190876357</v>
       </c>
       <c r="T7">
-        <v>0.6401471792954037</v>
+        <v>0.6453233697174034</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>50.72126604688601</v>
+        <v>42.26772170573834</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07158326259423775</v>
+        <v>0.0714363119681591</v>
       </c>
       <c r="C8">
-        <v>1916.520866025048</v>
+        <v>1905.468394136802</v>
       </c>
       <c r="D8">
-        <v>1848.096866025048</v>
+        <v>1858.690394136801</v>
       </c>
       <c r="E8">
-        <v>-1083.824</v>
+        <v>-1062.178</v>
       </c>
       <c r="F8">
-        <v>129.876</v>
+        <v>151.522</v>
       </c>
       <c r="G8">
         <v>198.3</v>
@@ -2065,28 +2065,28 @@
         <v>276.125</v>
       </c>
       <c r="M8">
-        <v>6.5327628</v>
+        <v>7.6215566</v>
       </c>
       <c r="N8">
-        <v>269.5922372</v>
+        <v>268.5034434</v>
       </c>
       <c r="O8">
-        <v>67.23630395768001</v>
+        <v>66.96475878395999</v>
       </c>
       <c r="P8">
-        <v>202.35593324232</v>
+        <v>201.53868461604</v>
       </c>
       <c r="Q8">
-        <v>416.35593324232</v>
+        <v>415.53868461604</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07374250190876357</v>
+        <v>0.07397145093350439</v>
       </c>
       <c r="T8">
-        <v>0.6453233697174034</v>
+        <v>0.6506108760624573</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>42.26772170573835</v>
+        <v>36.22947574777572</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2111,22 +2111,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07143631196815908</v>
+        <v>0.07128936134208042</v>
       </c>
       <c r="C9">
-        <v>1905.468394136803</v>
+        <v>1894.538069333179</v>
       </c>
       <c r="D9">
-        <v>1858.690394136802</v>
+        <v>1869.406069333179</v>
       </c>
       <c r="E9">
-        <v>-1062.178</v>
+        <v>-1040.532</v>
       </c>
       <c r="F9">
-        <v>151.522</v>
+        <v>173.168</v>
       </c>
       <c r="G9">
         <v>198.3</v>
@@ -2147,28 +2147,28 @@
         <v>276.125</v>
       </c>
       <c r="M9">
-        <v>7.621556600000002</v>
+        <v>8.710350400000001</v>
       </c>
       <c r="N9">
-        <v>268.5034434</v>
+        <v>267.4146496</v>
       </c>
       <c r="O9">
-        <v>66.96475878395999</v>
+        <v>66.69321361024001</v>
       </c>
       <c r="P9">
-        <v>201.53868461604</v>
+        <v>200.72143598976</v>
       </c>
       <c r="Q9">
-        <v>415.53868461604</v>
+        <v>414.72143598976</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07397145093350439</v>
+        <v>0.07420537711095697</v>
       </c>
       <c r="T9">
-        <v>0.6506108760624573</v>
+        <v>0.6560133281976207</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>36.22947574777572</v>
+        <v>31.70079127930376</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07128936134208042</v>
+        <v>0.07114241071600175</v>
       </c>
       <c r="C10">
-        <v>1894.538069333179</v>
+        <v>1883.732016462215</v>
       </c>
       <c r="D10">
-        <v>1869.406069333179</v>
+        <v>1880.246016462215</v>
       </c>
       <c r="E10">
-        <v>-1040.532</v>
+        <v>-1018.886</v>
       </c>
       <c r="F10">
-        <v>173.168</v>
+        <v>194.814</v>
       </c>
       <c r="G10">
         <v>198.3</v>
@@ -2229,28 +2229,28 @@
         <v>276.125</v>
       </c>
       <c r="M10">
-        <v>8.710350400000001</v>
+        <v>9.799144200000001</v>
       </c>
       <c r="N10">
-        <v>267.4146496</v>
+        <v>266.3258558</v>
       </c>
       <c r="O10">
-        <v>66.69321361024001</v>
+        <v>66.42166843652001</v>
       </c>
       <c r="P10">
-        <v>200.72143598976</v>
+        <v>199.90418736348</v>
       </c>
       <c r="Q10">
-        <v>414.72143598976</v>
+        <v>413.90418736348</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07420537711095697</v>
+        <v>0.07444444452307884</v>
       </c>
       <c r="T10">
-        <v>0.6560133281976207</v>
+        <v>0.6615345155445461</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>31.70079127930376</v>
+        <v>28.17848113715889</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2275,22 +2275,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07114241071600175</v>
+        <v>0.07099546008992308</v>
       </c>
       <c r="C11">
-        <v>1883.732016462215</v>
+        <v>1873.052409944013</v>
       </c>
       <c r="D11">
-        <v>1880.246016462215</v>
+        <v>1891.212409944013</v>
       </c>
       <c r="E11">
-        <v>-1018.886</v>
+        <v>-997.24</v>
       </c>
       <c r="F11">
-        <v>194.814</v>
+        <v>216.46</v>
       </c>
       <c r="G11">
         <v>198.3</v>
@@ -2311,28 +2311,28 @@
         <v>276.125</v>
       </c>
       <c r="M11">
-        <v>9.799144200000001</v>
+        <v>10.887938</v>
       </c>
       <c r="N11">
-        <v>266.3258558</v>
+        <v>265.237062</v>
       </c>
       <c r="O11">
-        <v>66.42166843652001</v>
+        <v>66.15012326279999</v>
       </c>
       <c r="P11">
-        <v>199.90418736348</v>
+        <v>199.0869387372</v>
       </c>
       <c r="Q11">
-        <v>413.90418736348</v>
+        <v>413.0869387372001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07444444452307884</v>
+        <v>0.07468882454435896</v>
       </c>
       <c r="T11">
-        <v>0.6615345155445461</v>
+        <v>0.6671783959436253</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>28.17848113715889</v>
+        <v>25.360633023443</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07099546008992308</v>
+        <v>0.07084850946384441</v>
       </c>
       <c r="C12">
-        <v>1873.052409944013</v>
+        <v>1862.501475224851</v>
       </c>
       <c r="D12">
-        <v>1891.212409944013</v>
+        <v>1902.30747522485</v>
       </c>
       <c r="E12">
-        <v>-997.24</v>
+        <v>-975.5940000000001</v>
       </c>
       <c r="F12">
-        <v>216.46</v>
+        <v>238.106</v>
       </c>
       <c r="G12">
         <v>198.3</v>
@@ -2393,28 +2393,28 @@
         <v>276.125</v>
       </c>
       <c r="M12">
-        <v>10.887938</v>
+        <v>11.9767318</v>
       </c>
       <c r="N12">
-        <v>265.237062</v>
+        <v>264.1482682</v>
       </c>
       <c r="O12">
-        <v>66.15012326279999</v>
+        <v>65.87857808908001</v>
       </c>
       <c r="P12">
-        <v>199.0869387372</v>
+        <v>198.26969011092</v>
       </c>
       <c r="Q12">
-        <v>413.0869387372001</v>
+        <v>412.26969011092</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07468882454435896</v>
+        <v>0.07493869625151056</v>
       </c>
       <c r="T12">
-        <v>0.6671783959436253</v>
+        <v>0.6729491051157176</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>25.360633023443</v>
+        <v>23.05512093040273</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2439,22 +2439,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07084850946384441</v>
+        <v>0.07070155883776574</v>
       </c>
       <c r="C13">
-        <v>1862.501475224851</v>
+        <v>1852.08149028277</v>
       </c>
       <c r="D13">
-        <v>1902.30747522485</v>
+        <v>1913.533490282769</v>
       </c>
       <c r="E13">
-        <v>-975.5940000000001</v>
+        <v>-953.9480000000001</v>
       </c>
       <c r="F13">
-        <v>238.106</v>
+        <v>259.752</v>
       </c>
       <c r="G13">
         <v>198.3</v>
@@ -2475,28 +2475,28 @@
         <v>276.125</v>
       </c>
       <c r="M13">
-        <v>11.9767318</v>
+        <v>13.0655256</v>
       </c>
       <c r="N13">
-        <v>264.1482682</v>
+        <v>263.0594744</v>
       </c>
       <c r="O13">
-        <v>65.87857808908001</v>
+        <v>65.60703291536001</v>
       </c>
       <c r="P13">
-        <v>198.26969011092</v>
+        <v>197.45244148464</v>
       </c>
       <c r="Q13">
-        <v>412.26969011092</v>
+        <v>411.45244148464</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07493869625151056</v>
+        <v>0.07519424686109742</v>
       </c>
       <c r="T13">
-        <v>0.6729491051157176</v>
+        <v>0.6788509667689937</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>23.05512093040273</v>
+        <v>21.13386085286917</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2521,22 +2521,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07070155883776574</v>
+        <v>0.07055460821168705</v>
       </c>
       <c r="C14">
-        <v>1852.08149028277</v>
+        <v>1841.794787186804</v>
       </c>
       <c r="D14">
-        <v>1913.533490282769</v>
+        <v>1924.892787186804</v>
       </c>
       <c r="E14">
-        <v>-953.9480000000001</v>
+        <v>-932.302</v>
       </c>
       <c r="F14">
-        <v>259.752</v>
+        <v>281.398</v>
       </c>
       <c r="G14">
         <v>198.3</v>
@@ -2557,28 +2557,28 @@
         <v>276.125</v>
       </c>
       <c r="M14">
-        <v>13.0655256</v>
+        <v>14.1543194</v>
       </c>
       <c r="N14">
-        <v>263.0594744</v>
+        <v>261.9706806</v>
       </c>
       <c r="O14">
-        <v>65.60703291536001</v>
+        <v>65.33548774163999</v>
       </c>
       <c r="P14">
-        <v>197.45244148464</v>
+        <v>196.63519285836</v>
       </c>
       <c r="Q14">
-        <v>411.45244148464</v>
+        <v>410.63519285836</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07519424686109742</v>
+        <v>0.07545567219734145</v>
       </c>
       <c r="T14">
-        <v>0.6788509667689937</v>
+        <v>0.684888503402805</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>21.13386085286917</v>
+        <v>19.50817924880231</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2603,22 +2603,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07055460821168705</v>
+        <v>0.07040765758560838</v>
       </c>
       <c r="C15">
-        <v>1841.794787186804</v>
+        <v>1831.643753712055</v>
       </c>
       <c r="D15">
-        <v>1924.892787186804</v>
+        <v>1936.387753712055</v>
       </c>
       <c r="E15">
-        <v>-932.302</v>
+        <v>-910.6559999999999</v>
       </c>
       <c r="F15">
-        <v>281.398</v>
+        <v>303.044</v>
       </c>
       <c r="G15">
         <v>198.3</v>
@@ -2639,28 +2639,28 @@
         <v>276.125</v>
       </c>
       <c r="M15">
-        <v>14.1543194</v>
+        <v>15.2431132</v>
       </c>
       <c r="N15">
-        <v>261.9706806</v>
+        <v>260.8818868</v>
       </c>
       <c r="O15">
-        <v>65.33548774163999</v>
+        <v>65.06394256792001</v>
       </c>
       <c r="P15">
-        <v>196.63519285836</v>
+        <v>195.81794423208</v>
       </c>
       <c r="Q15">
-        <v>410.63519285836</v>
+        <v>409.81794423208</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07545567219734145</v>
+        <v>0.07572317719256789</v>
       </c>
       <c r="T15">
-        <v>0.684888503402805</v>
+        <v>0.6910664478653096</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.50817924880231</v>
+        <v>18.11473787388786</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07040765758560838</v>
+        <v>0.07026070695952971</v>
       </c>
       <c r="C16">
-        <v>1831.643753712055</v>
+        <v>1821.630835013011</v>
       </c>
       <c r="D16">
-        <v>1936.387753712055</v>
+        <v>1948.020835013011</v>
       </c>
       <c r="E16">
-        <v>-910.6559999999999</v>
+        <v>-889.01</v>
       </c>
       <c r="F16">
-        <v>303.044</v>
+        <v>324.6900000000001</v>
       </c>
       <c r="G16">
         <v>198.3</v>
@@ -2721,28 +2721,28 @@
         <v>276.125</v>
       </c>
       <c r="M16">
-        <v>15.2431132</v>
+        <v>16.331907</v>
       </c>
       <c r="N16">
-        <v>260.8818868</v>
+        <v>259.793093</v>
       </c>
       <c r="O16">
-        <v>65.06394256792001</v>
+        <v>64.79239739420001</v>
       </c>
       <c r="P16">
-        <v>195.81794423208</v>
+        <v>195.0006956058</v>
       </c>
       <c r="Q16">
-        <v>409.81794423208</v>
+        <v>409.0006956058</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07572317719256789</v>
+        <v>0.07599697642297615</v>
       </c>
       <c r="T16">
-        <v>0.6910664478653096</v>
+        <v>0.6973897557269318</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.11473787388786</v>
+        <v>16.90708868229533</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07026070695952971</v>
+        <v>0.07011375633345104</v>
       </c>
       <c r="C17">
-        <v>1821.630835013011</v>
+        <v>1811.758535357519</v>
       </c>
       <c r="D17">
-        <v>1948.020835013011</v>
+        <v>1959.794535357519</v>
       </c>
       <c r="E17">
-        <v>-889.01</v>
+        <v>-867.364</v>
       </c>
       <c r="F17">
-        <v>324.69</v>
+        <v>346.336</v>
       </c>
       <c r="G17">
         <v>198.3</v>
@@ -2803,28 +2803,28 @@
         <v>276.125</v>
       </c>
       <c r="M17">
-        <v>16.331907</v>
+        <v>17.4207008</v>
       </c>
       <c r="N17">
-        <v>259.793093</v>
+        <v>258.7042992</v>
       </c>
       <c r="O17">
-        <v>64.79239739420001</v>
+        <v>64.52085222047999</v>
       </c>
       <c r="P17">
-        <v>195.0006956058</v>
+        <v>194.18344697952</v>
       </c>
       <c r="Q17">
-        <v>409.0006956058</v>
+        <v>408.18344697952</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07599697642297615</v>
+        <v>0.07627729468267982</v>
       </c>
       <c r="T17">
-        <v>0.6973897557269318</v>
+        <v>0.7038636185376403</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.90708868229534</v>
+        <v>15.85039563965188</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07011375633345104</v>
+        <v>0.06996680570737238</v>
       </c>
       <c r="C18">
-        <v>1811.758535357519</v>
+        <v>1802.029419924042</v>
       </c>
       <c r="D18">
-        <v>1959.794535357519</v>
+        <v>1971.711419924042</v>
       </c>
       <c r="E18">
-        <v>-867.364</v>
+        <v>-845.7180000000001</v>
       </c>
       <c r="F18">
-        <v>346.336</v>
+        <v>367.982</v>
       </c>
       <c r="G18">
         <v>198.3</v>
@@ -2885,28 +2885,28 @@
         <v>276.125</v>
       </c>
       <c r="M18">
-        <v>17.4207008</v>
+        <v>18.5094946</v>
       </c>
       <c r="N18">
-        <v>258.7042992</v>
+        <v>257.6155054</v>
       </c>
       <c r="O18">
-        <v>64.52085222047999</v>
+        <v>64.24930704676001</v>
       </c>
       <c r="P18">
-        <v>194.18344697952</v>
+        <v>193.36619835324</v>
       </c>
       <c r="Q18">
-        <v>408.18344697952</v>
+        <v>407.3661983532401</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07627729468267982</v>
+        <v>0.07656436759924383</v>
       </c>
       <c r="T18">
-        <v>0.7038636185376403</v>
+        <v>0.7104934780425829</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.85039563965188</v>
+        <v>14.91801942555471</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06996680570737238</v>
+        <v>0.06981985508129371</v>
       </c>
       <c r="C19">
-        <v>1802.029419924042</v>
+        <v>1792.446116664871</v>
       </c>
       <c r="D19">
-        <v>1971.711419924042</v>
+        <v>1983.774116664871</v>
       </c>
       <c r="E19">
-        <v>-845.7180000000001</v>
+        <v>-824.072</v>
       </c>
       <c r="F19">
-        <v>367.982</v>
+        <v>389.628</v>
       </c>
       <c r="G19">
         <v>198.3</v>
@@ -2967,28 +2967,28 @@
         <v>276.125</v>
       </c>
       <c r="M19">
-        <v>18.5094946</v>
+        <v>19.5982884</v>
       </c>
       <c r="N19">
-        <v>257.6155054</v>
+        <v>256.5267116</v>
       </c>
       <c r="O19">
-        <v>64.24930704676001</v>
+        <v>63.97776187304</v>
       </c>
       <c r="P19">
-        <v>193.36619835324</v>
+        <v>192.54894972696</v>
       </c>
       <c r="Q19">
-        <v>407.3661983532401</v>
+        <v>406.54894972696</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07656436759924383</v>
+        <v>0.07685844229426063</v>
       </c>
       <c r="T19">
-        <v>0.7104934780425829</v>
+        <v>0.7172850414378898</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.91801942555471</v>
+        <v>14.08924056857945</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3013,22 +3013,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06981985508129372</v>
+        <v>0.06967290445521504</v>
       </c>
       <c r="C20">
-        <v>1792.44611666487</v>
+        <v>1783.011318238162</v>
       </c>
       <c r="D20">
-        <v>1983.774116664869</v>
+        <v>1995.985318238162</v>
       </c>
       <c r="E20">
-        <v>-824.0720000000001</v>
+        <v>-802.426</v>
       </c>
       <c r="F20">
-        <v>389.628</v>
+        <v>411.274</v>
       </c>
       <c r="G20">
         <v>198.3</v>
@@ -3049,28 +3049,28 @@
         <v>276.125</v>
       </c>
       <c r="M20">
-        <v>19.5982884</v>
+        <v>20.6870822</v>
       </c>
       <c r="N20">
-        <v>256.5267116</v>
+        <v>255.4379178</v>
       </c>
       <c r="O20">
-        <v>63.97776187304</v>
+        <v>63.70621669932</v>
       </c>
       <c r="P20">
-        <v>192.54894972696</v>
+        <v>191.73170110068</v>
       </c>
       <c r="Q20">
-        <v>406.54894972696</v>
+        <v>405.73170110068</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07685844229426063</v>
+        <v>0.07715977809285807</v>
       </c>
       <c r="T20">
-        <v>0.7172850414378898</v>
+        <v>0.7242442977565376</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.08924056857945</v>
+        <v>13.34770159128579</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06967290445521504</v>
+        <v>0.06975113382913638</v>
       </c>
       <c r="C21">
-        <v>1783.011318238162</v>
+        <v>1754.846015940581</v>
       </c>
       <c r="D21">
-        <v>1995.985318238162</v>
+        <v>1989.466015940581</v>
       </c>
       <c r="E21">
-        <v>-802.426</v>
+        <v>-780.78</v>
       </c>
       <c r="F21">
-        <v>411.274</v>
+        <v>432.92</v>
       </c>
       <c r="G21">
         <v>198.3</v>
@@ -3131,45 +3131,45 @@
         <v>276.125</v>
       </c>
       <c r="M21">
-        <v>20.6870822</v>
+        <v>22.425256</v>
       </c>
       <c r="N21">
-        <v>255.4379178</v>
+        <v>253.699744</v>
       </c>
       <c r="O21">
-        <v>63.70621669932</v>
+        <v>63.27271615360001</v>
       </c>
       <c r="P21">
-        <v>191.73170110068</v>
+        <v>190.4270278464</v>
       </c>
       <c r="Q21">
-        <v>405.73170110068</v>
+        <v>404.4270278464001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07715977809285807</v>
+        <v>0.07746864728642047</v>
       </c>
       <c r="T21">
-        <v>0.7242442977565376</v>
+        <v>0.7313775354831518</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V21">
         <v>0.2494</v>
       </c>
       <c r="W21">
-        <v>0.03775518</v>
+        <v>0.03888108</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>13.34770159128579</v>
+        <v>12.31312587914269</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06975113382913638</v>
+        <v>0.06961544220305771</v>
       </c>
       <c r="C22">
-        <v>1754.846015940581</v>
+        <v>1744.535261216715</v>
       </c>
       <c r="D22">
-        <v>1989.466015940581</v>
+        <v>2000.801261216714</v>
       </c>
       <c r="E22">
-        <v>-780.78</v>
+        <v>-759.134</v>
       </c>
       <c r="F22">
-        <v>432.92</v>
+        <v>454.566</v>
       </c>
       <c r="G22">
         <v>198.3</v>
@@ -3213,28 +3213,28 @@
         <v>276.125</v>
       </c>
       <c r="M22">
-        <v>22.425256</v>
+        <v>23.5465188</v>
       </c>
       <c r="N22">
-        <v>253.699744</v>
+        <v>252.5784812</v>
       </c>
       <c r="O22">
-        <v>63.27271615360001</v>
+        <v>62.99307321128001</v>
       </c>
       <c r="P22">
-        <v>190.4270278464</v>
+        <v>189.58540798872</v>
       </c>
       <c r="Q22">
-        <v>404.4270278464001</v>
+        <v>403.58540798872</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07746864728642047</v>
+        <v>0.0777853359532376</v>
       </c>
       <c r="T22">
-        <v>0.7313775354831518</v>
+        <v>0.7386913615066422</v>
       </c>
       <c r="U22">
         <v>0.05180000000000001</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.31312587914269</v>
+        <v>11.72678655156447</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3259,22 +3259,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06961544220305771</v>
+        <v>0.06947975057697903</v>
       </c>
       <c r="C23">
-        <v>1744.535261216715</v>
+        <v>1734.35441477533</v>
       </c>
       <c r="D23">
-        <v>2000.801261216714</v>
+        <v>2012.26641477533</v>
       </c>
       <c r="E23">
-        <v>-759.134</v>
+        <v>-737.4880000000001</v>
       </c>
       <c r="F23">
-        <v>454.566</v>
+        <v>476.212</v>
       </c>
       <c r="G23">
         <v>198.3</v>
@@ -3295,28 +3295,28 @@
         <v>276.125</v>
       </c>
       <c r="M23">
-        <v>23.5465188</v>
+        <v>24.6677816</v>
       </c>
       <c r="N23">
-        <v>252.5784812</v>
+        <v>251.4572184</v>
       </c>
       <c r="O23">
-        <v>62.99307321128001</v>
+        <v>62.71343026896</v>
       </c>
       <c r="P23">
-        <v>189.58540798872</v>
+        <v>188.74378813104</v>
       </c>
       <c r="Q23">
-        <v>403.58540798872</v>
+        <v>402.74378813104</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0777853359532376</v>
+        <v>0.07811014484228081</v>
       </c>
       <c r="T23">
-        <v>0.7386913615066422</v>
+        <v>0.7461927215307348</v>
       </c>
       <c r="U23">
         <v>0.05180000000000001</v>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.72678655156447</v>
+        <v>11.19375079922063</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06947975057697903</v>
+        <v>0.06934405895090037</v>
       </c>
       <c r="C24">
-        <v>1734.35441477533</v>
+        <v>1724.305722720139</v>
       </c>
       <c r="D24">
-        <v>2012.26641477533</v>
+        <v>2023.863722720138</v>
       </c>
       <c r="E24">
-        <v>-737.4880000000001</v>
+        <v>-715.8420000000001</v>
       </c>
       <c r="F24">
-        <v>476.212</v>
+        <v>497.858</v>
       </c>
       <c r="G24">
         <v>198.3</v>
@@ -3377,28 +3377,28 @@
         <v>276.125</v>
       </c>
       <c r="M24">
-        <v>24.6677816</v>
+        <v>25.7890444</v>
       </c>
       <c r="N24">
-        <v>251.4572184</v>
+        <v>250.3359556</v>
       </c>
       <c r="O24">
-        <v>62.71343026896</v>
+        <v>62.43378732664</v>
       </c>
       <c r="P24">
-        <v>188.74378813104</v>
+        <v>187.90216827336</v>
       </c>
       <c r="Q24">
-        <v>402.74378813104</v>
+        <v>401.9021682733601</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07811014484228081</v>
+        <v>0.07844339032584463</v>
       </c>
       <c r="T24">
-        <v>0.7461927215307348</v>
+        <v>0.7538889220749337</v>
       </c>
       <c r="U24">
         <v>0.05180000000000001</v>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.19375079922063</v>
+        <v>10.70706598186321</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3423,22 +3423,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06934405895090037</v>
+        <v>0.06920836732482169</v>
       </c>
       <c r="C25">
-        <v>1724.305722720139</v>
+        <v>1714.391483234951</v>
       </c>
       <c r="D25">
-        <v>2023.863722720138</v>
+        <v>2035.59548323495</v>
       </c>
       <c r="E25">
-        <v>-715.8420000000001</v>
+        <v>-694.196</v>
       </c>
       <c r="F25">
-        <v>497.858</v>
+        <v>519.504</v>
       </c>
       <c r="G25">
         <v>198.3</v>
@@ -3459,28 +3459,28 @@
         <v>276.125</v>
       </c>
       <c r="M25">
-        <v>25.7890444</v>
+        <v>26.91030720000001</v>
       </c>
       <c r="N25">
-        <v>250.3359556</v>
+        <v>249.2146928</v>
       </c>
       <c r="O25">
-        <v>62.43378732664</v>
+        <v>62.15414438432</v>
       </c>
       <c r="P25">
-        <v>187.90216827336</v>
+        <v>187.06054841568</v>
       </c>
       <c r="Q25">
-        <v>401.9021682733601</v>
+        <v>401.06054841568</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07844339032584463</v>
+        <v>0.07878540542739695</v>
       </c>
       <c r="T25">
-        <v>0.7538889220749337</v>
+        <v>0.7617876542124011</v>
       </c>
       <c r="U25">
         <v>0.05180000000000001</v>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.70706598186321</v>
+        <v>10.26093823261891</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3505,22 +3505,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06920836732482169</v>
+        <v>0.06907267569874302</v>
       </c>
       <c r="C26">
-        <v>1714.391483234951</v>
+        <v>1704.614048101923</v>
       </c>
       <c r="D26">
-        <v>2035.59548323495</v>
+        <v>2047.464048101923</v>
       </c>
       <c r="E26">
-        <v>-694.1960000000001</v>
+        <v>-672.5500000000001</v>
       </c>
       <c r="F26">
-        <v>519.5039999999999</v>
+        <v>541.15</v>
       </c>
       <c r="G26">
         <v>198.3</v>
@@ -3541,28 +3541,28 @@
         <v>276.125</v>
       </c>
       <c r="M26">
-        <v>26.9103072</v>
+        <v>28.03157</v>
       </c>
       <c r="N26">
-        <v>249.2146928</v>
+        <v>248.09343</v>
       </c>
       <c r="O26">
-        <v>62.15414438432</v>
+        <v>61.874501442</v>
       </c>
       <c r="P26">
-        <v>187.06054841568</v>
+        <v>186.218928558</v>
       </c>
       <c r="Q26">
-        <v>401.06054841568</v>
+        <v>400.218928558</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07878540542739695</v>
+        <v>0.07913654093165737</v>
       </c>
       <c r="T26">
-        <v>0.7617876542124011</v>
+        <v>0.7698970192068676</v>
       </c>
       <c r="U26">
         <v>0.05180000000000001</v>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.26093823261891</v>
+        <v>9.850500703314156</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06907267569874302</v>
+        <v>0.06926874927266435</v>
       </c>
       <c r="C27">
-        <v>1704.614048101923</v>
+        <v>1665.862168759031</v>
       </c>
       <c r="D27">
-        <v>2047.464048101923</v>
+        <v>2030.358168759031</v>
       </c>
       <c r="E27">
-        <v>-672.5500000000001</v>
+        <v>-650.904</v>
       </c>
       <c r="F27">
-        <v>541.15</v>
+        <v>562.796</v>
       </c>
       <c r="G27">
         <v>198.3</v>
@@ -3623,45 +3623,45 @@
         <v>276.125</v>
       </c>
       <c r="M27">
-        <v>28.03157</v>
+        <v>30.10958600000001</v>
       </c>
       <c r="N27">
-        <v>248.09343</v>
+        <v>246.015414</v>
       </c>
       <c r="O27">
-        <v>61.874501442</v>
+        <v>61.3562442516</v>
       </c>
       <c r="P27">
-        <v>186.218928558</v>
+        <v>184.6591697484</v>
       </c>
       <c r="Q27">
-        <v>400.218928558</v>
+        <v>398.6591697484</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07913654093165737</v>
+        <v>0.07949716658468156</v>
       </c>
       <c r="T27">
-        <v>0.7698970192068676</v>
+        <v>0.7782255562282115</v>
       </c>
       <c r="U27">
-        <v>0.05180000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V27">
         <v>0.2494</v>
       </c>
       <c r="W27">
-        <v>0.03888108</v>
+        <v>0.0401571</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>9.850500703314156</v>
+        <v>9.170667441259402</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06926874927266435</v>
+        <v>0.06914581784658569</v>
       </c>
       <c r="C28">
-        <v>1665.862168759031</v>
+        <v>1654.907369503258</v>
       </c>
       <c r="D28">
-        <v>2030.358168759031</v>
+        <v>2041.049369503258</v>
       </c>
       <c r="E28">
-        <v>-650.904</v>
+        <v>-629.258</v>
       </c>
       <c r="F28">
-        <v>562.796</v>
+        <v>584.442</v>
       </c>
       <c r="G28">
         <v>198.3</v>
@@ -3705,28 +3705,28 @@
         <v>276.125</v>
       </c>
       <c r="M28">
-        <v>30.10958600000001</v>
+        <v>31.267647</v>
       </c>
       <c r="N28">
-        <v>246.015414</v>
+        <v>244.857353</v>
       </c>
       <c r="O28">
-        <v>61.3562442516</v>
+        <v>61.0674238382</v>
       </c>
       <c r="P28">
-        <v>184.6591697484</v>
+        <v>183.7899291618</v>
       </c>
       <c r="Q28">
-        <v>398.6591697484</v>
+        <v>397.7899291618</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07949716658468156</v>
+        <v>0.07986767239258313</v>
       </c>
       <c r="T28">
-        <v>0.7782255562282115</v>
+        <v>0.7867822723460307</v>
       </c>
       <c r="U28">
         <v>0.05350000000000001</v>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.170667441259402</v>
+        <v>8.831013091583129</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3751,22 +3751,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06914581784658569</v>
+        <v>0.06902288642050701</v>
       </c>
       <c r="C29">
-        <v>1654.907369503258</v>
+        <v>1644.065758981237</v>
       </c>
       <c r="D29">
-        <v>2041.049369503258</v>
+        <v>2051.853758981237</v>
       </c>
       <c r="E29">
-        <v>-629.258</v>
+        <v>-607.612</v>
       </c>
       <c r="F29">
-        <v>584.442</v>
+        <v>606.0880000000001</v>
       </c>
       <c r="G29">
         <v>198.3</v>
@@ -3787,28 +3787,28 @@
         <v>276.125</v>
       </c>
       <c r="M29">
-        <v>31.267647</v>
+        <v>32.42570800000001</v>
       </c>
       <c r="N29">
-        <v>244.857353</v>
+        <v>243.699292</v>
       </c>
       <c r="O29">
-        <v>61.0674238382</v>
+        <v>60.7786034248</v>
       </c>
       <c r="P29">
-        <v>183.7899291618</v>
+        <v>182.9206885752</v>
       </c>
       <c r="Q29">
-        <v>397.7899291618</v>
+        <v>396.9206885752</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07986767239258313</v>
+        <v>0.08024847002848196</v>
       </c>
       <c r="T29">
-        <v>0.7867822723460307</v>
+        <v>0.7955766750226783</v>
       </c>
       <c r="U29">
         <v>0.05350000000000001</v>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.831013091583129</v>
+        <v>8.515619766883731</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3833,22 +3833,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06902288642050701</v>
+        <v>0.06889995499442834</v>
       </c>
       <c r="C30">
-        <v>1644.065758981237</v>
+        <v>1633.339144268233</v>
       </c>
       <c r="D30">
-        <v>2051.853758981237</v>
+        <v>2062.773144268233</v>
       </c>
       <c r="E30">
-        <v>-607.612</v>
+        <v>-585.966</v>
       </c>
       <c r="F30">
-        <v>606.0880000000001</v>
+        <v>627.734</v>
       </c>
       <c r="G30">
         <v>198.3</v>
@@ -3869,28 +3869,28 @@
         <v>276.125</v>
       </c>
       <c r="M30">
-        <v>32.42570800000001</v>
+        <v>33.583769</v>
       </c>
       <c r="N30">
-        <v>243.699292</v>
+        <v>242.541231</v>
       </c>
       <c r="O30">
-        <v>60.7786034248</v>
+        <v>60.4897830114</v>
       </c>
       <c r="P30">
-        <v>182.9206885752</v>
+        <v>182.0514479886</v>
       </c>
       <c r="Q30">
-        <v>396.9206885752</v>
+        <v>396.0514479886</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08024847002848196</v>
+        <v>0.08063999435834979</v>
       </c>
       <c r="T30">
-        <v>0.7955766750226783</v>
+        <v>0.804618807352189</v>
       </c>
       <c r="U30">
         <v>0.05350000000000001</v>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.515619766883731</v>
+        <v>8.221977705956707</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06889995499442833</v>
+        <v>0.06877702356834967</v>
       </c>
       <c r="C31">
-        <v>1633.339144268235</v>
+        <v>1622.729371112297</v>
       </c>
       <c r="D31">
-        <v>2062.773144268234</v>
+        <v>2073.809371112297</v>
       </c>
       <c r="E31">
-        <v>-585.9660000000001</v>
+        <v>-564.3200000000001</v>
       </c>
       <c r="F31">
-        <v>627.7339999999999</v>
+        <v>649.38</v>
       </c>
       <c r="G31">
         <v>198.3</v>
@@ -3951,28 +3951,28 @@
         <v>276.125</v>
       </c>
       <c r="M31">
-        <v>33.583769</v>
+        <v>34.74183</v>
       </c>
       <c r="N31">
-        <v>242.541231</v>
+        <v>241.38317</v>
       </c>
       <c r="O31">
-        <v>60.48978301140001</v>
+        <v>60.200962598</v>
       </c>
       <c r="P31">
-        <v>182.0514479886</v>
+        <v>181.182207402</v>
       </c>
       <c r="Q31">
-        <v>396.0514479886</v>
+        <v>395.182207402</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08063999435834976</v>
+        <v>0.08104270509764239</v>
       </c>
       <c r="T31">
-        <v>0.8046188073521888</v>
+        <v>0.8139192863196858</v>
       </c>
       <c r="U31">
         <v>0.05350000000000001</v>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.221977705956709</v>
+        <v>7.947911782424818</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06877702356834967</v>
+        <v>0.068654092142271</v>
       </c>
       <c r="C32">
-        <v>1622.729371112297</v>
+        <v>1612.238324974349</v>
       </c>
       <c r="D32">
-        <v>2073.809371112297</v>
+        <v>2084.964324974349</v>
       </c>
       <c r="E32">
-        <v>-564.3200000000001</v>
+        <v>-542.6740000000001</v>
       </c>
       <c r="F32">
-        <v>649.38</v>
+        <v>671.026</v>
       </c>
       <c r="G32">
         <v>198.3</v>
@@ -4033,28 +4033,28 @@
         <v>276.125</v>
       </c>
       <c r="M32">
-        <v>34.74183</v>
+        <v>35.899891</v>
       </c>
       <c r="N32">
-        <v>241.38317</v>
+        <v>240.225109</v>
       </c>
       <c r="O32">
-        <v>60.200962598</v>
+        <v>59.9121421846</v>
       </c>
       <c r="P32">
-        <v>181.182207402</v>
+        <v>180.3129668154</v>
       </c>
       <c r="Q32">
-        <v>395.182207402</v>
+        <v>394.3129668154</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08104270509764239</v>
+        <v>0.08145708861198696</v>
       </c>
       <c r="T32">
-        <v>0.8139192863196858</v>
+        <v>0.8234893443876897</v>
       </c>
       <c r="U32">
         <v>0.05350000000000001</v>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.947911782424818</v>
+        <v>7.691527531378855</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4079,22 +4079,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.068654092142271</v>
+        <v>0.06872331431619232</v>
       </c>
       <c r="C33">
-        <v>1612.238324974349</v>
+        <v>1584.296299838875</v>
       </c>
       <c r="D33">
-        <v>2084.964324974349</v>
+        <v>2078.668299838875</v>
       </c>
       <c r="E33">
-        <v>-542.6740000000001</v>
+        <v>-521.028</v>
       </c>
       <c r="F33">
-        <v>671.026</v>
+        <v>692.672</v>
       </c>
       <c r="G33">
         <v>198.3</v>
@@ -4115,45 +4115,45 @@
         <v>276.125</v>
       </c>
       <c r="M33">
-        <v>35.899891</v>
+        <v>37.6120896</v>
       </c>
       <c r="N33">
-        <v>240.225109</v>
+        <v>238.5129104</v>
       </c>
       <c r="O33">
-        <v>59.9121421846</v>
+        <v>59.48511985376</v>
       </c>
       <c r="P33">
-        <v>180.3129668154</v>
+        <v>179.02779054624</v>
       </c>
       <c r="Q33">
-        <v>394.3129668154</v>
+        <v>393.02779054624</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08145708861198696</v>
+        <v>0.08188365987675342</v>
       </c>
       <c r="T33">
-        <v>0.8234893443876897</v>
+        <v>0.8333408747518114</v>
       </c>
       <c r="U33">
-        <v>0.05350000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V33">
         <v>0.2494</v>
       </c>
       <c r="W33">
-        <v>0.0401571</v>
+        <v>0.04075758</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>7.691527531378855</v>
+        <v>7.341389508973199</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06872331431619232</v>
+        <v>0.06860638769011365</v>
       </c>
       <c r="C34">
-        <v>1584.296299838875</v>
+        <v>1573.307475115352</v>
       </c>
       <c r="D34">
-        <v>2078.668299838875</v>
+        <v>2089.325475115352</v>
       </c>
       <c r="E34">
-        <v>-521.028</v>
+        <v>-499.3820000000001</v>
       </c>
       <c r="F34">
-        <v>692.672</v>
+        <v>714.318</v>
       </c>
       <c r="G34">
         <v>198.3</v>
@@ -4197,28 +4197,28 @@
         <v>276.125</v>
       </c>
       <c r="M34">
-        <v>37.6120896</v>
+        <v>38.7874674</v>
       </c>
       <c r="N34">
-        <v>238.5129104</v>
+        <v>237.3375326</v>
       </c>
       <c r="O34">
-        <v>59.48511985376</v>
+        <v>59.19198063044</v>
       </c>
       <c r="P34">
-        <v>179.02779054624</v>
+        <v>178.14555196956</v>
       </c>
       <c r="Q34">
-        <v>393.02779054624</v>
+        <v>392.1455519695601</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08188365987675342</v>
+        <v>0.08232296461210994</v>
       </c>
       <c r="T34">
-        <v>0.8333408747518114</v>
+        <v>0.8434864806491905</v>
       </c>
       <c r="U34">
         <v>0.05430000000000001</v>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.341389508973199</v>
+        <v>7.118923160216435</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4243,22 +4243,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06860638769011365</v>
+        <v>0.06848946106403499</v>
       </c>
       <c r="C35">
-        <v>1573.307475115352</v>
+        <v>1562.428490598707</v>
       </c>
       <c r="D35">
-        <v>2089.325475115352</v>
+        <v>2100.092490598707</v>
       </c>
       <c r="E35">
-        <v>-499.3820000000001</v>
+        <v>-477.736</v>
       </c>
       <c r="F35">
-        <v>714.318</v>
+        <v>735.9640000000001</v>
       </c>
       <c r="G35">
         <v>198.3</v>
@@ -4279,28 +4279,28 @@
         <v>276.125</v>
       </c>
       <c r="M35">
-        <v>38.7874674</v>
+        <v>39.96284520000001</v>
       </c>
       <c r="N35">
-        <v>237.3375326</v>
+        <v>236.1621548</v>
       </c>
       <c r="O35">
-        <v>59.19198063044</v>
+        <v>58.89884140712</v>
       </c>
       <c r="P35">
-        <v>178.14555196956</v>
+        <v>177.26331339288</v>
       </c>
       <c r="Q35">
-        <v>392.1455519695601</v>
+        <v>391.26331339288</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08232296461210994</v>
+        <v>0.08277558161217423</v>
       </c>
       <c r="T35">
-        <v>0.8434864806491905</v>
+        <v>0.8539395291495204</v>
       </c>
       <c r="U35">
         <v>0.05430000000000001</v>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.118923160216435</v>
+        <v>6.909543067268892</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4325,22 +4325,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06848946106403499</v>
+        <v>0.06837253443795632</v>
       </c>
       <c r="C36">
-        <v>1562.428490598707</v>
+        <v>1551.661053218859</v>
       </c>
       <c r="D36">
-        <v>2100.092490598707</v>
+        <v>2110.971053218859</v>
       </c>
       <c r="E36">
-        <v>-477.736</v>
+        <v>-456.09</v>
       </c>
       <c r="F36">
-        <v>735.9640000000001</v>
+        <v>757.61</v>
       </c>
       <c r="G36">
         <v>198.3</v>
@@ -4361,28 +4361,28 @@
         <v>276.125</v>
       </c>
       <c r="M36">
-        <v>39.96284520000001</v>
+        <v>41.138223</v>
       </c>
       <c r="N36">
-        <v>236.1621548</v>
+        <v>234.986777</v>
       </c>
       <c r="O36">
-        <v>58.89884140712</v>
+        <v>58.6057021838</v>
       </c>
       <c r="P36">
-        <v>177.26331339288</v>
+        <v>176.3810748162</v>
       </c>
       <c r="Q36">
-        <v>391.26331339288</v>
+        <v>390.3810748162</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08277558161217423</v>
+        <v>0.08324212528916357</v>
       </c>
       <c r="T36">
-        <v>0.8539395291495204</v>
+        <v>0.864714209911399</v>
       </c>
       <c r="U36">
         <v>0.05430000000000001</v>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.909543067268892</v>
+        <v>6.712127551061211</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06837253443795632</v>
+        <v>0.06825560781187764</v>
       </c>
       <c r="C37">
-        <v>1551.661053218859</v>
+        <v>1541.00690545775</v>
       </c>
       <c r="D37">
-        <v>2110.971053218859</v>
+        <v>2121.96290545775</v>
       </c>
       <c r="E37">
-        <v>-456.09</v>
+        <v>-434.444</v>
       </c>
       <c r="F37">
-        <v>757.61</v>
+        <v>779.2560000000001</v>
       </c>
       <c r="G37">
         <v>198.3</v>
@@ -4443,28 +4443,28 @@
         <v>276.125</v>
       </c>
       <c r="M37">
-        <v>41.138223</v>
+        <v>42.31360080000001</v>
       </c>
       <c r="N37">
-        <v>234.986777</v>
+        <v>233.8113992</v>
       </c>
       <c r="O37">
-        <v>58.6057021838</v>
+        <v>58.31256296048</v>
       </c>
       <c r="P37">
-        <v>176.3810748162</v>
+        <v>175.49883623952</v>
       </c>
       <c r="Q37">
-        <v>390.3810748162</v>
+        <v>389.49883623952</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08324212528916357</v>
+        <v>0.08372324845605883</v>
       </c>
       <c r="T37">
-        <v>0.864714209911399</v>
+        <v>0.8758255994470863</v>
       </c>
       <c r="U37">
         <v>0.05430000000000001</v>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.712127551061211</v>
+        <v>6.525679563531732</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4489,22 +4489,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06825560781187764</v>
+        <v>0.06813868118579898</v>
       </c>
       <c r="C38">
-        <v>1541.00690545775</v>
+        <v>1530.467826279781</v>
       </c>
       <c r="D38">
-        <v>2121.96290545775</v>
+        <v>2133.069826279781</v>
       </c>
       <c r="E38">
-        <v>-434.4440000000001</v>
+        <v>-412.7980000000001</v>
       </c>
       <c r="F38">
-        <v>779.256</v>
+        <v>800.9019999999999</v>
       </c>
       <c r="G38">
         <v>198.3</v>
@@ -4525,28 +4525,28 @@
         <v>276.125</v>
       </c>
       <c r="M38">
-        <v>42.3136008</v>
+        <v>43.4889786</v>
       </c>
       <c r="N38">
-        <v>233.8113992</v>
+        <v>232.6360214</v>
       </c>
       <c r="O38">
-        <v>58.31256296048</v>
+        <v>58.01942373716</v>
       </c>
       <c r="P38">
-        <v>175.49883623952</v>
+        <v>174.61659766284</v>
       </c>
       <c r="Q38">
-        <v>389.49883623952</v>
+        <v>388.61659766284</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08372324845605883</v>
+        <v>0.08421964537428409</v>
       </c>
       <c r="T38">
-        <v>0.8758255994470863</v>
+        <v>0.8872897315077158</v>
       </c>
       <c r="U38">
         <v>0.05430000000000001</v>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.525679563531733</v>
+        <v>6.349309845598443</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06813868118579898</v>
+        <v>0.06802175455972032</v>
       </c>
       <c r="C39">
-        <v>1530.467826279781</v>
+        <v>1520.045632091639</v>
       </c>
       <c r="D39">
-        <v>2133.069826279781</v>
+        <v>2144.293632091639</v>
       </c>
       <c r="E39">
-        <v>-412.7980000000001</v>
+        <v>-391.152</v>
       </c>
       <c r="F39">
-        <v>800.9019999999999</v>
+        <v>822.548</v>
       </c>
       <c r="G39">
         <v>198.3</v>
@@ -4607,28 +4607,28 @@
         <v>276.125</v>
       </c>
       <c r="M39">
-        <v>43.4889786</v>
+        <v>44.66435640000001</v>
       </c>
       <c r="N39">
-        <v>232.6360214</v>
+        <v>231.4606436</v>
       </c>
       <c r="O39">
-        <v>58.01942373716</v>
+        <v>57.72628451384</v>
       </c>
       <c r="P39">
-        <v>174.61659766284</v>
+        <v>173.73435908616</v>
       </c>
       <c r="Q39">
-        <v>388.61659766284</v>
+        <v>387.73435908616</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08421964537428409</v>
+        <v>0.08473205509632308</v>
       </c>
       <c r="T39">
-        <v>0.8872897315077158</v>
+        <v>0.8991236742799789</v>
       </c>
       <c r="U39">
         <v>0.05430000000000001</v>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.349309845598443</v>
+        <v>6.182222744398483</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06802175455972032</v>
+        <v>0.06819756193364164</v>
       </c>
       <c r="C40">
-        <v>1520.045632091639</v>
+        <v>1481.568218320304</v>
       </c>
       <c r="D40">
-        <v>2144.293632091639</v>
+        <v>2127.462218320304</v>
       </c>
       <c r="E40">
-        <v>-391.152</v>
+        <v>-369.5060000000001</v>
       </c>
       <c r="F40">
-        <v>822.548</v>
+        <v>844.194</v>
       </c>
       <c r="G40">
         <v>198.3</v>
@@ -4689,45 +4689,45 @@
         <v>276.125</v>
       </c>
       <c r="M40">
-        <v>44.66435640000001</v>
+        <v>46.6839282</v>
       </c>
       <c r="N40">
-        <v>231.4606436</v>
+        <v>229.4410718</v>
       </c>
       <c r="O40">
-        <v>57.72628451384</v>
+        <v>57.22260330692</v>
       </c>
       <c r="P40">
-        <v>173.73435908616</v>
+        <v>172.21846849308</v>
       </c>
       <c r="Q40">
-        <v>387.73435908616</v>
+        <v>386.21846849308</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08473205509632308</v>
+        <v>0.08526126513711743</v>
       </c>
       <c r="T40">
-        <v>0.8991236742799789</v>
+        <v>0.9113456151759226</v>
       </c>
       <c r="U40">
-        <v>0.05430000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V40">
         <v>0.2494</v>
       </c>
       <c r="W40">
-        <v>0.04075758</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>6.182222744398483</v>
+        <v>5.91477646904615</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4735,22 +4735,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06819756193364164</v>
+        <v>0.06808814130756297</v>
       </c>
       <c r="C41">
-        <v>1481.568218320304</v>
+        <v>1470.3667073728</v>
       </c>
       <c r="D41">
-        <v>2127.462218320304</v>
+        <v>2137.9067073728</v>
       </c>
       <c r="E41">
-        <v>-369.5060000000001</v>
+        <v>-347.86</v>
       </c>
       <c r="F41">
-        <v>844.194</v>
+        <v>865.84</v>
       </c>
       <c r="G41">
         <v>198.3</v>
@@ -4771,28 +4771,28 @@
         <v>276.125</v>
       </c>
       <c r="M41">
-        <v>46.6839282</v>
+        <v>47.88095200000001</v>
       </c>
       <c r="N41">
-        <v>229.4410718</v>
+        <v>228.244048</v>
       </c>
       <c r="O41">
-        <v>57.22260330692</v>
+        <v>56.9240655712</v>
       </c>
       <c r="P41">
-        <v>172.21846849308</v>
+        <v>171.3199824288</v>
       </c>
       <c r="Q41">
-        <v>386.21846849308</v>
+        <v>385.3199824288</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08526126513711743</v>
+        <v>0.08580811551260495</v>
       </c>
       <c r="T41">
-        <v>0.9113456151759226</v>
+        <v>0.923974954101731</v>
       </c>
       <c r="U41">
         <v>0.05530000000000001</v>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.91477646904615</v>
+        <v>5.766907057319996</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4817,22 +4817,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06808814130756297</v>
+        <v>0.06797872068148431</v>
       </c>
       <c r="C42">
-        <v>1470.3667073728</v>
+        <v>1459.268253995441</v>
       </c>
       <c r="D42">
-        <v>2137.9067073728</v>
+        <v>2148.454253995441</v>
       </c>
       <c r="E42">
-        <v>-347.86</v>
+        <v>-326.2140000000001</v>
       </c>
       <c r="F42">
-        <v>865.84</v>
+        <v>887.486</v>
       </c>
       <c r="G42">
         <v>198.3</v>
@@ -4853,28 +4853,28 @@
         <v>276.125</v>
       </c>
       <c r="M42">
-        <v>47.88095200000001</v>
+        <v>49.0779758</v>
       </c>
       <c r="N42">
-        <v>228.244048</v>
+        <v>227.0470242</v>
       </c>
       <c r="O42">
-        <v>56.9240655712</v>
+        <v>56.62552783548001</v>
       </c>
       <c r="P42">
-        <v>171.3199824288</v>
+        <v>170.42149636452</v>
       </c>
       <c r="Q42">
-        <v>385.3199824288</v>
+        <v>384.4214963645201</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08580811551260495</v>
+        <v>0.08637350318895644</v>
       </c>
       <c r="T42">
-        <v>0.923974954101731</v>
+        <v>0.9370324062114653</v>
       </c>
       <c r="U42">
         <v>0.05530000000000001</v>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.766907057319996</v>
+        <v>5.626250787629265</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4899,22 +4899,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06797872068148431</v>
+        <v>0.06786930005540563</v>
       </c>
       <c r="C43">
-        <v>1459.268253995441</v>
+        <v>1448.274391081048</v>
       </c>
       <c r="D43">
-        <v>2148.454253995441</v>
+        <v>2159.106391081048</v>
       </c>
       <c r="E43">
-        <v>-326.2140000000001</v>
+        <v>-304.568</v>
       </c>
       <c r="F43">
-        <v>887.486</v>
+        <v>909.1320000000001</v>
       </c>
       <c r="G43">
         <v>198.3</v>
@@ -4935,28 +4935,28 @@
         <v>276.125</v>
       </c>
       <c r="M43">
-        <v>49.0779758</v>
+        <v>50.27499960000001</v>
       </c>
       <c r="N43">
-        <v>227.0470242</v>
+        <v>225.8500004</v>
       </c>
       <c r="O43">
-        <v>56.62552783548001</v>
+        <v>56.32699009976</v>
       </c>
       <c r="P43">
-        <v>170.42149636452</v>
+        <v>169.52301030024</v>
       </c>
       <c r="Q43">
-        <v>384.4214963645201</v>
+        <v>383.52301030024</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08637350318895644</v>
+        <v>0.08695838699207867</v>
       </c>
       <c r="T43">
-        <v>0.9370324062114653</v>
+        <v>0.9505401152905006</v>
       </c>
       <c r="U43">
         <v>0.05530000000000001</v>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.626250787629265</v>
+        <v>5.492292435542853</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06786930005540563</v>
+        <v>0.06775987942932696</v>
       </c>
       <c r="C44">
-        <v>1448.274391081048</v>
+        <v>1437.386682074534</v>
       </c>
       <c r="D44">
-        <v>2159.106391081048</v>
+        <v>2169.864682074533</v>
       </c>
       <c r="E44">
-        <v>-304.5680000000001</v>
+        <v>-282.9220000000001</v>
       </c>
       <c r="F44">
-        <v>909.1319999999999</v>
+        <v>930.7779999999999</v>
       </c>
       <c r="G44">
         <v>198.3</v>
@@ -5017,28 +5017,28 @@
         <v>276.125</v>
       </c>
       <c r="M44">
-        <v>50.27499960000001</v>
+        <v>51.4720234</v>
       </c>
       <c r="N44">
-        <v>225.8500004</v>
+        <v>224.6529766</v>
       </c>
       <c r="O44">
-        <v>56.32699009976</v>
+        <v>56.02845236404</v>
       </c>
       <c r="P44">
-        <v>169.52301030024</v>
+        <v>168.62452423596</v>
       </c>
       <c r="Q44">
-        <v>383.52301030024</v>
+        <v>382.6245242359601</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08695838699207867</v>
+        <v>0.08756379303390693</v>
       </c>
       <c r="T44">
-        <v>0.9505401152905005</v>
+        <v>0.9645217790740633</v>
       </c>
       <c r="U44">
         <v>0.05530000000000001</v>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.492292435542853</v>
+        <v>5.364564704483717</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06775987942932696</v>
+        <v>0.06765045880324828</v>
       </c>
       <c r="C45">
-        <v>1437.386682074534</v>
+        <v>1426.606721737889</v>
       </c>
       <c r="D45">
-        <v>2169.864682074533</v>
+        <v>2180.730721737888</v>
       </c>
       <c r="E45">
-        <v>-282.9220000000001</v>
+        <v>-261.2760000000001</v>
       </c>
       <c r="F45">
-        <v>930.7779999999999</v>
+        <v>952.424</v>
       </c>
       <c r="G45">
         <v>198.3</v>
@@ -5099,28 +5099,28 @@
         <v>276.125</v>
       </c>
       <c r="M45">
-        <v>51.4720234</v>
+        <v>52.66904720000001</v>
       </c>
       <c r="N45">
-        <v>224.6529766</v>
+        <v>223.4559528</v>
       </c>
       <c r="O45">
-        <v>56.02845236404</v>
+        <v>55.72991462832</v>
       </c>
       <c r="P45">
-        <v>168.62452423596</v>
+        <v>167.72603817168</v>
       </c>
       <c r="Q45">
-        <v>382.6245242359601</v>
+        <v>381.72603817168</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08756379303390693</v>
+        <v>0.08819082072008622</v>
       </c>
       <c r="T45">
-        <v>0.9645217790740633</v>
+        <v>0.9790027879927535</v>
       </c>
       <c r="U45">
         <v>0.05530000000000001</v>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.364564704483717</v>
+        <v>5.242642779381814</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5145,22 +5145,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06765045880324828</v>
+        <v>0.06754103817716961</v>
       </c>
       <c r="C46">
-        <v>1426.606721737889</v>
+        <v>1415.93613693826</v>
       </c>
       <c r="D46">
-        <v>2180.730721737888</v>
+        <v>2191.70613693826</v>
       </c>
       <c r="E46">
-        <v>-261.2760000000001</v>
+        <v>-239.6300000000001</v>
       </c>
       <c r="F46">
-        <v>952.424</v>
+        <v>974.0699999999999</v>
       </c>
       <c r="G46">
         <v>198.3</v>
@@ -5181,28 +5181,28 @@
         <v>276.125</v>
       </c>
       <c r="M46">
-        <v>52.66904720000001</v>
+        <v>53.86607100000001</v>
       </c>
       <c r="N46">
-        <v>223.4559528</v>
+        <v>222.258929</v>
       </c>
       <c r="O46">
-        <v>55.72991462832</v>
+        <v>55.4313768926</v>
       </c>
       <c r="P46">
-        <v>167.72603817168</v>
+        <v>166.8275521074</v>
       </c>
       <c r="Q46">
-        <v>381.72603817168</v>
+        <v>380.8275521074</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08819082072008622</v>
+        <v>0.08884064941303565</v>
       </c>
       <c r="T46">
-        <v>0.9790027879927535</v>
+        <v>0.9940103790539416</v>
       </c>
       <c r="U46">
         <v>0.05530000000000001</v>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.242642779381814</v>
+        <v>5.126139606506663</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06754103817716961</v>
+        <v>0.06743161755109095</v>
       </c>
       <c r="C47">
-        <v>1415.93613693826</v>
+        <v>1405.376587459947</v>
       </c>
       <c r="D47">
-        <v>2191.70613693826</v>
+        <v>2202.792587459947</v>
       </c>
       <c r="E47">
-        <v>-239.6300000000001</v>
+        <v>-217.984</v>
       </c>
       <c r="F47">
-        <v>974.0699999999999</v>
+        <v>995.716</v>
       </c>
       <c r="G47">
         <v>198.3</v>
@@ -5263,28 +5263,28 @@
         <v>276.125</v>
       </c>
       <c r="M47">
-        <v>53.86607100000001</v>
+        <v>55.06309480000001</v>
       </c>
       <c r="N47">
-        <v>222.258929</v>
+        <v>221.0619052</v>
       </c>
       <c r="O47">
-        <v>55.4313768926</v>
+        <v>55.13283915688</v>
       </c>
       <c r="P47">
-        <v>166.8275521074</v>
+        <v>165.92906604312</v>
       </c>
       <c r="Q47">
-        <v>380.8275521074</v>
+        <v>379.92906604312</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08884064941303565</v>
+        <v>0.08951454583535359</v>
       </c>
       <c r="T47">
-        <v>0.9940103790539416</v>
+        <v>1.0095738068211</v>
       </c>
       <c r="U47">
         <v>0.05530000000000001</v>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.126139606506663</v>
+        <v>5.014701788973909</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06743161755109095</v>
+        <v>0.06732219692501229</v>
       </c>
       <c r="C48">
-        <v>1405.376587459947</v>
+        <v>1394.929766841174</v>
       </c>
       <c r="D48">
-        <v>2202.792587459947</v>
+        <v>2213.991766841174</v>
       </c>
       <c r="E48">
-        <v>-217.984</v>
+        <v>-196.3380000000001</v>
       </c>
       <c r="F48">
-        <v>995.716</v>
+        <v>1017.362</v>
       </c>
       <c r="G48">
         <v>198.3</v>
@@ -5345,28 +5345,28 @@
         <v>276.125</v>
       </c>
       <c r="M48">
-        <v>55.06309480000001</v>
+        <v>56.26011860000001</v>
       </c>
       <c r="N48">
-        <v>221.0619052</v>
+        <v>219.8648814</v>
       </c>
       <c r="O48">
-        <v>55.13283915688</v>
+        <v>54.83430142116</v>
       </c>
       <c r="P48">
-        <v>165.92906604312</v>
+        <v>165.03057997884</v>
       </c>
       <c r="Q48">
-        <v>379.92906604312</v>
+        <v>379.03057997884</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08951454583535359</v>
+        <v>0.09021387231134392</v>
       </c>
       <c r="T48">
-        <v>1.0095738068211</v>
+        <v>1.025724533749282</v>
       </c>
       <c r="U48">
         <v>0.05530000000000001</v>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.014701788973909</v>
+        <v>4.908006006229783</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06732219692501229</v>
+        <v>0.06721277629893362</v>
       </c>
       <c r="C49">
-        <v>1394.929766841174</v>
+        <v>1384.597403236509</v>
       </c>
       <c r="D49">
-        <v>2213.991766841174</v>
+        <v>2225.305403236509</v>
       </c>
       <c r="E49">
-        <v>-196.3380000000001</v>
+        <v>-174.692</v>
       </c>
       <c r="F49">
-        <v>1017.362</v>
+        <v>1039.008</v>
       </c>
       <c r="G49">
         <v>198.3</v>
@@ -5427,28 +5427,28 @@
         <v>276.125</v>
       </c>
       <c r="M49">
-        <v>56.26011860000001</v>
+        <v>57.45714240000001</v>
       </c>
       <c r="N49">
-        <v>219.8648814</v>
+        <v>218.6678576</v>
       </c>
       <c r="O49">
-        <v>54.83430142116</v>
+        <v>54.53576368544</v>
       </c>
       <c r="P49">
-        <v>165.03057997884</v>
+        <v>164.13209391456</v>
       </c>
       <c r="Q49">
-        <v>379.03057997884</v>
+        <v>378.13209391456</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09021387231134392</v>
+        <v>0.09094009595948771</v>
       </c>
       <c r="T49">
-        <v>1.025724533749282</v>
+        <v>1.042496442482395</v>
       </c>
       <c r="U49">
         <v>0.05530000000000001</v>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.908006006229783</v>
+        <v>4.805755881099996</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5473,22 +5473,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0672127762989336</v>
+        <v>0.06710335567285494</v>
       </c>
       <c r="C50">
-        <v>1384.597403236511</v>
+        <v>1374.381260305865</v>
       </c>
       <c r="D50">
-        <v>2225.30540323651</v>
+        <v>2236.735260305865</v>
       </c>
       <c r="E50">
-        <v>-174.6920000000002</v>
+        <v>-153.046</v>
       </c>
       <c r="F50">
-        <v>1039.008</v>
+        <v>1060.654</v>
       </c>
       <c r="G50">
         <v>198.3</v>
@@ -5509,28 +5509,28 @@
         <v>276.125</v>
       </c>
       <c r="M50">
-        <v>57.4571424</v>
+        <v>58.65416620000001</v>
       </c>
       <c r="N50">
-        <v>218.6678576</v>
+        <v>217.4708338</v>
       </c>
       <c r="O50">
-        <v>54.53576368544</v>
+        <v>54.23722594972</v>
       </c>
       <c r="P50">
-        <v>164.13209391456</v>
+        <v>163.23360785028</v>
       </c>
       <c r="Q50">
-        <v>378.13209391456</v>
+        <v>377.23360785028</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.0909400959594877</v>
+        <v>0.09169479896638222</v>
       </c>
       <c r="T50">
-        <v>1.042496442482395</v>
+        <v>1.05992607312661</v>
       </c>
       <c r="U50">
         <v>0.05530000000000001</v>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.805755881099997</v>
+        <v>4.707679230465303</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06710335567285494</v>
+        <v>0.06699393504677627</v>
       </c>
       <c r="C51">
-        <v>1374.381260305865</v>
+        <v>1364.283138131042</v>
       </c>
       <c r="D51">
-        <v>2236.735260305865</v>
+        <v>2248.283138131042</v>
       </c>
       <c r="E51">
-        <v>-153.046</v>
+        <v>-131.4000000000001</v>
       </c>
       <c r="F51">
-        <v>1060.654</v>
+        <v>1082.3</v>
       </c>
       <c r="G51">
         <v>198.3</v>
@@ -5591,28 +5591,28 @@
         <v>276.125</v>
       </c>
       <c r="M51">
-        <v>58.65416620000001</v>
+        <v>59.85119000000001</v>
       </c>
       <c r="N51">
-        <v>217.4708338</v>
+        <v>216.27381</v>
       </c>
       <c r="O51">
-        <v>54.23722594972</v>
+        <v>53.938688214</v>
       </c>
       <c r="P51">
-        <v>163.23360785028</v>
+        <v>162.335121786</v>
       </c>
       <c r="Q51">
-        <v>377.23360785028</v>
+        <v>376.3351217860001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09169479896638222</v>
+        <v>0.09247969009355253</v>
       </c>
       <c r="T51">
-        <v>1.05992607312661</v>
+        <v>1.078052888996594</v>
       </c>
       <c r="U51">
         <v>0.05530000000000001</v>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.707679230465303</v>
+        <v>4.613525645855996</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06699393504677627</v>
+        <v>0.06688451442069759</v>
       </c>
       <c r="C52">
-        <v>1364.283138131042</v>
+        <v>1354.304874160805</v>
       </c>
       <c r="D52">
-        <v>2248.283138131042</v>
+        <v>2259.950874160805</v>
       </c>
       <c r="E52">
-        <v>-131.4000000000001</v>
+        <v>-109.7540000000001</v>
       </c>
       <c r="F52">
-        <v>1082.3</v>
+        <v>1103.946</v>
       </c>
       <c r="G52">
         <v>198.3</v>
@@ -5673,28 +5673,28 @@
         <v>276.125</v>
       </c>
       <c r="M52">
-        <v>59.85119000000001</v>
+        <v>61.04821380000001</v>
       </c>
       <c r="N52">
-        <v>216.27381</v>
+        <v>215.0767862</v>
       </c>
       <c r="O52">
-        <v>53.938688214</v>
+        <v>53.64015047828</v>
       </c>
       <c r="P52">
-        <v>162.335121786</v>
+        <v>161.43663572172</v>
       </c>
       <c r="Q52">
-        <v>376.3351217860001</v>
+        <v>375.43663572172</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09247969009355253</v>
+        <v>0.0932966175932604</v>
       </c>
       <c r="T52">
-        <v>1.078052888996594</v>
+        <v>1.096919574902088</v>
       </c>
       <c r="U52">
         <v>0.05530000000000001</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.613525645855996</v>
+        <v>4.523064358682349</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06688451442069759</v>
+        <v>0.06775087379461892</v>
       </c>
       <c r="C53">
-        <v>1354.304874160805</v>
+        <v>1243.462897601964</v>
       </c>
       <c r="D53">
-        <v>2259.950874160805</v>
+        <v>2170.754897601964</v>
       </c>
       <c r="E53">
-        <v>-109.7540000000001</v>
+        <v>-88.10799999999995</v>
       </c>
       <c r="F53">
-        <v>1103.946</v>
+        <v>1125.592</v>
       </c>
       <c r="G53">
         <v>198.3</v>
@@ -5755,45 +5755,45 @@
         <v>276.125</v>
       </c>
       <c r="M53">
-        <v>61.04821380000001</v>
+        <v>65.05921760000001</v>
       </c>
       <c r="N53">
-        <v>215.0767862</v>
+        <v>211.0657824</v>
       </c>
       <c r="O53">
-        <v>53.64015047828</v>
+        <v>52.63980613056</v>
       </c>
       <c r="P53">
-        <v>161.43663572172</v>
+        <v>158.42597626944</v>
       </c>
       <c r="Q53">
-        <v>375.43663572172</v>
+        <v>372.42597626944</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.0932966175932604</v>
+        <v>0.09414758373878943</v>
       </c>
       <c r="T53">
-        <v>1.096919574902088</v>
+        <v>1.11657237272031</v>
       </c>
       <c r="U53">
-        <v>0.05530000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V53">
         <v>0.2494</v>
       </c>
       <c r="W53">
-        <v>0.04150818000000001</v>
+        <v>0.04338468</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.523064358682349</v>
+        <v>4.244210277745485</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5801,22 +5801,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06775087379461892</v>
+        <v>0.06766021816854026</v>
       </c>
       <c r="C54">
-        <v>1243.462897601964</v>
+        <v>1230.819147386856</v>
       </c>
       <c r="D54">
-        <v>2170.754897601964</v>
+        <v>2179.757147386856</v>
       </c>
       <c r="E54">
-        <v>-88.10799999999995</v>
+        <v>-66.46199999999999</v>
       </c>
       <c r="F54">
-        <v>1125.592</v>
+        <v>1147.238</v>
       </c>
       <c r="G54">
         <v>198.3</v>
@@ -5837,28 +5837,28 @@
         <v>276.125</v>
       </c>
       <c r="M54">
-        <v>65.05921760000001</v>
+        <v>66.3103564</v>
       </c>
       <c r="N54">
-        <v>211.0657824</v>
+        <v>209.8146436</v>
       </c>
       <c r="O54">
-        <v>52.63980613056</v>
+        <v>52.32777211384001</v>
       </c>
       <c r="P54">
-        <v>158.42597626944</v>
+        <v>157.48687148616</v>
       </c>
       <c r="Q54">
-        <v>372.42597626944</v>
+        <v>371.48687148616</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09414758373878943</v>
+        <v>0.09503476120966012</v>
       </c>
       <c r="T54">
-        <v>1.11657237272031</v>
+        <v>1.137061459807393</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.244210277745485</v>
+        <v>4.164130838542741</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06766021816854026</v>
+        <v>0.06756956254246159</v>
       </c>
       <c r="C55">
-        <v>1230.819147386856</v>
+        <v>1218.250373835958</v>
       </c>
       <c r="D55">
-        <v>2179.757147386856</v>
+        <v>2188.834373835958</v>
       </c>
       <c r="E55">
-        <v>-66.46199999999999</v>
+        <v>-44.81600000000003</v>
       </c>
       <c r="F55">
-        <v>1147.238</v>
+        <v>1168.884</v>
       </c>
       <c r="G55">
         <v>198.3</v>
@@ -5919,28 +5919,28 @@
         <v>276.125</v>
       </c>
       <c r="M55">
-        <v>66.3103564</v>
+        <v>67.56149520000001</v>
       </c>
       <c r="N55">
-        <v>209.8146436</v>
+        <v>208.5635048</v>
       </c>
       <c r="O55">
-        <v>52.32777211384001</v>
+        <v>52.01573809711999</v>
       </c>
       <c r="P55">
-        <v>157.48687148616</v>
+        <v>156.54776670288</v>
       </c>
       <c r="Q55">
-        <v>371.48687148616</v>
+        <v>370.54776670288</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09503476120966012</v>
+        <v>0.09596051161404692</v>
       </c>
       <c r="T55">
-        <v>1.137061459807393</v>
+        <v>1.158441376767828</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.164130838542741</v>
+        <v>4.087017304495652</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06756956254246159</v>
+        <v>0.06747890691638292</v>
       </c>
       <c r="C56">
-        <v>1218.250373835958</v>
+        <v>1205.757517548783</v>
       </c>
       <c r="D56">
-        <v>2188.834373835958</v>
+        <v>2197.987517548783</v>
       </c>
       <c r="E56">
-        <v>-44.81600000000003</v>
+        <v>-23.17000000000007</v>
       </c>
       <c r="F56">
-        <v>1168.884</v>
+        <v>1190.53</v>
       </c>
       <c r="G56">
         <v>198.3</v>
@@ -6001,28 +6001,28 @@
         <v>276.125</v>
       </c>
       <c r="M56">
-        <v>67.56149520000001</v>
+        <v>68.812634</v>
       </c>
       <c r="N56">
-        <v>208.5635048</v>
+        <v>207.312366</v>
       </c>
       <c r="O56">
-        <v>52.01573809711999</v>
+        <v>51.7037040804</v>
       </c>
       <c r="P56">
-        <v>156.54776670288</v>
+        <v>155.6086619196</v>
       </c>
       <c r="Q56">
-        <v>370.54776670288</v>
+        <v>369.6086619196</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09596051161404692</v>
+        <v>0.09692740648085094</v>
       </c>
       <c r="T56">
-        <v>1.158441376767828</v>
+        <v>1.180771512259837</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.087017304495652</v>
+        <v>4.012707898959368</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6047,22 +6047,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06747890691638292</v>
+        <v>0.06885942729030424</v>
       </c>
       <c r="C57">
-        <v>1205.757517548783</v>
+        <v>1052.522536113989</v>
       </c>
       <c r="D57">
-        <v>2197.987517548783</v>
+        <v>2066.398536113988</v>
       </c>
       <c r="E57">
-        <v>-23.17000000000007</v>
+        <v>-1.523999999999887</v>
       </c>
       <c r="F57">
-        <v>1190.53</v>
+        <v>1212.176</v>
       </c>
       <c r="G57">
         <v>198.3</v>
@@ -6083,45 +6083,45 @@
         <v>276.125</v>
       </c>
       <c r="M57">
-        <v>68.812634</v>
+        <v>74.30638880000002</v>
       </c>
       <c r="N57">
-        <v>207.312366</v>
+        <v>201.8186112</v>
       </c>
       <c r="O57">
-        <v>51.7037040804</v>
+        <v>50.33356163327999</v>
       </c>
       <c r="P57">
-        <v>155.6086619196</v>
+        <v>151.48504956672</v>
       </c>
       <c r="Q57">
-        <v>369.6086619196</v>
+        <v>365.48504956672</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09692740648085094</v>
+        <v>0.09793825111432783</v>
       </c>
       <c r="T57">
-        <v>1.180771512259837</v>
+        <v>1.204116653910574</v>
       </c>
       <c r="U57">
-        <v>0.0578</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V57">
         <v>0.2494</v>
       </c>
       <c r="W57">
-        <v>0.04338468</v>
+        <v>0.04601178</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.012707898959368</v>
+        <v>3.716033095662965</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6129,22 +6129,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06885942729030424</v>
+        <v>0.06879504266422556</v>
       </c>
       <c r="C58">
-        <v>1052.522536113989</v>
+        <v>1036.66231781572</v>
       </c>
       <c r="D58">
-        <v>2066.398536113988</v>
+        <v>2072.18431781572</v>
       </c>
       <c r="E58">
-        <v>-1.523999999999887</v>
+        <v>20.12200000000007</v>
       </c>
       <c r="F58">
-        <v>1212.176</v>
+        <v>1233.822</v>
       </c>
       <c r="G58">
         <v>198.3</v>
@@ -6165,28 +6165,28 @@
         <v>276.125</v>
       </c>
       <c r="M58">
-        <v>74.30638880000002</v>
+        <v>75.63328860000001</v>
       </c>
       <c r="N58">
-        <v>201.8186112</v>
+        <v>200.4917114</v>
       </c>
       <c r="O58">
-        <v>50.33356163327999</v>
+        <v>50.00263282316</v>
       </c>
       <c r="P58">
-        <v>151.48504956672</v>
+        <v>150.48907857684</v>
       </c>
       <c r="Q58">
-        <v>365.48504956672</v>
+        <v>364.48907857684</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09793825111432783</v>
+        <v>0.09899611177726877</v>
       </c>
       <c r="T58">
-        <v>1.204116653910574</v>
+        <v>1.228547616103205</v>
       </c>
       <c r="U58">
         <v>0.06130000000000001</v>
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.716033095662965</v>
+        <v>3.65083953258116</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06879504266422556</v>
+        <v>0.0687306580381469</v>
       </c>
       <c r="C59">
-        <v>1036.66231781572</v>
+        <v>1020.834590115045</v>
       </c>
       <c r="D59">
-        <v>2072.18431781572</v>
+        <v>2078.002590115045</v>
       </c>
       <c r="E59">
-        <v>20.12200000000007</v>
+        <v>41.76800000000003</v>
       </c>
       <c r="F59">
-        <v>1233.822</v>
+        <v>1255.468</v>
       </c>
       <c r="G59">
         <v>198.3</v>
@@ -6247,28 +6247,28 @@
         <v>276.125</v>
       </c>
       <c r="M59">
-        <v>75.63328860000001</v>
+        <v>76.96018840000001</v>
       </c>
       <c r="N59">
-        <v>200.4917114</v>
+        <v>199.1648116</v>
       </c>
       <c r="O59">
-        <v>50.00263282316</v>
+        <v>49.67170401304001</v>
       </c>
       <c r="P59">
-        <v>150.48907857684</v>
+        <v>149.49310758696</v>
       </c>
       <c r="Q59">
-        <v>364.48907857684</v>
+        <v>363.49310758696</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09899611177726877</v>
+        <v>0.1001043467574926</v>
       </c>
       <c r="T59">
-        <v>1.228547616103205</v>
+        <v>1.254141957447867</v>
       </c>
       <c r="U59">
         <v>0.06130000000000001</v>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.65083953258116</v>
+        <v>3.587894023398726</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0687306580381469</v>
+        <v>0.06866627341206823</v>
       </c>
       <c r="C60">
-        <v>1020.834590115045</v>
+        <v>1005.039627463547</v>
       </c>
       <c r="D60">
-        <v>2078.002590115045</v>
+        <v>2083.853627463547</v>
       </c>
       <c r="E60">
-        <v>41.7679999999998</v>
+        <v>63.41399999999976</v>
       </c>
       <c r="F60">
-        <v>1255.468</v>
+        <v>1277.114</v>
       </c>
       <c r="G60">
         <v>198.3</v>
@@ -6329,28 +6329,28 @@
         <v>276.125</v>
       </c>
       <c r="M60">
-        <v>76.96018839999999</v>
+        <v>78.2870882</v>
       </c>
       <c r="N60">
-        <v>199.1648116</v>
+        <v>197.8379118</v>
       </c>
       <c r="O60">
-        <v>49.67170401304001</v>
+        <v>49.34077520292</v>
       </c>
       <c r="P60">
-        <v>149.49310758696</v>
+        <v>148.49713659708</v>
       </c>
       <c r="Q60">
-        <v>363.49310758696</v>
+        <v>362.49713659708</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1001043467574926</v>
+        <v>0.1012666419806542</v>
       </c>
       <c r="T60">
-        <v>1.254141957447867</v>
+        <v>1.280984803248366</v>
       </c>
       <c r="U60">
         <v>0.06130000000000001</v>
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.587894023398727</v>
+        <v>3.527082260290273</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6375,22 +6375,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06866627341206823</v>
+        <v>0.06986289678598956</v>
       </c>
       <c r="C61">
-        <v>1005.039627463547</v>
+        <v>879.7657068257661</v>
       </c>
       <c r="D61">
-        <v>2083.853627463547</v>
+        <v>1980.225706825766</v>
       </c>
       <c r="E61">
-        <v>63.41399999999976</v>
+        <v>85.05999999999995</v>
       </c>
       <c r="F61">
-        <v>1277.114</v>
+        <v>1298.76</v>
       </c>
       <c r="G61">
         <v>198.3</v>
@@ -6411,45 +6411,45 @@
         <v>276.125</v>
       </c>
       <c r="M61">
-        <v>78.2870882</v>
+        <v>83.250516</v>
       </c>
       <c r="N61">
-        <v>197.8379118</v>
+        <v>192.874484</v>
       </c>
       <c r="O61">
-        <v>49.34077520292</v>
+        <v>48.1028963096</v>
       </c>
       <c r="P61">
-        <v>148.49713659708</v>
+        <v>144.7715876904</v>
       </c>
       <c r="Q61">
-        <v>362.49713659708</v>
+        <v>358.7715876904</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1012666419806542</v>
+        <v>0.1024870519649739</v>
       </c>
       <c r="T61">
-        <v>1.280984803248366</v>
+        <v>1.30916979133889</v>
       </c>
       <c r="U61">
-        <v>0.06130000000000001</v>
+        <v>0.0641</v>
       </c>
       <c r="V61">
         <v>0.2494</v>
       </c>
       <c r="W61">
-        <v>0.04601178</v>
+        <v>0.04811346</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.527082260290273</v>
+        <v>3.316796258656222</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6457,22 +6457,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.06986289678598956</v>
+        <v>0.06981952895991089</v>
       </c>
       <c r="C62">
-        <v>879.7657068257661</v>
+        <v>861.6950510464399</v>
       </c>
       <c r="D62">
-        <v>1980.225706825766</v>
+        <v>1983.80105104644</v>
       </c>
       <c r="E62">
-        <v>85.05999999999995</v>
+        <v>106.7059999999999</v>
       </c>
       <c r="F62">
-        <v>1298.76</v>
+        <v>1320.406</v>
       </c>
       <c r="G62">
         <v>198.3</v>
@@ -6493,28 +6493,28 @@
         <v>276.125</v>
       </c>
       <c r="M62">
-        <v>83.250516</v>
+        <v>84.63802460000001</v>
       </c>
       <c r="N62">
-        <v>192.874484</v>
+        <v>191.4869754</v>
       </c>
       <c r="O62">
-        <v>48.1028963096</v>
+        <v>47.75685166476001</v>
       </c>
       <c r="P62">
-        <v>144.7715876904</v>
+        <v>143.73012373524</v>
       </c>
       <c r="Q62">
-        <v>358.7715876904</v>
+        <v>357.73012373524</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1024870519649739</v>
+        <v>0.1037700470766946</v>
       </c>
       <c r="T62">
-        <v>1.30916979133889</v>
+        <v>1.338800163434056</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.316796258656222</v>
+        <v>3.262422549497924</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6539,22 +6539,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.06981952895991089</v>
+        <v>0.06977616113383223</v>
       </c>
       <c r="C63">
-        <v>861.6950510464399</v>
+        <v>843.6373293565591</v>
       </c>
       <c r="D63">
-        <v>1983.80105104644</v>
+        <v>1987.389329356559</v>
       </c>
       <c r="E63">
-        <v>106.7059999999999</v>
+        <v>128.3519999999999</v>
       </c>
       <c r="F63">
-        <v>1320.406</v>
+        <v>1342.052</v>
       </c>
       <c r="G63">
         <v>198.3</v>
@@ -6575,28 +6575,28 @@
         <v>276.125</v>
       </c>
       <c r="M63">
-        <v>84.63802460000001</v>
+        <v>86.0255332</v>
       </c>
       <c r="N63">
-        <v>191.4869754</v>
+        <v>190.0994668</v>
       </c>
       <c r="O63">
-        <v>47.75685166476001</v>
+        <v>47.41080701992001</v>
       </c>
       <c r="P63">
-        <v>143.73012373524</v>
+        <v>142.68865978008</v>
       </c>
       <c r="Q63">
-        <v>357.73012373524</v>
+        <v>356.68865978008</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1037700470766946</v>
+        <v>0.1051205682469269</v>
       </c>
       <c r="T63">
-        <v>1.338800163434056</v>
+        <v>1.369990028797389</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.262422549497924</v>
+        <v>3.209802830957635</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.06977616113383223</v>
+        <v>0.06973279330775356</v>
       </c>
       <c r="C64">
-        <v>843.6373293565591</v>
+        <v>825.5926120684362</v>
       </c>
       <c r="D64">
-        <v>1987.389329356559</v>
+        <v>1990.990612068436</v>
       </c>
       <c r="E64">
-        <v>128.3519999999999</v>
+        <v>149.9979999999998</v>
       </c>
       <c r="F64">
-        <v>1342.052</v>
+        <v>1363.698</v>
       </c>
       <c r="G64">
         <v>198.3</v>
@@ -6657,28 +6657,28 @@
         <v>276.125</v>
       </c>
       <c r="M64">
-        <v>86.0255332</v>
+        <v>87.4130418</v>
       </c>
       <c r="N64">
-        <v>190.0994668</v>
+        <v>188.7119582</v>
       </c>
       <c r="O64">
-        <v>47.41080701992001</v>
+        <v>47.06476237508</v>
       </c>
       <c r="P64">
-        <v>142.68865978008</v>
+        <v>141.64719582492</v>
       </c>
       <c r="Q64">
-        <v>356.68865978008</v>
+        <v>355.64719582492</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1051205682469269</v>
+        <v>0.1065440905614961</v>
       </c>
       <c r="T64">
-        <v>1.369990028797389</v>
+        <v>1.402865832829009</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.209802830957635</v>
+        <v>3.158853579672593</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6703,22 +6703,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.06973279330775356</v>
+        <v>0.06968942548167488</v>
       </c>
       <c r="C65">
-        <v>825.5926120684362</v>
+        <v>807.5609700049508</v>
       </c>
       <c r="D65">
-        <v>1990.990612068436</v>
+        <v>1994.604970004951</v>
       </c>
       <c r="E65">
-        <v>149.9979999999998</v>
+        <v>171.644</v>
       </c>
       <c r="F65">
-        <v>1363.698</v>
+        <v>1385.344</v>
       </c>
       <c r="G65">
         <v>198.3</v>
@@ -6739,28 +6739,28 @@
         <v>276.125</v>
       </c>
       <c r="M65">
-        <v>87.4130418</v>
+        <v>88.80055040000001</v>
       </c>
       <c r="N65">
-        <v>188.7119582</v>
+        <v>187.3244496</v>
       </c>
       <c r="O65">
-        <v>47.06476237508</v>
+        <v>46.71871773023999</v>
       </c>
       <c r="P65">
-        <v>141.64719582492</v>
+        <v>140.60573186976</v>
       </c>
       <c r="Q65">
-        <v>355.64719582492</v>
+        <v>354.60573186976</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1065440905614961</v>
+        <v>0.1080466974490969</v>
       </c>
       <c r="T65">
-        <v>1.402865832829009</v>
+        <v>1.437568070417943</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.158853579672593</v>
+        <v>3.109496492490208</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6785,22 +6785,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.06968942548167488</v>
+        <v>0.0696460576555962</v>
       </c>
       <c r="C66">
-        <v>807.5609700049508</v>
+        <v>789.5424745041926</v>
       </c>
       <c r="D66">
-        <v>1994.604970004951</v>
+        <v>1998.232474504192</v>
       </c>
       <c r="E66">
-        <v>171.644</v>
+        <v>193.29</v>
       </c>
       <c r="F66">
-        <v>1385.344</v>
+        <v>1406.99</v>
       </c>
       <c r="G66">
         <v>198.3</v>
@@ -6821,28 +6821,28 @@
         <v>276.125</v>
       </c>
       <c r="M66">
-        <v>88.80055040000001</v>
+        <v>90.18805900000001</v>
       </c>
       <c r="N66">
-        <v>187.3244496</v>
+        <v>185.936941</v>
       </c>
       <c r="O66">
-        <v>46.71871773023999</v>
+        <v>46.3726730854</v>
       </c>
       <c r="P66">
-        <v>140.60573186976</v>
+        <v>139.5642679146</v>
       </c>
       <c r="Q66">
-        <v>354.60573186976</v>
+        <v>353.5642679146</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1080466974490969</v>
+        <v>0.1096351675874178</v>
       </c>
       <c r="T66">
-        <v>1.437568070417943</v>
+        <v>1.474253293011958</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.109496492490208</v>
+        <v>3.061658084913436</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6867,22 +6867,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0696460576555962</v>
+        <v>0.06960268982951753</v>
       </c>
       <c r="C67">
-        <v>789.5424745041926</v>
+        <v>771.537197424153</v>
       </c>
       <c r="D67">
-        <v>1998.232474504192</v>
+        <v>2001.873197424153</v>
       </c>
       <c r="E67">
-        <v>193.29</v>
+        <v>214.9359999999999</v>
       </c>
       <c r="F67">
-        <v>1406.99</v>
+        <v>1428.636</v>
       </c>
       <c r="G67">
         <v>198.3</v>
@@ -6903,28 +6903,28 @@
         <v>276.125</v>
       </c>
       <c r="M67">
-        <v>90.18805900000001</v>
+        <v>91.5755676</v>
       </c>
       <c r="N67">
-        <v>185.936941</v>
+        <v>184.5494324</v>
       </c>
       <c r="O67">
-        <v>46.3726730854</v>
+        <v>46.02662844056</v>
       </c>
       <c r="P67">
-        <v>139.5642679146</v>
+        <v>138.52280395944</v>
       </c>
       <c r="Q67">
-        <v>353.5642679146</v>
+        <v>352.52280395944</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1096351675874178</v>
+        <v>0.1113170771456398</v>
       </c>
       <c r="T67">
-        <v>1.474253293011958</v>
+        <v>1.513096469876209</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.061658084913436</v>
+        <v>3.015269326051111</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6949,22 +6949,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.06960268982951753</v>
+        <v>0.07348195760343887</v>
       </c>
       <c r="C68">
-        <v>771.537197424153</v>
+        <v>469.3546005008322</v>
       </c>
       <c r="D68">
-        <v>2001.873197424153</v>
+        <v>1721.336600500832</v>
       </c>
       <c r="E68">
-        <v>214.9359999999999</v>
+        <v>236.5819999999999</v>
       </c>
       <c r="F68">
-        <v>1428.636</v>
+        <v>1450.282</v>
       </c>
       <c r="G68">
         <v>198.3</v>
@@ -6985,45 +6985,45 @@
         <v>276.125</v>
       </c>
       <c r="M68">
-        <v>91.5755676</v>
+        <v>104.2752758</v>
       </c>
       <c r="N68">
-        <v>184.5494324</v>
+        <v>171.8497242</v>
       </c>
       <c r="O68">
-        <v>46.02662844056</v>
+        <v>42.85932121548</v>
       </c>
       <c r="P68">
-        <v>138.52280395944</v>
+        <v>128.99040298452</v>
       </c>
       <c r="Q68">
-        <v>352.52280395944</v>
+        <v>342.99040298452</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1113170771456398</v>
+        <v>0.1131009206164814</v>
       </c>
       <c r="T68">
-        <v>1.513096469876209</v>
+        <v>1.554293778671627</v>
       </c>
       <c r="U68">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V68">
         <v>0.2494</v>
       </c>
       <c r="W68">
-        <v>0.04811346</v>
+        <v>0.05396814</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y68">
-        <v>3.015269326051111</v>
+        <v>2.648039028250645</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07348195760343887</v>
+        <v>0.07349713657736021</v>
       </c>
       <c r="C69">
-        <v>469.3546005008322</v>
+        <v>446.7652494329025</v>
       </c>
       <c r="D69">
-        <v>1721.336600500832</v>
+        <v>1720.393249432903</v>
       </c>
       <c r="E69">
-        <v>236.5819999999999</v>
+        <v>258.2280000000001</v>
       </c>
       <c r="F69">
-        <v>1450.282</v>
+        <v>1471.928</v>
       </c>
       <c r="G69">
         <v>198.3</v>
@@ -7067,28 +7067,28 @@
         <v>276.125</v>
       </c>
       <c r="M69">
-        <v>104.2752758</v>
+        <v>105.8316232</v>
       </c>
       <c r="N69">
-        <v>171.8497242</v>
+        <v>170.2933768</v>
       </c>
       <c r="O69">
-        <v>42.85932121548</v>
+        <v>42.47116817392</v>
       </c>
       <c r="P69">
-        <v>128.99040298452</v>
+        <v>127.82220862608</v>
       </c>
       <c r="Q69">
-        <v>342.99040298452</v>
+        <v>341.82220862608</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1131009206164814</v>
+        <v>0.1149962543042506</v>
       </c>
       <c r="T69">
-        <v>1.554293778671627</v>
+        <v>1.598065919266759</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.648039028250645</v>
+        <v>2.609097277835194</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7113,22 +7113,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07349713657736021</v>
+        <v>0.07351231555128152</v>
       </c>
       <c r="C70">
-        <v>446.7652494329025</v>
+        <v>424.1769317756425</v>
       </c>
       <c r="D70">
-        <v>1720.393249432903</v>
+        <v>1719.450931775643</v>
       </c>
       <c r="E70">
-        <v>258.2280000000001</v>
+        <v>279.874</v>
       </c>
       <c r="F70">
-        <v>1471.928</v>
+        <v>1493.574</v>
       </c>
       <c r="G70">
         <v>198.3</v>
@@ -7149,28 +7149,28 @@
         <v>276.125</v>
       </c>
       <c r="M70">
-        <v>105.8316232</v>
+        <v>107.3879706</v>
       </c>
       <c r="N70">
-        <v>170.2933768</v>
+        <v>168.7370294</v>
       </c>
       <c r="O70">
-        <v>42.47116817392</v>
+        <v>42.08301513236</v>
       </c>
       <c r="P70">
-        <v>127.82220862608</v>
+        <v>126.65401426764</v>
       </c>
       <c r="Q70">
-        <v>341.82220862608</v>
+        <v>340.65401426764</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1149962543042506</v>
+        <v>0.1170138675847791</v>
       </c>
       <c r="T70">
-        <v>1.598065919266759</v>
+        <v>1.644662068932544</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.609097277835194</v>
+        <v>2.571284273808597</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7195,22 +7195,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07351231555128152</v>
+        <v>0.07352749452520285</v>
       </c>
       <c r="C71">
-        <v>424.1769317756425</v>
+        <v>401.5896458318757</v>
       </c>
       <c r="D71">
-        <v>1719.450931775643</v>
+        <v>1718.509645831876</v>
       </c>
       <c r="E71">
-        <v>279.874</v>
+        <v>301.52</v>
       </c>
       <c r="F71">
-        <v>1493.574</v>
+        <v>1515.22</v>
       </c>
       <c r="G71">
         <v>198.3</v>
@@ -7231,28 +7231,28 @@
         <v>276.125</v>
       </c>
       <c r="M71">
-        <v>107.3879706</v>
+        <v>108.944318</v>
       </c>
       <c r="N71">
-        <v>168.7370294</v>
+        <v>167.180682</v>
       </c>
       <c r="O71">
-        <v>42.08301513236</v>
+        <v>41.6948620908</v>
       </c>
       <c r="P71">
-        <v>126.65401426764</v>
+        <v>125.4858199092</v>
       </c>
       <c r="Q71">
-        <v>340.65401426764</v>
+        <v>339.4858199092</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1170138675847791</v>
+        <v>0.1191659884173429</v>
       </c>
       <c r="T71">
-        <v>1.644662068932544</v>
+        <v>1.694364628576049</v>
       </c>
       <c r="U71">
         <v>0.07190000000000001</v>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.571284273808597</v>
+        <v>2.534551641325617</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7277,22 +7277,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07352749452520285</v>
+        <v>0.0756210848991242</v>
       </c>
       <c r="C72">
-        <v>401.5896458318757</v>
+        <v>259.2956122618343</v>
       </c>
       <c r="D72">
-        <v>1718.509645831876</v>
+        <v>1597.861612261834</v>
       </c>
       <c r="E72">
-        <v>301.52</v>
+        <v>323.1659999999999</v>
       </c>
       <c r="F72">
-        <v>1515.22</v>
+        <v>1536.866</v>
       </c>
       <c r="G72">
         <v>198.3</v>
@@ -7313,45 +7313,45 @@
         <v>276.125</v>
       </c>
       <c r="M72">
-        <v>108.944318</v>
+        <v>116.4944428</v>
       </c>
       <c r="N72">
-        <v>167.180682</v>
+        <v>159.6305572</v>
       </c>
       <c r="O72">
-        <v>41.6948620908</v>
+        <v>39.81186096568</v>
       </c>
       <c r="P72">
-        <v>125.4858199092</v>
+        <v>119.81869623432</v>
       </c>
       <c r="Q72">
-        <v>339.4858199092</v>
+        <v>333.81869623432</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1191659884173429</v>
+        <v>0.1214665313762903</v>
       </c>
       <c r="T72">
-        <v>1.694364628576049</v>
+        <v>1.747494950953588</v>
       </c>
       <c r="U72">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V72">
         <v>0.2494</v>
       </c>
       <c r="W72">
-        <v>0.05396814</v>
+        <v>0.05689548</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.534551641325617</v>
+        <v>2.370284739453683</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7359,22 +7359,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.0756210848991242</v>
+        <v>0.07566553727304554</v>
       </c>
       <c r="C73">
-        <v>259.2956122618345</v>
+        <v>235.2713278461401</v>
       </c>
       <c r="D73">
-        <v>1597.861612261834</v>
+        <v>1595.48332784614</v>
       </c>
       <c r="E73">
-        <v>323.1659999999997</v>
+        <v>344.8119999999999</v>
       </c>
       <c r="F73">
-        <v>1536.866</v>
+        <v>1558.512</v>
       </c>
       <c r="G73">
         <v>198.3</v>
@@ -7395,28 +7395,28 @@
         <v>276.125</v>
       </c>
       <c r="M73">
-        <v>116.4944428</v>
+        <v>118.1352096</v>
       </c>
       <c r="N73">
-        <v>159.6305572</v>
+        <v>157.9897904</v>
       </c>
       <c r="O73">
-        <v>39.81186096568</v>
+        <v>39.40265372576</v>
       </c>
       <c r="P73">
-        <v>119.81869623432</v>
+        <v>118.58713667424</v>
       </c>
       <c r="Q73">
-        <v>333.81869623432</v>
+        <v>332.58713667424</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1214665313762903</v>
+        <v>0.1239313988323054</v>
       </c>
       <c r="T73">
-        <v>1.747494950953587</v>
+        <v>1.804420296358094</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.370284739453683</v>
+        <v>2.337364118072382</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07566553727304554</v>
+        <v>0.07570998964696685</v>
       </c>
       <c r="C74">
-        <v>235.2713278461401</v>
+        <v>211.254112666471</v>
       </c>
       <c r="D74">
-        <v>1595.48332784614</v>
+        <v>1593.112112666471</v>
       </c>
       <c r="E74">
-        <v>344.8119999999999</v>
+        <v>366.4579999999999</v>
       </c>
       <c r="F74">
-        <v>1558.512</v>
+        <v>1580.158</v>
       </c>
       <c r="G74">
         <v>198.3</v>
@@ -7477,28 +7477,28 @@
         <v>276.125</v>
       </c>
       <c r="M74">
-        <v>118.1352096</v>
+        <v>119.7759764</v>
       </c>
       <c r="N74">
-        <v>157.9897904</v>
+        <v>156.3490236</v>
       </c>
       <c r="O74">
-        <v>39.40265372576</v>
+        <v>38.99344648584</v>
       </c>
       <c r="P74">
-        <v>118.58713667424</v>
+        <v>117.35557711416</v>
       </c>
       <c r="Q74">
-        <v>332.58713667424</v>
+        <v>331.35557711416</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1239313988323054</v>
+        <v>0.1265788490628402</v>
       </c>
       <c r="T74">
-        <v>1.804420296358094</v>
+        <v>1.865562334014785</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.337364118072382</v>
+        <v>2.305345431523445</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7523,22 +7523,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07570998964696685</v>
+        <v>0.07575444202088819</v>
       </c>
       <c r="C75">
-        <v>211.254112666471</v>
+        <v>187.2439352505983</v>
       </c>
       <c r="D75">
-        <v>1593.112112666471</v>
+        <v>1590.747935250598</v>
       </c>
       <c r="E75">
-        <v>366.4579999999999</v>
+        <v>388.1039999999998</v>
       </c>
       <c r="F75">
-        <v>1580.158</v>
+        <v>1601.804</v>
       </c>
       <c r="G75">
         <v>198.3</v>
@@ -7559,28 +7559,28 @@
         <v>276.125</v>
       </c>
       <c r="M75">
-        <v>119.7759764</v>
+        <v>121.4167432</v>
       </c>
       <c r="N75">
-        <v>156.3490236</v>
+        <v>154.7082568</v>
       </c>
       <c r="O75">
-        <v>38.99344648584</v>
+        <v>38.58423924592</v>
       </c>
       <c r="P75">
-        <v>117.35557711416</v>
+        <v>116.12401755408</v>
       </c>
       <c r="Q75">
-        <v>331.35557711416</v>
+        <v>330.1240175540801</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1265788490628402</v>
+        <v>0.1294299493111084</v>
       </c>
       <c r="T75">
-        <v>1.865562334014785</v>
+        <v>1.931407605337376</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.305345431523445</v>
+        <v>2.274192114881237</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07575444202088819</v>
+        <v>0.07579889439480951</v>
       </c>
       <c r="C76">
-        <v>187.2439352505983</v>
+        <v>163.2407643128395</v>
       </c>
       <c r="D76">
-        <v>1590.747935250598</v>
+        <v>1588.390764312839</v>
       </c>
       <c r="E76">
-        <v>388.1039999999998</v>
+        <v>409.7499999999998</v>
       </c>
       <c r="F76">
-        <v>1601.804</v>
+        <v>1623.45</v>
       </c>
       <c r="G76">
         <v>198.3</v>
@@ -7641,28 +7641,28 @@
         <v>276.125</v>
       </c>
       <c r="M76">
-        <v>121.4167432</v>
+        <v>123.05751</v>
       </c>
       <c r="N76">
-        <v>154.7082568</v>
+        <v>153.06749</v>
       </c>
       <c r="O76">
-        <v>38.58423924592</v>
+        <v>38.17503200600001</v>
       </c>
       <c r="P76">
-        <v>116.12401755408</v>
+        <v>114.892457994</v>
       </c>
       <c r="Q76">
-        <v>330.1240175540801</v>
+        <v>328.892457994</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1294299493111084</v>
+        <v>0.132509137579238</v>
       </c>
       <c r="T76">
-        <v>1.931407605337376</v>
+        <v>2.002520498365775</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.274192114881237</v>
+        <v>2.243869553349487</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7687,22 +7687,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07579889439480951</v>
+        <v>0.07584334676873083</v>
       </c>
       <c r="C77">
-        <v>163.2407643128395</v>
+        <v>139.2445687526726</v>
       </c>
       <c r="D77">
-        <v>1588.390764312839</v>
+        <v>1586.040568752673</v>
       </c>
       <c r="E77">
-        <v>409.7499999999998</v>
+        <v>431.396</v>
       </c>
       <c r="F77">
-        <v>1623.45</v>
+        <v>1645.096</v>
       </c>
       <c r="G77">
         <v>198.3</v>
@@ -7723,28 +7723,28 @@
         <v>276.125</v>
       </c>
       <c r="M77">
-        <v>123.05751</v>
+        <v>124.6982768</v>
       </c>
       <c r="N77">
-        <v>153.06749</v>
+        <v>151.4267232</v>
       </c>
       <c r="O77">
-        <v>38.17503200600001</v>
+        <v>37.76582476607999</v>
       </c>
       <c r="P77">
-        <v>114.892457994</v>
+        <v>113.66089843392</v>
       </c>
       <c r="Q77">
-        <v>328.892457994</v>
+        <v>327.66089843392</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.132509137579238</v>
+        <v>0.1358449248697118</v>
       </c>
       <c r="T77">
-        <v>2.002520498365775</v>
+        <v>2.079559465813207</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.243869553349487</v>
+        <v>2.214344953963309</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7769,22 +7769,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07584334676873083</v>
+        <v>0.07588779914265217</v>
       </c>
       <c r="C78">
-        <v>139.2445687526726</v>
+        <v>115.2553176533704</v>
       </c>
       <c r="D78">
-        <v>1586.040568752673</v>
+        <v>1583.69731765337</v>
       </c>
       <c r="E78">
-        <v>431.396</v>
+        <v>453.0419999999999</v>
       </c>
       <c r="F78">
-        <v>1645.096</v>
+        <v>1666.742</v>
       </c>
       <c r="G78">
         <v>198.3</v>
@@ -7805,28 +7805,28 @@
         <v>276.125</v>
       </c>
       <c r="M78">
-        <v>124.6982768</v>
+        <v>126.3390436</v>
       </c>
       <c r="N78">
-        <v>151.4267232</v>
+        <v>149.7859564</v>
       </c>
       <c r="O78">
-        <v>37.76582476607999</v>
+        <v>37.35661752615999</v>
       </c>
       <c r="P78">
-        <v>113.66089843392</v>
+        <v>112.42933887384</v>
       </c>
       <c r="Q78">
-        <v>327.66089843392</v>
+        <v>326.42933887384</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1358449248697118</v>
+        <v>0.1394707806202268</v>
       </c>
       <c r="T78">
-        <v>2.079559465813207</v>
+        <v>2.163297473908241</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.214344953963309</v>
+        <v>2.185587227288461</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7851,22 +7851,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07588779914265217</v>
+        <v>0.0759322515165735</v>
       </c>
       <c r="C79">
-        <v>115.2553176533704</v>
+        <v>91.27298028064524</v>
       </c>
       <c r="D79">
-        <v>1583.69731765337</v>
+        <v>1581.360980280645</v>
       </c>
       <c r="E79">
-        <v>453.0419999999999</v>
+        <v>474.6879999999999</v>
       </c>
       <c r="F79">
-        <v>1666.742</v>
+        <v>1688.388</v>
       </c>
       <c r="G79">
         <v>198.3</v>
@@ -7887,28 +7887,28 @@
         <v>276.125</v>
       </c>
       <c r="M79">
-        <v>126.3390436</v>
+        <v>127.9798104</v>
       </c>
       <c r="N79">
-        <v>149.7859564</v>
+        <v>148.1451896</v>
       </c>
       <c r="O79">
-        <v>37.35661752615999</v>
+        <v>36.94741028624</v>
       </c>
       <c r="P79">
-        <v>112.42933887384</v>
+        <v>111.19777931376</v>
       </c>
       <c r="Q79">
-        <v>326.42933887384</v>
+        <v>325.19777931376</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1394707806202268</v>
+        <v>0.1434262596207886</v>
       </c>
       <c r="T79">
-        <v>2.163297473908241</v>
+        <v>2.254648028193734</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.185587227288461</v>
+        <v>2.15756687822066</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7933,22 +7933,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.0759322515165735</v>
+        <v>0.07597670389049482</v>
       </c>
       <c r="C80">
-        <v>91.27298028064524</v>
+        <v>67.29752608130252</v>
       </c>
       <c r="D80">
-        <v>1581.360980280645</v>
+        <v>1579.031526081303</v>
       </c>
       <c r="E80">
-        <v>474.6879999999999</v>
+        <v>496.3340000000001</v>
       </c>
       <c r="F80">
-        <v>1688.388</v>
+        <v>1710.034</v>
       </c>
       <c r="G80">
         <v>198.3</v>
@@ -7969,28 +7969,28 @@
         <v>276.125</v>
       </c>
       <c r="M80">
-        <v>127.9798104</v>
+        <v>129.6205772</v>
       </c>
       <c r="N80">
-        <v>148.1451896</v>
+        <v>146.5044228</v>
       </c>
       <c r="O80">
-        <v>36.94741028624</v>
+        <v>36.53820304632</v>
       </c>
       <c r="P80">
-        <v>111.19777931376</v>
+        <v>109.96621975368</v>
       </c>
       <c r="Q80">
-        <v>325.19777931376</v>
+        <v>323.96621975368</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1434262596207886</v>
+        <v>0.1477584509071183</v>
       </c>
       <c r="T80">
-        <v>2.254648028193734</v>
+        <v>2.354698635268321</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.15756687822066</v>
+        <v>2.130255905078626</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07597670389049482</v>
+        <v>0.07602115626441616</v>
       </c>
       <c r="C81">
-        <v>67.29752608130252</v>
+        <v>43.32892468191153</v>
       </c>
       <c r="D81">
-        <v>1579.031526081303</v>
+        <v>1576.708924681912</v>
       </c>
       <c r="E81">
-        <v>496.3340000000001</v>
+        <v>517.98</v>
       </c>
       <c r="F81">
-        <v>1710.034</v>
+        <v>1731.68</v>
       </c>
       <c r="G81">
         <v>198.3</v>
@@ -8051,28 +8051,28 @@
         <v>276.125</v>
       </c>
       <c r="M81">
-        <v>129.6205772</v>
+        <v>131.261344</v>
       </c>
       <c r="N81">
-        <v>146.5044228</v>
+        <v>144.863656</v>
       </c>
       <c r="O81">
-        <v>36.53820304632</v>
+        <v>36.1289958064</v>
       </c>
       <c r="P81">
-        <v>109.96621975368</v>
+        <v>108.7346601936</v>
       </c>
       <c r="Q81">
-        <v>323.96621975368</v>
+        <v>322.7346601936</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1477584509071183</v>
+        <v>0.1525238613220808</v>
       </c>
       <c r="T81">
-        <v>2.354698635268321</v>
+        <v>2.464754303050366</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.130255905078626</v>
+        <v>2.103627706265144</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8097,22 +8097,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07602115626441616</v>
+        <v>0.07606560863833749</v>
       </c>
       <c r="C82">
-        <v>43.32892468191153</v>
+        <v>19.367145887486</v>
       </c>
       <c r="D82">
-        <v>1576.708924681912</v>
+        <v>1574.393145887486</v>
       </c>
       <c r="E82">
-        <v>517.98</v>
+        <v>539.626</v>
       </c>
       <c r="F82">
-        <v>1731.68</v>
+        <v>1753.326</v>
       </c>
       <c r="G82">
         <v>198.3</v>
@@ -8133,28 +8133,28 @@
         <v>276.125</v>
       </c>
       <c r="M82">
-        <v>131.261344</v>
+        <v>132.9021108</v>
       </c>
       <c r="N82">
-        <v>144.863656</v>
+        <v>143.2228892</v>
       </c>
       <c r="O82">
-        <v>36.1289958064</v>
+        <v>35.71978856648</v>
       </c>
       <c r="P82">
-        <v>108.7346601936</v>
+        <v>107.50310063352</v>
       </c>
       <c r="Q82">
-        <v>322.7346601936</v>
+        <v>321.50310063352</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1525238613220808</v>
+        <v>0.1577908938859868</v>
       </c>
       <c r="T82">
-        <v>2.464754303050366</v>
+        <v>2.586394777967363</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.103627706265144</v>
+        <v>2.077656993842117</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8179,22 +8179,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07606560863833749</v>
+        <v>0.07611006101225881</v>
       </c>
       <c r="C83">
-        <v>19.367145887486</v>
+        <v>-4.587840319828274</v>
       </c>
       <c r="D83">
-        <v>1574.393145887486</v>
+        <v>1572.084159680172</v>
       </c>
       <c r="E83">
-        <v>539.626</v>
+        <v>561.2719999999999</v>
       </c>
       <c r="F83">
-        <v>1753.326</v>
+        <v>1774.972</v>
       </c>
       <c r="G83">
         <v>198.3</v>
@@ -8215,28 +8215,28 @@
         <v>276.125</v>
       </c>
       <c r="M83">
-        <v>132.9021108</v>
+        <v>134.5428776</v>
       </c>
       <c r="N83">
-        <v>143.2228892</v>
+        <v>141.5821224</v>
       </c>
       <c r="O83">
-        <v>35.71978856648</v>
+        <v>35.31058132656</v>
       </c>
       <c r="P83">
-        <v>107.50310063352</v>
+        <v>106.27154107344</v>
       </c>
       <c r="Q83">
-        <v>321.50310063352</v>
+        <v>320.2715410734401</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1577908938859868</v>
+        <v>0.1636431522903268</v>
       </c>
       <c r="T83">
-        <v>2.586394777967363</v>
+        <v>2.721550861208472</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.077656993842117</v>
+        <v>2.052319713429409</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07611006101225881</v>
+        <v>0.07615451338618015</v>
       </c>
       <c r="C84">
-        <v>-4.587840319828274</v>
+        <v>-28.5360637820479</v>
       </c>
       <c r="D84">
-        <v>1572.084159680172</v>
+        <v>1569.781936217952</v>
       </c>
       <c r="E84">
-        <v>561.2719999999999</v>
+        <v>582.9180000000001</v>
       </c>
       <c r="F84">
-        <v>1774.972</v>
+        <v>1796.618</v>
       </c>
       <c r="G84">
         <v>198.3</v>
@@ -8297,28 +8297,28 @@
         <v>276.125</v>
       </c>
       <c r="M84">
-        <v>134.5428776</v>
+        <v>136.1836444</v>
       </c>
       <c r="N84">
-        <v>141.5821224</v>
+        <v>139.9413556</v>
       </c>
       <c r="O84">
-        <v>35.31058132656</v>
+        <v>34.90137408664</v>
       </c>
       <c r="P84">
-        <v>106.27154107344</v>
+        <v>105.03998151336</v>
       </c>
       <c r="Q84">
-        <v>320.2715410734401</v>
+        <v>319.03998151336</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1636431522903268</v>
+        <v>0.1701839116834127</v>
       </c>
       <c r="T84">
-        <v>2.721550861208472</v>
+        <v>2.872607660125005</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.052319713429409</v>
+        <v>2.027592969894114</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07615451338618015</v>
+        <v>0.07619896576010148</v>
       </c>
       <c r="C85">
-        <v>-28.5360637820479</v>
+        <v>-52.47755416663495</v>
       </c>
       <c r="D85">
-        <v>1569.781936217952</v>
+        <v>1567.486445833365</v>
       </c>
       <c r="E85">
-        <v>582.9180000000001</v>
+        <v>604.5640000000001</v>
       </c>
       <c r="F85">
-        <v>1796.618</v>
+        <v>1818.264</v>
       </c>
       <c r="G85">
         <v>198.3</v>
@@ -8379,28 +8379,28 @@
         <v>276.125</v>
       </c>
       <c r="M85">
-        <v>136.1836444</v>
+        <v>137.8244112</v>
       </c>
       <c r="N85">
-        <v>139.9413556</v>
+        <v>138.3005888</v>
       </c>
       <c r="O85">
-        <v>34.90137408664</v>
+        <v>34.49216684672</v>
       </c>
       <c r="P85">
-        <v>105.03998151336</v>
+        <v>103.80842195328</v>
       </c>
       <c r="Q85">
-        <v>319.03998151336</v>
+        <v>317.80842195328</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1701839116834127</v>
+        <v>0.1775422660006343</v>
       </c>
       <c r="T85">
-        <v>2.872607660125005</v>
+        <v>3.042546558906105</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.027592969894114</v>
+        <v>2.003454958347756</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8425,22 +8425,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07619896576010148</v>
+        <v>0.08530316013402281</v>
       </c>
       <c r="C86">
-        <v>-52.47755416663472</v>
+        <v>-435.3782293100335</v>
       </c>
       <c r="D86">
-        <v>1567.486445833365</v>
+        <v>1206.231770689966</v>
       </c>
       <c r="E86">
-        <v>604.5639999999999</v>
+        <v>626.2099999999998</v>
       </c>
       <c r="F86">
-        <v>1818.264</v>
+        <v>1839.91</v>
       </c>
       <c r="G86">
         <v>198.3</v>
@@ -8461,45 +8461,45 @@
         <v>276.125</v>
       </c>
       <c r="M86">
-        <v>137.8244112</v>
+        <v>165.5919</v>
       </c>
       <c r="N86">
-        <v>138.3005888</v>
+        <v>110.5331</v>
       </c>
       <c r="O86">
-        <v>34.49216684672</v>
+        <v>27.56695514</v>
       </c>
       <c r="P86">
-        <v>103.80842195328</v>
+        <v>82.96614485999999</v>
       </c>
       <c r="Q86">
-        <v>317.80842195328</v>
+        <v>296.96614486</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1775422660006342</v>
+        <v>0.1858817342268187</v>
       </c>
       <c r="T86">
-        <v>3.042546558906102</v>
+        <v>3.235143977524682</v>
       </c>
       <c r="U86">
-        <v>0.07580000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V86">
         <v>0.2494</v>
       </c>
       <c r="W86">
-        <v>0.05689548</v>
+        <v>0.067554</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y86">
-        <v>2.003454958347756</v>
+        <v>1.667503060234226</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08530316013402281</v>
+        <v>0.08545419770794414</v>
       </c>
       <c r="C87">
-        <v>-435.3782293100335</v>
+        <v>-461.6186059652782</v>
       </c>
       <c r="D87">
-        <v>1206.231770689966</v>
+        <v>1201.637394034722</v>
       </c>
       <c r="E87">
-        <v>626.2099999999998</v>
+        <v>647.8559999999998</v>
       </c>
       <c r="F87">
-        <v>1839.91</v>
+        <v>1861.556</v>
       </c>
       <c r="G87">
         <v>198.3</v>
@@ -8543,28 +8543,28 @@
         <v>276.125</v>
       </c>
       <c r="M87">
-        <v>165.5919</v>
+        <v>167.54004</v>
       </c>
       <c r="N87">
-        <v>110.5331</v>
+        <v>108.58496</v>
       </c>
       <c r="O87">
-        <v>27.56695514</v>
+        <v>27.081089024</v>
       </c>
       <c r="P87">
-        <v>82.96614485999999</v>
+        <v>81.503870976</v>
       </c>
       <c r="Q87">
-        <v>296.96614486</v>
+        <v>295.503870976</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1858817342268187</v>
+        <v>0.1954125550567438</v>
       </c>
       <c r="T87">
-        <v>3.235143977524682</v>
+        <v>3.455255313088773</v>
       </c>
       <c r="U87">
         <v>0.09000000000000001</v>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.667503060234226</v>
+        <v>1.648113489766386</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8589,22 +8589,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08545419770794414</v>
+        <v>0.08560523528186548</v>
       </c>
       <c r="C88">
-        <v>-461.6186059652782</v>
+        <v>-487.8241166789569</v>
       </c>
       <c r="D88">
-        <v>1201.637394034722</v>
+        <v>1197.077883321043</v>
       </c>
       <c r="E88">
-        <v>647.8559999999998</v>
+        <v>669.502</v>
       </c>
       <c r="F88">
-        <v>1861.556</v>
+        <v>1883.202</v>
       </c>
       <c r="G88">
         <v>198.3</v>
@@ -8625,28 +8625,28 @@
         <v>276.125</v>
       </c>
       <c r="M88">
-        <v>167.54004</v>
+        <v>169.48818</v>
       </c>
       <c r="N88">
-        <v>108.58496</v>
+        <v>106.63682</v>
       </c>
       <c r="O88">
-        <v>27.081089024</v>
+        <v>26.59522290799999</v>
       </c>
       <c r="P88">
-        <v>81.503870976</v>
+        <v>80.04159709199998</v>
       </c>
       <c r="Q88">
-        <v>295.503870976</v>
+        <v>294.041597092</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1954125550567438</v>
+        <v>0.2064096560143497</v>
       </c>
       <c r="T88">
-        <v>3.455255313088773</v>
+        <v>3.709229931047339</v>
       </c>
       <c r="U88">
         <v>0.09000000000000001</v>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.648113489766386</v>
+        <v>1.629169656550681</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8671,22 +8671,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08560523528186548</v>
+        <v>0.0857562728557868</v>
       </c>
       <c r="C89">
-        <v>-487.8241166789569</v>
+        <v>-513.9951568383394</v>
       </c>
       <c r="D89">
-        <v>1197.077883321043</v>
+        <v>1192.552843161661</v>
       </c>
       <c r="E89">
-        <v>669.502</v>
+        <v>691.1479999999999</v>
       </c>
       <c r="F89">
-        <v>1883.202</v>
+        <v>1904.848</v>
       </c>
       <c r="G89">
         <v>198.3</v>
@@ -8707,28 +8707,28 @@
         <v>276.125</v>
       </c>
       <c r="M89">
-        <v>169.48818</v>
+        <v>171.43632</v>
       </c>
       <c r="N89">
-        <v>106.63682</v>
+        <v>104.68868</v>
       </c>
       <c r="O89">
-        <v>26.59522290799999</v>
+        <v>26.109356792</v>
       </c>
       <c r="P89">
-        <v>80.04159709199998</v>
+        <v>78.57932320799998</v>
       </c>
       <c r="Q89">
-        <v>294.041597092</v>
+        <v>292.579323208</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2064096560143497</v>
+        <v>0.2192396071315567</v>
       </c>
       <c r="T89">
-        <v>3.709229931047339</v>
+        <v>4.005533651999</v>
       </c>
       <c r="U89">
         <v>0.09000000000000001</v>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.629169656550681</v>
+        <v>1.610656364998968</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8753,22 +8753,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.0857562728557868</v>
+        <v>0.08590731042970813</v>
       </c>
       <c r="C90">
-        <v>-513.9951568383394</v>
+        <v>-540.1321158748422</v>
       </c>
       <c r="D90">
-        <v>1192.552843161661</v>
+        <v>1188.061884125158</v>
       </c>
       <c r="E90">
-        <v>691.1479999999999</v>
+        <v>712.7939999999999</v>
       </c>
       <c r="F90">
-        <v>1904.848</v>
+        <v>1926.494</v>
       </c>
       <c r="G90">
         <v>198.3</v>
@@ -8789,28 +8789,28 @@
         <v>276.125</v>
       </c>
       <c r="M90">
-        <v>171.43632</v>
+        <v>173.38446</v>
       </c>
       <c r="N90">
-        <v>104.68868</v>
+        <v>102.74054</v>
       </c>
       <c r="O90">
-        <v>26.109356792</v>
+        <v>25.623490676</v>
       </c>
       <c r="P90">
-        <v>78.57932320799998</v>
+        <v>77.11704932399999</v>
       </c>
       <c r="Q90">
-        <v>292.579323208</v>
+        <v>291.117049324</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2192396071315567</v>
+        <v>0.2344022766337103</v>
       </c>
       <c r="T90">
-        <v>4.005533651999</v>
+        <v>4.355710776760053</v>
       </c>
       <c r="U90">
         <v>0.09000000000000001</v>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.610656364998968</v>
+        <v>1.59255910247089</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8835,22 +8835,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08590731042970813</v>
+        <v>0.08605834800362946</v>
       </c>
       <c r="C91">
-        <v>-540.1321158748422</v>
+        <v>-566.2353773757488</v>
       </c>
       <c r="D91">
-        <v>1188.061884125158</v>
+        <v>1183.604622624251</v>
       </c>
       <c r="E91">
-        <v>712.7939999999999</v>
+        <v>734.4399999999998</v>
       </c>
       <c r="F91">
-        <v>1926.494</v>
+        <v>1948.14</v>
       </c>
       <c r="G91">
         <v>198.3</v>
@@ -8871,28 +8871,28 @@
         <v>276.125</v>
       </c>
       <c r="M91">
-        <v>173.38446</v>
+        <v>175.3326</v>
       </c>
       <c r="N91">
-        <v>102.74054</v>
+        <v>100.7924</v>
       </c>
       <c r="O91">
-        <v>25.623490676</v>
+        <v>25.13762456</v>
       </c>
       <c r="P91">
-        <v>77.11704932399999</v>
+        <v>75.65477543999998</v>
       </c>
       <c r="Q91">
-        <v>291.117049324</v>
+        <v>289.65477544</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2344022766337103</v>
+        <v>0.2525974800362946</v>
       </c>
       <c r="T91">
-        <v>4.355710776760053</v>
+        <v>4.775923326473317</v>
       </c>
       <c r="U91">
         <v>0.09000000000000001</v>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.59255910247089</v>
+        <v>1.574864001332325</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8917,22 +8917,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08605834800362946</v>
+        <v>0.08620938557755078</v>
       </c>
       <c r="C92">
-        <v>-566.2353773757488</v>
+        <v>-592.3053191934275</v>
       </c>
       <c r="D92">
-        <v>1183.604622624251</v>
+        <v>1179.180680806573</v>
       </c>
       <c r="E92">
-        <v>734.4399999999998</v>
+        <v>756.086</v>
       </c>
       <c r="F92">
-        <v>1948.14</v>
+        <v>1969.786</v>
       </c>
       <c r="G92">
         <v>198.3</v>
@@ -8953,28 +8953,28 @@
         <v>276.125</v>
       </c>
       <c r="M92">
-        <v>175.3326</v>
+        <v>177.28074</v>
       </c>
       <c r="N92">
-        <v>100.7924</v>
+        <v>98.84425999999996</v>
       </c>
       <c r="O92">
-        <v>25.13762456</v>
+        <v>24.65175844399999</v>
       </c>
       <c r="P92">
-        <v>75.65477543999998</v>
+        <v>74.19250155599997</v>
       </c>
       <c r="Q92">
-        <v>289.65477544</v>
+        <v>288.192501556</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2525974800362946</v>
+        <v>0.2748360619727866</v>
       </c>
       <c r="T92">
-        <v>4.775923326473317</v>
+        <v>5.289516442789529</v>
       </c>
       <c r="U92">
         <v>0.09000000000000001</v>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.574864001332325</v>
+        <v>1.557557803515486</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8999,22 +8999,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08620938557755078</v>
+        <v>0.08636042315147213</v>
       </c>
       <c r="C93">
-        <v>-592.3053191934275</v>
+        <v>-618.3423135521116</v>
       </c>
       <c r="D93">
-        <v>1179.180680806573</v>
+        <v>1174.789686447888</v>
       </c>
       <c r="E93">
-        <v>756.086</v>
+        <v>777.732</v>
       </c>
       <c r="F93">
-        <v>1969.786</v>
+        <v>1991.432</v>
       </c>
       <c r="G93">
         <v>198.3</v>
@@ -9035,28 +9035,28 @@
         <v>276.125</v>
       </c>
       <c r="M93">
-        <v>177.28074</v>
+        <v>179.22888</v>
       </c>
       <c r="N93">
-        <v>98.84425999999996</v>
+        <v>96.89611999999997</v>
       </c>
       <c r="O93">
-        <v>24.65175844399999</v>
+        <v>24.16589232799999</v>
       </c>
       <c r="P93">
-        <v>74.19250155599997</v>
+        <v>72.73022767199997</v>
       </c>
       <c r="Q93">
-        <v>288.192501556</v>
+        <v>286.730227672</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2748360619727866</v>
+        <v>0.3026342893934016</v>
       </c>
       <c r="T93">
-        <v>5.289516442789529</v>
+        <v>5.931507838184796</v>
       </c>
       <c r="U93">
         <v>0.09000000000000001</v>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.557557803515486</v>
+        <v>1.540627827390318</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9081,22 +9081,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08636042315147213</v>
+        <v>0.08651146072539345</v>
       </c>
       <c r="C94">
-        <v>-618.3423135521116</v>
+        <v>-644.3467271522945</v>
       </c>
       <c r="D94">
-        <v>1174.789686447888</v>
+        <v>1170.431272847705</v>
       </c>
       <c r="E94">
-        <v>777.732</v>
+        <v>799.3779999999999</v>
       </c>
       <c r="F94">
-        <v>1991.432</v>
+        <v>2013.078</v>
       </c>
       <c r="G94">
         <v>198.3</v>
@@ -9117,28 +9117,28 @@
         <v>276.125</v>
       </c>
       <c r="M94">
-        <v>179.22888</v>
+        <v>181.17702</v>
       </c>
       <c r="N94">
-        <v>96.89611999999997</v>
+        <v>94.94797999999997</v>
       </c>
       <c r="O94">
-        <v>24.16589232799999</v>
+        <v>23.68002621199999</v>
       </c>
       <c r="P94">
-        <v>72.73022767199997</v>
+        <v>71.26795378799997</v>
       </c>
       <c r="Q94">
-        <v>286.730227672</v>
+        <v>285.267953788</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3026342893934016</v>
+        <v>0.3383748675056209</v>
       </c>
       <c r="T94">
-        <v>5.931507838184796</v>
+        <v>6.756925346550137</v>
       </c>
       <c r="U94">
         <v>0.09000000000000001</v>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.540627827390318</v>
+        <v>1.524061936773217</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9163,22 +9163,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08651146072539345</v>
+        <v>0.08666249829931477</v>
       </c>
       <c r="C95">
-        <v>-644.3467271522945</v>
+        <v>-670.3189212728221</v>
       </c>
       <c r="D95">
-        <v>1170.431272847705</v>
+        <v>1166.105078727178</v>
       </c>
       <c r="E95">
-        <v>799.3779999999999</v>
+        <v>821.0239999999999</v>
       </c>
       <c r="F95">
-        <v>2013.078</v>
+        <v>2034.724</v>
       </c>
       <c r="G95">
         <v>198.3</v>
@@ -9199,28 +9199,28 @@
         <v>276.125</v>
       </c>
       <c r="M95">
-        <v>181.17702</v>
+        <v>183.12516</v>
       </c>
       <c r="N95">
-        <v>94.94797999999997</v>
+        <v>92.99983999999998</v>
       </c>
       <c r="O95">
-        <v>23.68002621199999</v>
+        <v>23.19416009599999</v>
       </c>
       <c r="P95">
-        <v>71.26795378799997</v>
+        <v>69.80567990399999</v>
       </c>
       <c r="Q95">
-        <v>285.267953788</v>
+        <v>283.805679904</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3383748675056209</v>
+        <v>0.3860289716552466</v>
       </c>
       <c r="T95">
-        <v>6.756925346550137</v>
+        <v>7.857482024370592</v>
       </c>
       <c r="U95">
         <v>0.09000000000000001</v>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.524061936773217</v>
+        <v>1.507848511913928</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9245,22 +9245,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08666249829931477</v>
+        <v>0.1308216841750686</v>
       </c>
       <c r="C96">
-        <v>-670.3189212728221</v>
+        <v>-1297.625129275076</v>
       </c>
       <c r="D96">
-        <v>1166.105078727178</v>
+        <v>560.4448707249237</v>
       </c>
       <c r="E96">
-        <v>821.0239999999999</v>
+        <v>842.6699999999998</v>
       </c>
       <c r="F96">
-        <v>2034.724</v>
+        <v>2056.37</v>
       </c>
       <c r="G96">
         <v>198.3</v>
@@ -9281,45 +9281,45 @@
         <v>276.125</v>
       </c>
       <c r="M96">
-        <v>183.12516</v>
+        <v>301.875116</v>
       </c>
       <c r="N96">
-        <v>92.99983999999998</v>
+        <v>-25.75011599999999</v>
       </c>
       <c r="O96">
-        <v>23.19416009599999</v>
+        <v>-6.422078930399998</v>
       </c>
       <c r="P96">
-        <v>69.80567990399999</v>
+        <v>-19.32803706959999</v>
       </c>
       <c r="Q96">
-        <v>283.805679904</v>
+        <v>194.6719629304</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3860289716552466</v>
+        <v>0.4635228362316688</v>
       </c>
       <c r="T96">
-        <v>7.857482024370592</v>
+        <v>9.647178665858405</v>
       </c>
       <c r="U96">
-        <v>0.09000000000000001</v>
+        <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2494</v>
+        <v>0.2281260407035339</v>
       </c>
       <c r="W96">
-        <v>0.067554</v>
+        <v>0.1133110972247212</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y96">
-        <v>1.507848511913928</v>
+        <v>0.9146994414736722</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9327,22 +9327,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1308216841750686</v>
+        <v>0.1318316841750686</v>
       </c>
       <c r="C97">
-        <v>-1297.625129275076</v>
+        <v>-1325.850674065578</v>
       </c>
       <c r="D97">
-        <v>560.4448707249237</v>
+        <v>553.865325934422</v>
       </c>
       <c r="E97">
-        <v>842.6699999999998</v>
+        <v>864.316</v>
       </c>
       <c r="F97">
-        <v>2056.37</v>
+        <v>2078.016</v>
       </c>
       <c r="G97">
         <v>198.3</v>
@@ -9363,37 +9363,37 @@
         <v>276.125</v>
       </c>
       <c r="M97">
-        <v>301.875116</v>
+        <v>305.0527488</v>
       </c>
       <c r="N97">
-        <v>-25.75011599999999</v>
+        <v>-28.92774880000002</v>
       </c>
       <c r="O97">
-        <v>-6.422078930399998</v>
+        <v>-7.214580550720004</v>
       </c>
       <c r="P97">
-        <v>-19.32803706959999</v>
+        <v>-21.71316824928001</v>
       </c>
       <c r="Q97">
-        <v>194.6719629304</v>
+        <v>192.28683175072</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4635228362316688</v>
+        <v>0.5679535452895863</v>
       </c>
       <c r="T97">
-        <v>9.647178665858405</v>
+        <v>12.05897333232301</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2281260407035339</v>
+        <v>0.2257497277795387</v>
       </c>
       <c r="W97">
-        <v>0.1133110972247212</v>
+        <v>0.1136599399619637</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.9146994414736722</v>
+        <v>0.9051713222916548</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9409,22 +9409,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1318316841750686</v>
+        <v>0.1328416841750686</v>
       </c>
       <c r="C98">
-        <v>-1325.850674065578</v>
+        <v>-1353.923525573513</v>
       </c>
       <c r="D98">
-        <v>553.865325934422</v>
+        <v>547.4384744264868</v>
       </c>
       <c r="E98">
-        <v>864.3159999999996</v>
+        <v>885.9619999999998</v>
       </c>
       <c r="F98">
-        <v>2078.016</v>
+        <v>2099.662</v>
       </c>
       <c r="G98">
         <v>198.3</v>
@@ -9445,37 +9445,37 @@
         <v>276.125</v>
       </c>
       <c r="M98">
-        <v>305.0527488</v>
+        <v>308.2303816</v>
       </c>
       <c r="N98">
-        <v>-28.92774879999996</v>
+        <v>-32.10538159999999</v>
       </c>
       <c r="O98">
-        <v>-7.21458055071999</v>
+        <v>-8.007082171039997</v>
       </c>
       <c r="P98">
-        <v>-21.71316824927997</v>
+        <v>-24.09829942895999</v>
       </c>
       <c r="Q98">
-        <v>192.2868317507201</v>
+        <v>189.90170057104</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5679535452895849</v>
+        <v>0.7420047270527798</v>
       </c>
       <c r="T98">
-        <v>12.05897333232298</v>
+        <v>16.07863110976397</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2257497277795387</v>
+        <v>0.2234224109983064</v>
       </c>
       <c r="W98">
-        <v>0.1136599399619637</v>
+        <v>0.1140015900654486</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.9051713222916549</v>
+        <v>0.895839659175246</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9491,22 +9491,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1328416841750686</v>
+        <v>0.1338516841750686</v>
       </c>
       <c r="C99">
-        <v>-1353.923525573513</v>
+        <v>-1381.848938220197</v>
       </c>
       <c r="D99">
-        <v>547.4384744264868</v>
+        <v>541.1590617798028</v>
       </c>
       <c r="E99">
-        <v>885.9619999999998</v>
+        <v>907.6079999999999</v>
       </c>
       <c r="F99">
-        <v>2099.662</v>
+        <v>2121.308</v>
       </c>
       <c r="G99">
         <v>198.3</v>
@@ -9527,37 +9527,37 @@
         <v>276.125</v>
       </c>
       <c r="M99">
-        <v>308.2303816</v>
+        <v>311.4080144</v>
       </c>
       <c r="N99">
-        <v>-32.10538159999999</v>
+        <v>-35.28301440000001</v>
       </c>
       <c r="O99">
-        <v>-8.007082171039997</v>
+        <v>-8.799583791360003</v>
       </c>
       <c r="P99">
-        <v>-24.09829942895999</v>
+        <v>-26.48343060864001</v>
       </c>
       <c r="Q99">
-        <v>189.90170057104</v>
+        <v>187.51656939136</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7420047270527798</v>
+        <v>1.09010709057917</v>
       </c>
       <c r="T99">
-        <v>16.07863110976397</v>
+        <v>24.11794666464596</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2234224109983064</v>
+        <v>0.2211425904779155</v>
       </c>
       <c r="W99">
-        <v>0.1140015900654486</v>
+        <v>0.114336267717842</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.895839659175246</v>
+        <v>0.8866984381632537</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9573,22 +9573,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1338516841750686</v>
+        <v>0.1348616841750686</v>
       </c>
       <c r="C100">
-        <v>-1381.848938220197</v>
+        <v>-1409.631928076836</v>
       </c>
       <c r="D100">
-        <v>541.1590617798028</v>
+        <v>535.0220719231633</v>
       </c>
       <c r="E100">
-        <v>907.6079999999999</v>
+        <v>929.2539999999997</v>
       </c>
       <c r="F100">
-        <v>2121.308</v>
+        <v>2142.954</v>
       </c>
       <c r="G100">
         <v>198.3</v>
@@ -9609,37 +9609,37 @@
         <v>276.125</v>
       </c>
       <c r="M100">
-        <v>311.4080144</v>
+        <v>314.5856472</v>
       </c>
       <c r="N100">
-        <v>-35.28301440000001</v>
+        <v>-38.46064719999998</v>
       </c>
       <c r="O100">
-        <v>-8.799583791360003</v>
+        <v>-9.592085411679996</v>
       </c>
       <c r="P100">
-        <v>-26.48343060864001</v>
+        <v>-28.86856178831999</v>
       </c>
       <c r="Q100">
-        <v>187.51656939136</v>
+        <v>185.13143821168</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.09010709057917</v>
+        <v>2.134414181158339</v>
       </c>
       <c r="T100">
-        <v>24.11794666464596</v>
+        <v>48.23589332929192</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2211425904779155</v>
+        <v>0.2189088269377345</v>
       </c>
       <c r="W100">
-        <v>0.114336267717842</v>
+        <v>0.1146641842055406</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9647,91 +9647,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8866984381632537</v>
+        <v>0.8777418882828167</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1348616841750686</v>
-      </c>
-      <c r="C101">
-        <v>-1409.631928076836</v>
-      </c>
-      <c r="D101">
-        <v>535.0220719231633</v>
-      </c>
-      <c r="E101">
-        <v>929.2539999999997</v>
-      </c>
-      <c r="F101">
-        <v>2142.954</v>
-      </c>
-      <c r="G101">
-        <v>198.3</v>
-      </c>
-      <c r="H101">
-        <v>950.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>490.125</v>
-      </c>
-      <c r="K101">
-        <v>214</v>
-      </c>
-      <c r="L101">
-        <v>276.125</v>
-      </c>
-      <c r="M101">
-        <v>314.5856472</v>
-      </c>
-      <c r="N101">
-        <v>-38.46064719999998</v>
-      </c>
-      <c r="O101">
-        <v>-9.592085411679996</v>
-      </c>
-      <c r="P101">
-        <v>-28.86856178831999</v>
-      </c>
-      <c r="Q101">
-        <v>185.13143821168</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.134414181158339</v>
-      </c>
-      <c r="T101">
-        <v>48.23589332929192</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2189088269377345</v>
-      </c>
-      <c r="W101">
-        <v>0.1146641842055406</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8777418882828167</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
